--- a/项目计划/提交文件/项目计划表_四人仿真.xlsx
+++ b/项目计划/提交文件/项目计划表_四人仿真.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目总表" sheetId="1" r:id="Rb0076badfe8045dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务与甘特" sheetId="2" r:id="R196f536f9cff4ca9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源计划" sheetId="3" r:id="R3b664ec1103a422a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本预算" sheetId="4" r:id="Rce87b4ae43a8476c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="质量与变更" sheetId="5" r:id="R69773a7453474886"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日期甘特" sheetId="6" r:id="R4e08418ace814f06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目总表" sheetId="1" r:id="R4c747586d83f447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务与甘特" sheetId="2" r:id="R5e629adf0d6e4f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源计划" sheetId="3" r:id="Rdce2c8a266ec4b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本预算" sheetId="4" r:id="Rc35cee75e0f042cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="质量与变更" sheetId="5" r:id="R739410d1fec4422d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日期甘特" sheetId="6" r:id="Rf347a7541df5444a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -511,7 +511,7 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>全部日期、投入与费用为教学仿真设定。计划包含44项业务活动；实际执行记录、提交平台和格式留空。</x:v>
+        <x:v>本计划采用4人、8周的模拟项目设定，覆盖44项活动。实际执行数据在发生后记录。</x:v>
       </x:c>
       <x:c r="B4" s="4"/>
       <x:c r="C4" s="4"/>
@@ -562,7 +562,7 @@
         <x:v>需求已知</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>沿用大作业一需求，覆盖FR-01～28、NFR-01～11、IF-01～04</x:v>
+        <x:v>依据SRS V1.2需求基线，覆盖FR-01～28、NFR-01～11、IF-01～04。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="45" customHeight="1">
@@ -573,10 +573,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>课上要求</x:v>
+        <x:v>编制信息</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>大作业二，个人提交完整项目计划</x:v>
+        <x:v>项目经理负责本计划的编制、维护与提交。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="45" customHeight="1">
@@ -590,7 +590,7 @@
         <x:v>已知</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>2026-10-14完成计划补全；不代表项目实际开始。</x:v>
+        <x:v>本版计划编制日期为2026-10-14，项目开工日期按进度计划执行。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="45" customHeight="1">
@@ -601,10 +601,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>课上要求</x:v>
+        <x:v>工期约束</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>老师01:47、31:03</x:v>
+        <x:v>项目周期为8周，每周5个工作日，共40个工作日。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="45" customHeight="1">
@@ -615,10 +615,10 @@
         <x:v>3–5人</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>课上要求</x:v>
+        <x:v>人员配置约束</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>老师30:27口头调整人数，取代课件的10人</x:v>
+        <x:v>团队规模控制在3–5人，本计划配置4人。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="45" customHeight="1">
@@ -630,8 +630,8 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:f>IF(ISNUMBER(B13),IF(AND(B13&gt;=3,B13&lt;=5),"人数符合课上范围","人数需调整至3–5"),"待确认，留空")</x:f>
-        <x:v>人数符合课上范围</x:v>
+        <x:f>IF(ISNUMBER(B13),IF(AND(B13&gt;=3,B13&lt;=5),"团队规模符合计划约束","团队规模须为3–5人"),"待确认，留空")</x:f>
+        <x:v>团队规模符合计划约束</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
         <x:v>R01–R04明确启用，R05停用；不表示已确认真实团队成员。</x:v>
@@ -682,17 +682,17 @@
     </x:row>
     <x:row r="17" ht="45" customHeight="1">
       <x:c r="A17" s="9" t="str">
-        <x:v>作业截止日期</x:v>
+        <x:v>计划提交截止日期</x:v>
       </x:c>
       <x:c r="B17" s="15" t="n">
         <x:f>B15+B11*7-1</x:f>
         <x:v>46369</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>用户约定</x:v>
+        <x:v>提交期限</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>从模拟开工日计算，截止第8自然周末；按用户设定。</x:v>
+        <x:v>从计划开工日计算，提交截止为第8自然周末。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="45" customHeight="1">
@@ -730,13 +730,13 @@
         <x:v>关键路径及可行性</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>Project已核算，40工作日完成；逐日负荷≤8人时/人</x:v>
+        <x:v>40个工作日完成计划活动；人员每日分配投入不超过8小时。</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>仿真核验通过</x:v>
+        <x:v>进度与资源平衡</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>关键任务含持续计划管理；使用资源平衡后的不早于开始约束，结果仅适用于本版本。</x:v>
+        <x:v>采用资源平衡后的不早于开始约束；资源或依赖变更后重新核算关键路径。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="45" customHeight="1">
@@ -748,7 +748,7 @@
         <x:v>待确认，留空</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>老师展示Project并提到其他工具，未指定上传平台及文件格式</x:v>
+        <x:v>计划提交平台、文件格式及命名规则待确定。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="45" customHeight="1">
@@ -782,7 +782,7 @@
         <x:v>计划部分</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
-        <x:v>初稿安排</x:v>
+        <x:v>计划安排</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
         <x:v>对应工作表</x:v>
@@ -1010,7 +1010,7 @@
         <x:v>完整验收计划、交付证据包、个人项目计划</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>完整验收须包含AC-10B；本文件未声明实际通过</x:v>
+        <x:v>最终验收须满足SRS验收标准，包括AC-10B真实交换验证。</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="30" customHeight="1">
@@ -1027,58 +1027,58 @@
     </x:row>
     <x:row r="45" ht="38" customHeight="1">
       <x:c r="A45" s="11" t="str">
-        <x:v>依据/分类</x:v>
+        <x:v>计划依据/分类</x:v>
       </x:c>
       <x:c r="B45" s="11" t="str">
         <x:v>内容</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>定位</x:v>
+        <x:v>适用范围</x:v>
       </x:c>
       <x:c r="D45" s="11" t="str">
-        <x:v>用途</x:v>
+        <x:v>控制要求</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="60" customHeight="1">
       <x:c r="A46" s="9" t="str">
-        <x:v>课堂要求</x:v>
+        <x:v>计划约束</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>个人提交，8周，3–5人，范围/进度/成本/质量计划及持续迭代</x:v>
+        <x:v>周期8周；团队规模3–5人，配置4人；统一管理范围、进度、成本和质量。</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
-        <x:v>10月12日 01:04–02:19、30:27–31:03</x:v>
+        <x:v>项目总表、任务与甘特、资源计划</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>作为计划约束</x:v>
+        <x:v>作为计划编制与实施的约束。</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="60" customHeight="1">
       <x:c r="A47" s="9" t="str">
-        <x:v>课堂方法</x:v>
+        <x:v>进度与资源管理</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>资源冲突、关键路径、渐进明细与可验证迭代成果</x:v>
+        <x:v>依据WBS确定活动顺序和工期，统筹关键路径、人员负荷与迭代交付。</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
-        <x:v>05:53–22:20</x:v>
+        <x:v>任务与甘特、资源计划、日期甘特</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>用于任务和资源安排</x:v>
+        <x:v>按任务依赖和资源可用容量安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="60" customHeight="1">
       <x:c r="A48" s="9" t="str">
-        <x:v>课堂成本</x:v>
+        <x:v>成本管理规则</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>直接/间接、人力/非人力、分时预算与管理储备</x:v>
+        <x:v>区分直接/间接、人力/非人力成本，按周编制预算，管理储备单列。</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
-        <x:v>35:29–37:03、45:21、52:57–55:59</x:v>
+        <x:v>成本预算</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>用于成本预算结构</x:v>
+        <x:v>成本基准与任务进度、工作量保持一致。</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="60" customHeight="1">
@@ -1100,13 +1100,13 @@
         <x:v>暂时性实施规划</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>本表任务拆分、相对周次、里程碑与计划复核安排</x:v>
+        <x:v>任务分解、依赖关系、阶段里程碑与计划复核安排。</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>初稿建议，待成员和工作量确认后修订</x:v>
+        <x:v>本版计划基线</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>不作为实际进度或通过记录</x:v>
+        <x:v>计划调整按版本记录，实际执行数据另行登记。</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
@@ -1134,7 +1134,7 @@
         <x:v>本次编制</x:v>
       </x:c>
       <x:c r="D52" s="29" t="str">
-        <x:v>由初稿补齐，后续复核沿用版本记录</x:v>
+        <x:v>当前计划版本为V1.0，后续调整按版本记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
@@ -1313,7 +1313,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="36" t="str">
-        <x:v>人员、费率、设备及采购金额均为教学仿真设定，非市场报价或实际支出</x:v>
+        <x:v>人员、费率、设备与采购金额均为模拟估算，实际支出另行记录。</x:v>
       </x:c>
       <x:c r="B67" s="36"/>
       <x:c r="C67" s="36"/>
@@ -7911,7 +7911,7 @@
         <x:v>46367</x:v>
       </x:c>
       <x:c r="V50" s="9" t="str">
-        <x:v>课堂大作业二</x:v>
+        <x:v>完整计划及版本记录评审</x:v>
       </x:c>
       <x:c r="W50" s="9" t="str">
         <x:v>项目经理和QA并行复核最终计划，与仿真验收安排同日定稿；不等待或虚构实际执行结果；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
@@ -10368,7 +10368,7 @@
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>成本控制基准不含管理储备；总预算包含10%管理储备。全部为教学估算，实际支出未发生。</x:v>
+        <x:v>成本控制基准不含管理储备，总预算包含10%管理储备。本表为模拟估算，实际支出在发生后记录。</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -12713,7 +12713,7 @@
         <x:v>可能影响</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>初稿应对安排</x:v>
+        <x:v>风险应对措施</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
         <x:v>责任人</x:v>

--- a/项目计划/提交文件/项目计划表_四人仿真.xlsx
+++ b/项目计划/提交文件/项目计划表_四人仿真.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目总表" sheetId="1" r:id="R189d85f5acf546f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务与甘特" sheetId="2" r:id="R33c458f0d3434eb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源计划" sheetId="3" r:id="R3c8e78aaa33f4cec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本预算" sheetId="4" r:id="R79cd1842ce7c4022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="质量与变更" sheetId="5" r:id="R492f75c9d7754760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日期甘特" sheetId="6" r:id="R609664471e8a4dd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目总表" sheetId="1" r:id="Rb0076badfe8045dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务与甘特" sheetId="2" r:id="R196f536f9cff4ca9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源计划" sheetId="3" r:id="R3b664ec1103a422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本预算" sheetId="4" r:id="Rce87b4ae43a8476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="质量与变更" sheetId="5" r:id="R69773a7453474886"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日期甘特" sheetId="6" r:id="R4e08418ace814f06"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -511,7 +511,7 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>全部日期、投入与费用为教学仿真设定。计划包含44项业务活动；实际执行及作业提交信息留空。</x:v>
+        <x:v>全部日期、投入与费用为教学仿真设定。计划包含44项业务活动；实际执行记录、提交平台和格式留空。</x:v>
       </x:c>
       <x:c r="B4" s="4"/>
       <x:c r="C4" s="4"/>
@@ -684,12 +684,15 @@
       <x:c r="A17" s="9" t="str">
         <x:v>作业截止日期</x:v>
       </x:c>
-      <x:c r="B17" s="15"/>
+      <x:c r="B17" s="15" t="n">
+        <x:f>B15+B11*7-1</x:f>
+        <x:v>46369</x:v>
+      </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>待确认，留空</x:v>
+        <x:v>用户约定</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>课堂所核对说明未明确截止日期</x:v>
+        <x:v>从模拟开工日计算，截止第8自然周末；按用户设定。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="45" customHeight="1">

--- a/项目计划/提交文件/项目计划表_四人仿真.xlsx
+++ b/项目计划/提交文件/项目计划表_四人仿真.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目总表" sheetId="1" r:id="R4c747586d83f447c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务与甘特" sheetId="2" r:id="R5e629adf0d6e4f1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源计划" sheetId="3" r:id="Rdce2c8a266ec4b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本预算" sheetId="4" r:id="Rc35cee75e0f042cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="质量与变更" sheetId="5" r:id="R739410d1fec4422d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日期甘特" sheetId="6" r:id="Rf347a7541df5444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目总表" sheetId="1" r:id="Ra7b3c7cf53924a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务与甘特" sheetId="2" r:id="R3ccd34fa917d489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源计划" sheetId="3" r:id="R86089b04b3b24999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本预算" sheetId="4" r:id="Rf705290a8ae345ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="质量与变更" sheetId="5" r:id="R499151838b3a4181"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日期甘特" sheetId="6" r:id="R22acb462c5ba4035"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -29,7 +29,7 @@
     <x:numFmt numFmtId="207" formatCode="0"/>
     <x:numFmt numFmtId="208" formatCode="m/d"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -75,13 +75,23 @@
       <x:color rgb="FF111111"/>
       <x:name val="SimSun"/>
     </x:font>
+    <x:font>
+      <x:sz val="10.5"/>
+      <x:color rgb="FF111111"/>
+      <x:name val="SimSun"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -121,7 +131,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="57">
+  <x:cellXfs count="76">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -280,6 +290,53 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -497,7 +554,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>项目计划表（4人8周仿真，V1.0）</x:v>
+        <x:v>项目计划表（4人8周仿真，V1.1）</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -584,13 +641,13 @@
         <x:v>本版编制日期</x:v>
       </x:c>
       <x:c r="B10" s="12" t="d">
-        <x:v>2026-10-14T00:00:00.000Z</x:v>
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>已知</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>本版计划编制日期为2026-10-14，项目开工日期按进度计划执行。</x:v>
+        <x:v>本版修订日期为2026-10-20；计划开工与完成日期按既定排期执行。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="45" customHeight="1">
@@ -838,13 +895,13 @@
         <x:v>成本估算</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>按任务难度、模块复用与投入人时估算；人工加非人工与间接费用</x:v>
+        <x:v>按WBS活动分资源人时×仿真费率自下而上汇总，非人工与间接费用分项估算。</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
         <x:v>成本预算</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>金额为仿真估算，不是报价或已发生支出</x:v>
+        <x:v>依据、方法和假设可追溯；不确定项逐轮复核，未确认参数留空。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="66" customHeight="1">
@@ -852,13 +909,13 @@
         <x:v>成本预算</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>W1–W8分周预算；成本控制基准加10%管理储备</x:v>
+        <x:v>W1–W8分周成本基准；10%管理储备单列；已识别风险应急储备尚未单列。</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
         <x:v>成本预算</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>管理储备预留额度独立于基准，实际支出未发生</x:v>
+        <x:v>基准、储备与实际支出分别管理；储备调整须办理基线变更。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="66" customHeight="1">
@@ -880,13 +937,13 @@
         <x:v>迭代</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>W2/W4/W6/W8复核；本次V0.1→V1.0补全人员、排期和预算</x:v>
+        <x:v>W1–W8每周复核并记录；W2/W4/W6/W8开展阶段重点复核。</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
         <x:v>质量与变更</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>后续版本和变更实际发生后再记录</x:v>
+        <x:v>逐轮记录真实产出、估算细化、偏差及版本；无基线变化时不制造修订。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="66" customHeight="1">
@@ -1072,13 +1129,13 @@
         <x:v>成本管理规则</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>区分直接/间接、人力/非人力成本，按周编制预算，管理储备单列。</x:v>
+        <x:v>估算、预算和控制形成闭环；分周成本基准与AC、EV分别记录，应急与管理储备分开管理。</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
         <x:v>成本预算</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>成本基准与任务进度、工作量保持一致。</x:v>
+        <x:v>实际成本和完成工作预算未发生时留空；基线变化经变更流程处理。</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="60" customHeight="1">
@@ -1100,13 +1157,13 @@
         <x:v>暂时性实施规划</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>任务分解、依赖关系、阶段里程碑与计划复核安排。</x:v>
+        <x:v>沿用既有任务与投入，按周细化估算假设、外部条件、成本偏差和风险响应。</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
         <x:v>本版计划基线</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>计划调整按版本记录，实际执行数据另行登记。</x:v>
+        <x:v>每轮7个自然日；变更同步两种计划、变更单、版本记录及真实提交证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
@@ -1128,13 +1185,13 @@
         <x:v>计划版本</x:v>
       </x:c>
       <x:c r="B52" s="29" t="str">
-        <x:v>V1.0</x:v>
+        <x:v>V1.1</x:v>
       </x:c>
       <x:c r="C52" s="29" t="str">
-        <x:v>本次编制</x:v>
+        <x:v>CM-R3修订</x:v>
       </x:c>
       <x:c r="D52" s="29" t="str">
-        <x:v>当前计划版本为V1.0，后续调整按版本记录。</x:v>
+        <x:v>CR-003完善估算、储备边界和逐周控制；预算、工时与排期沿用原值。</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
@@ -1148,7 +1205,7 @@
         <x:v>可编辑仿真假设</x:v>
       </x:c>
       <x:c r="D53" s="29" t="str">
-        <x:v>T3开发模块基准人时乘50%；测试/评审/交付不折减。依赖成熟组件与AI辅助。</x:v>
+        <x:v>T3开发模块基准人时乘50%；测试/评审/交付不折减。依赖成熟组件与自动化工具辅助。</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
@@ -1207,7 +1264,7 @@
         <x:v>计算</x:v>
       </x:c>
       <x:c r="D57" s="29" t="str">
-        <x:v>直接人工、非人工及间接费用，不含管理储备</x:v>
+        <x:v>已安排人工、非人工及间接费用；独立应急储备未量化，不含管理储备。</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
@@ -1222,7 +1279,7 @@
         <x:v>输入在成本预算</x:v>
       </x:c>
       <x:c r="D58" s="29" t="str">
-        <x:v>相同储备池覆盖各项风险，避免重复加总</x:v>
+        <x:v>管理储备用于未识别风险；不直接承诺覆盖已识别的RK01–RK05。</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
@@ -1237,7 +1294,7 @@
         <x:v>计算</x:v>
       </x:c>
       <x:c r="D59" s="29" t="str">
-        <x:v>基准的10%，与Project总计划储备一致</x:v>
+        <x:v>保留基准10%的模拟额度；启用或重分类先评估影响并办理变更。</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
@@ -1260,13 +1317,13 @@
         <x:v>效率假设未达到时</x:v>
       </x:c>
       <x:c r="B61" s="29" t="str">
-        <x:v>W2/W4复核调整工期或预算</x:v>
+        <x:v>每周复核效率和剩余工作；影响既定参数时提出CR。</x:v>
       </x:c>
       <x:c r="C61" s="29" t="str">
         <x:v>风险条件</x:v>
       </x:c>
       <x:c r="D61" s="29" t="str">
-        <x:v>不能以取消测试、缩减AC-10B或降低标准抵销偏差</x:v>
+        <x:v>先优化分工、依赖和范围优先级；不取消必要测试或降低验收标准。</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
@@ -1321,7 +1378,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="36" t="str">
-        <x:v>既有SRS与离线原型仅复用需求和交互设计；通用组件及AI辅助，不认定已有正式后端</x:v>
+        <x:v>既有SRS与离线原型仅复用需求和交互设计；通用组件及自动化工具辅助，不认定已有正式后端</x:v>
       </x:c>
       <x:c r="B68" s="36"/>
       <x:c r="C68" s="36"/>
@@ -1345,7 +1402,7 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="36" t="str">
-        <x:v>每次W2/W4/W6/W8复核明确成果与变更；只记录本次计划迭代，不虚构后续实际执行</x:v>
+        <x:v>W1–W8按周复核并保留真实版本记录；W2/W4/W6/W8为阶段重点复核，不预填未来完成结果。</x:v>
       </x:c>
       <x:c r="B71" s="36"/>
       <x:c r="C71" s="36"/>
@@ -1353,7 +1410,7 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="36" t="str">
-        <x:v>直接人工费率不含一般管理分摊，间接人工5%；管理储备10%单列，不计成本控制基准</x:v>
+        <x:v>直接人工费率不含一般管理分摊；管理储备10%单列，已识别风险应急储备未单列、金额待评估。</x:v>
       </x:c>
       <x:c r="B72" s="36"/>
       <x:c r="C72" s="36"/>
@@ -1676,7 +1733,7 @@
         <x:v>独立估算R04人时</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="58" customHeight="1">
+    <x:row r="7" ht="72" customHeight="1">
       <x:c r="A7" s="16" t="str">
         <x:v>T1.1</x:v>
       </x:c>
@@ -1777,7 +1834,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE7" s="29" t="str">
-        <x:v>已有SRS逐条确认43项需求、范围和验收映射，四人并行核对</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。已有SRS逐条确认43项需求、范围和验收映射，四人并行核对</x:v>
       </x:c>
       <x:c r="AF7" s="29" t="str">
         <x:v>是</x:v>
@@ -1817,7 +1874,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="58" customHeight="1">
+    <x:row r="8" ht="72" customHeight="1">
       <x:c r="A8" s="16" t="str">
         <x:v>T1.2</x:v>
       </x:c>
@@ -1920,7 +1977,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE8" s="29" t="str">
-        <x:v>四项计划、WBS与预算编制，项目经理主导，QA复核2小时</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。四项计划、WBS与预算编制，项目经理主导，QA复核2小时</x:v>
       </x:c>
       <x:c r="AF8" s="29" t="str">
         <x:v>是</x:v>
@@ -1960,7 +2017,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="58" customHeight="1">
+    <x:row r="9" ht="72" customHeight="1">
       <x:c r="A9" s="16" t="str">
         <x:v>T1.3</x:v>
       </x:c>
@@ -2063,7 +2120,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE9" s="29" t="str">
-        <x:v>14组验收、边界数据、压力数据方案</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。14组验收、边界数据、压力数据方案</x:v>
       </x:c>
       <x:c r="AF9" s="29" t="str">
         <x:v>否</x:v>
@@ -2103,7 +2160,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="58" customHeight="1">
+    <x:row r="10" ht="72" customHeight="1">
       <x:c r="A10" s="16" t="str">
         <x:v>T2.1</x:v>
       </x:c>
@@ -2206,7 +2263,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE10" s="29" t="str">
-        <x:v>分层架构、权限边界和状态流设计，QA参加2小时可测性评审</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。分层架构、权限边界和状态流设计，QA参加2小时可测性评审</x:v>
       </x:c>
       <x:c r="AF10" s="29" t="str">
         <x:v>否</x:v>
@@ -2246,7 +2303,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="58" customHeight="1">
+    <x:row r="11" ht="72" customHeight="1">
       <x:c r="A11" s="16" t="str">
         <x:v>T2.2</x:v>
       </x:c>
@@ -2349,7 +2406,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE11" s="29" t="str">
-        <x:v>版本、事务、冻结快照和审计模型设计</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。版本、事务、冻结快照和审计模型设计</x:v>
       </x:c>
       <x:c r="AF11" s="29" t="str">
         <x:v>否</x:v>
@@ -2389,7 +2446,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="58" customHeight="1">
+    <x:row r="12" ht="72" customHeight="1">
       <x:c r="A12" s="16" t="str">
         <x:v>T2.3</x:v>
       </x:c>
@@ -2492,7 +2549,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE12" s="29" t="str">
-        <x:v>已有SRS契约细化、错误码及导出接口设计</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。已有SRS契约细化、错误码及导出接口设计</x:v>
       </x:c>
       <x:c r="AF12" s="29" t="str">
         <x:v>否</x:v>
@@ -2532,7 +2589,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="58" customHeight="1">
+    <x:row r="13" ht="72" customHeight="1">
       <x:c r="A13" s="16" t="str">
         <x:v>T2.4</x:v>
       </x:c>
@@ -2635,7 +2692,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE13" s="29" t="str">
-        <x:v>仿真假设W2具备协议、端点、测试凭据和字段映射</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。外部协议和验证条件未确认；不预置未经证实的模型参数。仿真假设W2具备协议、端点、测试凭据和字段映射</x:v>
       </x:c>
       <x:c r="AF13" s="29" t="str">
         <x:v>否</x:v>
@@ -2675,7 +2732,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="58" customHeight="1">
+    <x:row r="14" ht="72" customHeight="1">
       <x:c r="A14" s="16" t="str">
         <x:v>T2.5</x:v>
       </x:c>
@@ -2785,7 +2842,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE14" s="29" t="str">
-        <x:v>D4–D39每日1小时配置、计划、风险和成本跟踪</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。D4–D39每日1小时配置、计划、风险和成本跟踪</x:v>
       </x:c>
       <x:c r="AF14" s="29" t="str">
         <x:v>是</x:v>
@@ -2825,7 +2882,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="58" customHeight="1">
+    <x:row r="15" ht="72" customHeight="1">
       <x:c r="A15" s="16" t="str">
         <x:v>T3.1</x:v>
       </x:c>
@@ -2929,7 +2986,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE15" s="29" t="str">
-        <x:v>复用通用脚手架，配置本地环境与依赖</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。复用通用脚手架，配置本地环境与依赖</x:v>
       </x:c>
       <x:c r="AF15" s="29" t="str">
         <x:v>否</x:v>
@@ -2969,7 +3026,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="58" customHeight="1">
+    <x:row r="16" ht="72" customHeight="1">
       <x:c r="A16" s="16" t="str">
         <x:v>T3.2</x:v>
       </x:c>
@@ -3043,7 +3100,7 @@
         <x:v>AC-05, AC-08, AC-13</x:v>
       </x:c>
       <x:c r="W16" s="9" t="str">
-        <x:v>认证、范围鉴权与TOTP复用成熟库，人工复核；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>认证、范围鉴权与TOTP复用成熟库，人工复核；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X16" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -3072,7 +3129,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE16" s="29" t="str">
-        <x:v>认证、范围鉴权与TOTP复用成熟库，人工复核；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。认证、范围鉴权与TOTP复用成熟库，人工复核；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF16" s="29" t="str">
         <x:v>否</x:v>
@@ -3112,7 +3169,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="58" customHeight="1">
+    <x:row r="17" ht="72" customHeight="1">
       <x:c r="A17" s="16" t="str">
         <x:v>T3.3</x:v>
       </x:c>
@@ -3186,7 +3243,7 @@
         <x:v>AC-01, AC-03</x:v>
       </x:c>
       <x:c r="W17" s="9" t="str">
-        <x:v>字典及地区种子、基准版本维护；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>字典及地区种子、基准版本维护；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X17" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -3215,7 +3272,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE17" s="29" t="str">
-        <x:v>字典及地区种子、基准版本维护；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。字典及地区种子、基准版本维护；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF17" s="29" t="str">
         <x:v>否</x:v>
@@ -3255,7 +3312,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="58" customHeight="1">
+    <x:row r="18" ht="72" customHeight="1">
       <x:c r="A18" s="16" t="str">
         <x:v>T3.4</x:v>
       </x:c>
@@ -3330,7 +3387,7 @@
         <x:v>AC-01, AC-06</x:v>
       </x:c>
       <x:c r="W18" s="9" t="str">
-        <x:v>资料备案状态链、变更版本和审批界面；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>资料备案状态链、变更版本和审批界面；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X18" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -3359,7 +3416,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE18" s="29" t="str">
-        <x:v>资料备案状态链、变更版本和审批界面；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。资料备案状态链、变更版本和审批界面；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF18" s="29" t="str">
         <x:v>否</x:v>
@@ -3399,7 +3456,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="58" customHeight="1">
+    <x:row r="19" ht="72" customHeight="1">
       <x:c r="A19" s="16" t="str">
         <x:v>T3.5</x:v>
       </x:c>
@@ -3473,7 +3530,7 @@
         <x:v>AC-02</x:v>
       </x:c>
       <x:c r="W19" s="9" t="str">
-        <x:v>月报校验、幂等提交、版本与冻结快照；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>月报校验、幂等提交、版本与冻结快照；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="X19" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -3502,7 +3559,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE19" s="29" t="str">
-        <x:v>月报校验、幂等提交、版本与冻结快照；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。月报校验、幂等提交、版本与冻结快照；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF19" s="29" t="str">
         <x:v>否</x:v>
@@ -3542,7 +3599,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="58" customHeight="1">
+    <x:row r="20" ht="72" customHeight="1">
       <x:c r="A20" s="16" t="str">
         <x:v>T3.6</x:v>
       </x:c>
@@ -3616,7 +3673,7 @@
         <x:v>AC-03, AC-05</x:v>
       </x:c>
       <x:c r="W20" s="9" t="str">
-        <x:v>市省审核、退回与补报状态转换；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>市省审核、退回与补报状态转换；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="X20" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -3645,7 +3702,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE20" s="29" t="str">
-        <x:v>市省审核、退回与补报状态转换；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。市省审核、退回与补报状态转换；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF20" s="29" t="str">
         <x:v>否</x:v>
@@ -3685,7 +3742,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="58" customHeight="1">
+    <x:row r="21" ht="72" customHeight="1">
       <x:c r="A21" s="16" t="str">
         <x:v>T3.7</x:v>
       </x:c>
@@ -3760,7 +3817,7 @@
         <x:v>AC-02, AC-03</x:v>
       </x:c>
       <x:c r="W21" s="9" t="str">
-        <x:v>调查期、补报窗口及权限，复用状态基础；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>调查期、补报窗口及权限，复用状态基础；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X21" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -3789,7 +3846,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE21" s="29" t="str">
-        <x:v>调查期、补报窗口及权限，复用状态基础；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。调查期、补报窗口及权限，复用状态基础；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF21" s="29" t="str">
         <x:v>否</x:v>
@@ -3829,7 +3886,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="58" customHeight="1">
+    <x:row r="22" ht="72" customHeight="1">
       <x:c r="A22" s="16" t="str">
         <x:v>T3.8</x:v>
       </x:c>
@@ -3904,7 +3961,7 @@
         <x:v>AC-04, AC-09</x:v>
       </x:c>
       <x:c r="W22" s="9" t="str">
-        <x:v>独立修订、生效与撤销事务、审计一致性；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>独立修订、生效与撤销事务、审计一致性；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="X22" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -3933,7 +3990,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE22" s="29" t="str">
-        <x:v>独立修订、生效与撤销事务、审计一致性；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。独立修订、生效与撤销事务、审计一致性；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF22" s="29" t="str">
         <x:v>否</x:v>
@@ -3973,7 +4030,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="58" customHeight="1">
+    <x:row r="23" ht="72" customHeight="1">
       <x:c r="A23" s="16" t="str">
         <x:v>T3.9</x:v>
       </x:c>
@@ -4048,7 +4105,7 @@
         <x:v>AC-01, AC-05, AC-06</x:v>
       </x:c>
       <x:c r="W23" s="9" t="str">
-        <x:v>历史查询和快照显示复用资料模块；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>历史查询和快照显示复用资料模块；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="X23" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -4077,7 +4134,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE23" s="29" t="str">
-        <x:v>历史查询和快照显示复用资料模块；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。历史查询和快照显示复用资料模块；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF23" s="29" t="str">
         <x:v>否</x:v>
@@ -4117,7 +4174,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="58" customHeight="1">
+    <x:row r="24" ht="72" customHeight="1">
       <x:c r="A24" s="16" t="str">
         <x:v>T3.10</x:v>
       </x:c>
@@ -4191,7 +4248,7 @@
         <x:v>AC-04, AC-07</x:v>
       </x:c>
       <x:c r="W24" s="9" t="str">
-        <x:v>六指标、原始/修订口径及零分母规则；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>六指标、原始/修订口径及零分母规则；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="X24" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -4220,7 +4277,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE24" s="29" t="str">
-        <x:v>六指标、原始/修订口径及零分母规则；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。六指标、原始/修订口径及零分母规则；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF24" s="29" t="str">
         <x:v>否</x:v>
@@ -4260,7 +4317,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="58" customHeight="1">
+    <x:row r="25" ht="87" customHeight="1">
       <x:c r="A25" s="16" t="str">
         <x:v>T3.11</x:v>
       </x:c>
@@ -4334,7 +4391,7 @@
         <x:v>AC-06, AC-09</x:v>
       </x:c>
       <x:c r="W25" s="9" t="str">
-        <x:v>13条件查询、异步导出与安全鉴权；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>13条件查询、异步导出与安全鉴权；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="X25" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -4363,7 +4420,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE25" s="29" t="str">
-        <x:v>13条件查询、异步导出与安全鉴权；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。13条件查询、异步导出与安全鉴权；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF25" s="29" t="str">
         <x:v>否</x:v>
@@ -4403,7 +4460,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="58" customHeight="1">
+    <x:row r="26" ht="72" customHeight="1">
       <x:c r="A26" s="16" t="str">
         <x:v>T3.12</x:v>
       </x:c>
@@ -4477,7 +4534,7 @@
         <x:v>AC-07</x:v>
       </x:c>
       <x:c r="W26" s="9" t="str">
-        <x:v>取样、地区过滤和同源图表复用查询；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>取样、地区过滤和同源图表复用查询；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X26" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -4506,7 +4563,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE26" s="29" t="str">
-        <x:v>取样、地区过滤和同源图表复用查询；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。取样、地区过滤和同源图表复用查询；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF26" s="29" t="str">
         <x:v>否</x:v>
@@ -4546,7 +4603,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="58" customHeight="1">
+    <x:row r="27" ht="87" customHeight="1">
       <x:c r="A27" s="16" t="str">
         <x:v>T3.13</x:v>
       </x:c>
@@ -4620,7 +4677,7 @@
         <x:v>AC-07</x:v>
       </x:c>
       <x:c r="W27" s="9" t="str">
-        <x:v>两期、连续期趋势与缺样本语义；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>两期、连续期趋势与缺样本语义；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="X27" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -4649,7 +4706,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE27" s="29" t="str">
-        <x:v>两期、连续期趋势与缺样本语义；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。两期、连续期趋势与缺样本语义；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF27" s="29" t="str">
         <x:v>否</x:v>
@@ -4689,7 +4746,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="58" customHeight="1">
+    <x:row r="28" ht="72" customHeight="1">
       <x:c r="A28" s="16" t="str">
         <x:v>T3.14</x:v>
       </x:c>
@@ -4763,7 +4820,7 @@
         <x:v>AC-08, AC-05</x:v>
       </x:c>
       <x:c r="W28" s="9" t="str">
-        <x:v>通知和账号管理界面复用权限基础；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>通知和账号管理界面复用权限基础；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X28" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -4792,7 +4849,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE28" s="29" t="str">
-        <x:v>通知和账号管理界面复用权限基础；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。通知和账号管理界面复用权限基础；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF28" s="29" t="str">
         <x:v>否</x:v>
@@ -4832,7 +4889,7 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="58" customHeight="1">
+    <x:row r="29" ht="72" customHeight="1">
       <x:c r="A29" s="16" t="str">
         <x:v>T3.15</x:v>
       </x:c>
@@ -4906,7 +4963,7 @@
         <x:v>AC-09, AC-13</x:v>
       </x:c>
       <x:c r="W29" s="9" t="str">
-        <x:v>删除恢复、清理计时、脱敏与审计链；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>删除恢复、清理计时、脱敏与审计链；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X29" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -4935,7 +4992,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE29" s="29" t="str">
-        <x:v>删除恢复、清理计时、脱敏与审计链；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。删除恢复、清理计时、脱敏与审计链；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF29" s="29" t="str">
         <x:v>否</x:v>
@@ -4975,7 +5032,7 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="58" customHeight="1">
+    <x:row r="30" ht="72" customHeight="1">
       <x:c r="A30" s="16" t="str">
         <x:v>T3.16</x:v>
       </x:c>
@@ -5050,7 +5107,7 @@
         <x:v>AC-14</x:v>
       </x:c>
       <x:c r="W30" s="9" t="str">
-        <x:v>实际宿主采集与失败标识，复用监控库；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>实际宿主采集与失败标识，复用监控库；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X30" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -5079,7 +5136,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE30" s="29" t="str">
-        <x:v>实际宿主采集与失败标识，复用监控库；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。实际宿主采集与失败标识，复用监控库；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF30" s="29" t="str">
         <x:v>否</x:v>
@@ -5119,7 +5176,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="58" customHeight="1">
+    <x:row r="31" ht="87" customHeight="1">
       <x:c r="A31" s="16" t="str">
         <x:v>T3.17</x:v>
       </x:c>
@@ -5194,7 +5251,7 @@
         <x:v>AC-10A</x:v>
       </x:c>
       <x:c r="W31" s="9" t="str">
-        <x:v>批次冻结、黄金摘要、MOCK回执及恢复；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>批次冻结、黄金摘要、MOCK回执及恢复；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="X31" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -5223,7 +5280,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE31" s="29" t="str">
-        <x:v>批次冻结、黄金摘要、MOCK回执及恢复；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。批次冻结、黄金摘要、MOCK回执及恢复；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF31" s="29" t="str">
         <x:v>否</x:v>
@@ -5263,7 +5320,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="58" customHeight="1">
+    <x:row r="32" ht="87" customHeight="1">
       <x:c r="A32" s="16" t="str">
         <x:v>T3.18</x:v>
       </x:c>
@@ -5338,7 +5395,7 @@
         <x:v>AC-10B</x:v>
       </x:c>
       <x:c r="W32" s="9" t="str">
-        <x:v>按假定已具备的真实协议实现认证、映射及传输；复用批次界面，不另行重复前端开发；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>按假定已具备的真实协议实现认证、映射及传输；复用批次界面，不另行重复前端开发；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X32" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -5367,7 +5424,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE32" s="29" t="str">
-        <x:v>按假定已具备的真实协议实现认证、映射及传输；复用批次界面，不另行重复前端开发；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。外部协议和验证条件未确认；不预置未经证实的模型参数。按假定已具备的真实协议实现认证、映射及传输；复用批次界面，不另行重复前端开发；按模块专长重新分工，测试部署成员兼工具及自动化开发；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF32" s="29" t="str">
         <x:v>否</x:v>
@@ -5407,7 +5464,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="58" customHeight="1">
+    <x:row r="33" ht="72" customHeight="1">
       <x:c r="A33" s="16" t="str">
         <x:v>T3.19</x:v>
       </x:c>
@@ -5481,7 +5538,7 @@
         <x:v>AC-12, AC-14</x:v>
       </x:c>
       <x:c r="W33" s="9" t="str">
-        <x:v>部署、配置、备份、迁移和回滚脚本；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>部署、配置、备份、迁移和回滚脚本；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="X33" s="9" t="str">
         <x:v>仿真计划，未执行</x:v>
@@ -5510,7 +5567,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE33" s="29" t="str">
-        <x:v>部署、配置、备份、迁移和回滚脚本；仿真假设成熟组件和AI辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。部署、配置、备份、迁移和回滚脚本；仿真假设成熟组件和自动化工具辅助使开发工作量为独立手写初估的50%，仍保留人工复核，非已完成代码复用</x:v>
       </x:c>
       <x:c r="AF33" s="29" t="str">
         <x:v>否</x:v>
@@ -5550,7 +5607,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="58" customHeight="1">
+    <x:row r="34" ht="72" customHeight="1">
       <x:c r="A34" s="16" t="str">
         <x:v>T4.1</x:v>
       </x:c>
@@ -5653,7 +5710,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE34" s="29" t="str">
-        <x:v>四人阶段评审、检查AC与未解决问题</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。四人阶段评审、检查AC与未解决问题</x:v>
       </x:c>
       <x:c r="AF34" s="29" t="str">
         <x:v>否</x:v>
@@ -5693,7 +5750,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="58" customHeight="1">
+    <x:row r="35" ht="72" customHeight="1">
       <x:c r="A35" s="16" t="str">
         <x:v>T4.2</x:v>
       </x:c>
@@ -5796,7 +5853,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE35" s="29" t="str">
-        <x:v>多模块集成、数据一致性和联调</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。多模块集成、数据一致性和联调</x:v>
       </x:c>
       <x:c r="AF35" s="29" t="str">
         <x:v>否</x:v>
@@ -5836,7 +5893,7 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="58" customHeight="1">
+    <x:row r="36" ht="72" customHeight="1">
       <x:c r="A36" s="16" t="str">
         <x:v>T4.3</x:v>
       </x:c>
@@ -5939,7 +5996,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE36" s="29" t="str">
-        <x:v>QA主导，开发人员并行执行AC-01至09</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。QA主导，开发人员并行执行AC-01至09</x:v>
       </x:c>
       <x:c r="AF36" s="29" t="str">
         <x:v>否</x:v>
@@ -5979,7 +6036,7 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="58" customHeight="1">
+    <x:row r="37" ht="72" customHeight="1">
       <x:c r="A37" s="16" t="str">
         <x:v>T4.4</x:v>
       </x:c>
@@ -6082,7 +6139,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE37" s="29" t="str">
-        <x:v>黄金摘要、回执超时与恢复测试</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。黄金摘要、回执超时与恢复测试</x:v>
       </x:c>
       <x:c r="AF37" s="29" t="str">
         <x:v>否</x:v>
@@ -6122,7 +6179,7 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="58" customHeight="1">
+    <x:row r="38" ht="72" customHeight="1">
       <x:c r="A38" s="16" t="str">
         <x:v>T4.5</x:v>
       </x:c>
@@ -6225,7 +6282,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE38" s="29" t="str">
-        <x:v>计划受控真实交换验证；不填实际通过记录；按模块专长重新分工，测试部署成员兼工具及自动化开发</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。外部协议和验证条件未确认；不预置未经证实的模型参数。计划受控真实交换验证；不填实际通过记录；按模块专长重新分工，测试部署成员兼工具及自动化开发</x:v>
       </x:c>
       <x:c r="AF38" s="29" t="str">
         <x:v>否</x:v>
@@ -6265,7 +6322,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="58" customHeight="1">
+    <x:row r="39" ht="72" customHeight="1">
       <x:c r="A39" s="16" t="str">
         <x:v>T4.6</x:v>
       </x:c>
@@ -6368,7 +6425,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE39" s="29" t="str">
-        <x:v>QA制定用例，PM与后端分担鉴权和并发验证</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。QA制定用例，PM与后端分担鉴权和并发验证</x:v>
       </x:c>
       <x:c r="AF39" s="29" t="str">
         <x:v>否</x:v>
@@ -6408,7 +6465,7 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="58" customHeight="1">
+    <x:row r="40" ht="72" customHeight="1">
       <x:c r="A40" s="16" t="str">
         <x:v>T4.7</x:v>
       </x:c>
@@ -6511,7 +6568,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE40" s="29" t="str">
-        <x:v>独立负载机、合成60万月报与200并发</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。独立负载机、合成60万月报与200并发</x:v>
       </x:c>
       <x:c r="AF40" s="29" t="str">
         <x:v>否</x:v>
@@ -6551,7 +6608,7 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="58" customHeight="1">
+    <x:row r="41" ht="72" customHeight="1">
       <x:c r="A41" s="16" t="str">
         <x:v>T4.8</x:v>
       </x:c>
@@ -6655,7 +6712,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE41" s="29" t="str">
-        <x:v>4工作日覆盖不少于72自然小时，自动监测；人时只计配置、观察和恢复演练</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。4工作日覆盖不少于72自然小时，自动监测；人时只计配置、观察和恢复演练</x:v>
       </x:c>
       <x:c r="AF41" s="29" t="str">
         <x:v>否</x:v>
@@ -6695,7 +6752,7 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="58" customHeight="1">
+    <x:row r="42" ht="72" customHeight="1">
       <x:c r="A42" s="16" t="str">
         <x:v>T4.9</x:v>
       </x:c>
@@ -6798,7 +6855,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE42" s="29" t="str">
-        <x:v>兼容、导出、部署和实际监控证据</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。兼容、导出、部署和实际监控证据</x:v>
       </x:c>
       <x:c r="AF42" s="29" t="str">
         <x:v>否</x:v>
@@ -6838,7 +6895,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="58" customHeight="1">
+    <x:row r="43" ht="72" customHeight="1">
       <x:c r="A43" s="16" t="str">
         <x:v>T4.10</x:v>
       </x:c>
@@ -6942,7 +6999,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE43" s="29" t="str">
-        <x:v>按既有模块预留56人时修复与全量回归</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。按既有模块预留56人时修复与全量回归</x:v>
       </x:c>
       <x:c r="AF43" s="29" t="str">
         <x:v>否</x:v>
@@ -6982,7 +7039,7 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="58" customHeight="1">
+    <x:row r="44" ht="72" customHeight="1">
       <x:c r="A44" s="16" t="str">
         <x:v>T5.1</x:v>
       </x:c>
@@ -7085,7 +7142,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE44" s="29" t="str">
-        <x:v>仿真独立试运行环境与部署窗口；按模块专长重新分工，测试部署成员兼工具及自动化开发；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。仿真独立试运行环境与部署窗口；按模块专长重新分工，测试部署成员兼工具及自动化开发；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF44" s="29" t="str">
         <x:v>否</x:v>
@@ -7125,7 +7182,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="58" customHeight="1">
+    <x:row r="45" ht="72" customHeight="1">
       <x:c r="A45" s="16" t="str">
         <x:v>T5.2</x:v>
       </x:c>
@@ -7228,7 +7285,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE45" s="29" t="str">
-        <x:v>用合成数据模拟业务试运行和反馈</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。用合成数据模拟业务试运行和反馈</x:v>
       </x:c>
       <x:c r="AF45" s="29" t="str">
         <x:v>否</x:v>
@@ -7268,7 +7325,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="58" customHeight="1">
+    <x:row r="46" ht="72" customHeight="1">
       <x:c r="A46" s="16" t="str">
         <x:v>T5.3</x:v>
       </x:c>
@@ -7371,7 +7428,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE46" s="29" t="str">
-        <x:v>四角色操作手册及维护说明</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。四角色操作手册及维护说明</x:v>
       </x:c>
       <x:c r="AF46" s="29" t="str">
         <x:v>否</x:v>
@@ -7411,7 +7468,7 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="58" customHeight="1">
+    <x:row r="47" ht="72" customHeight="1">
       <x:c r="A47" s="16" t="str">
         <x:v>T5.4</x:v>
       </x:c>
@@ -7514,7 +7571,7 @@
         <x:v>低</x:v>
       </x:c>
       <x:c r="AE47" s="29" t="str">
-        <x:v>一次远程培训演示，无实际参加记录</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。一次远程培训演示，无实际参加记录</x:v>
       </x:c>
       <x:c r="AF47" s="29" t="str">
         <x:v>是</x:v>
@@ -7554,7 +7611,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="58" customHeight="1">
+    <x:row r="48" ht="72" customHeight="1">
       <x:c r="A48" s="16" t="str">
         <x:v>T5.5</x:v>
       </x:c>
@@ -7657,7 +7714,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE48" s="29" t="str">
-        <x:v>代码、配置、构建和证据包移交准备</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。代码、配置、构建和证据包移交准备</x:v>
       </x:c>
       <x:c r="AF48" s="29" t="str">
         <x:v>否</x:v>
@@ -7697,7 +7754,7 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="58" customHeight="1">
+    <x:row r="49" ht="72" customHeight="1">
       <x:c r="A49" s="16" t="str">
         <x:v>T5.6</x:v>
       </x:c>
@@ -7800,7 +7857,7 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="AE49" s="29" t="str">
-        <x:v>全范围验收评审，必须含AC-10B计划证据</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。外部协议和验证条件未确认；不预置未经证实的模型参数。全范围验收评审，必须含AC-10B计划证据</x:v>
       </x:c>
       <x:c r="AF49" s="29" t="str">
         <x:v>是</x:v>
@@ -7840,7 +7897,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="58" customHeight="1">
+    <x:row r="50" ht="72" customHeight="1">
       <x:c r="A50" s="16" t="str">
         <x:v>T5.7</x:v>
       </x:c>
@@ -7943,7 +8000,7 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="AE50" s="29" t="str">
-        <x:v>项目经理和QA并行复核最终计划，与仿真验收安排同日定稿；不等待或虚构实际执行结果；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
+        <x:v>自下而上估算：按WBS活动分资源人时×仿真费率汇总；复杂度、复用条件和工作量假设逐轮复核。项目经理和QA并行复核最终计划，与仿真验收安排同日定稿；不等待或虚构实际执行结果；已确认SRS接口后先交付内部接口骨架，模块重叠编码；集成和验收等待全部相关模块完成</x:v>
       </x:c>
       <x:c r="AF50" s="29" t="str">
         <x:v>是</x:v>
@@ -10391,7 +10448,7 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>人工随任务工作量、费率与排期联动；C11为5%一般管理分摊，C14为独立共享储备，避免重复计费。</x:v>
+        <x:v>人工按WBS分资源投入×费率自下而上汇总；C11为5%间接管理分摊；C14为独立管理储备。</x:v>
       </x:c>
       <x:c r="B4" s="4"/>
       <x:c r="C4" s="4"/>
@@ -10513,7 +10570,7 @@
         <x:v>估算依据/待确认事项</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="70" customHeight="1">
+    <x:row r="8" ht="112" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>C01</x:v>
       </x:c>
@@ -10583,10 +10640,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S8" s="9" t="str">
-        <x:v>任务分资源投入×仿真费率；按资源计划逐日/分周投入计，不含一般管理分摊。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="70" customHeight="1">
+        <x:v>自下而上法：任务分资源投入×仿真费率；按资源计划逐日/分周投入计，不含一般管理分摊。 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="112" customHeight="1">
       <x:c r="A9" s="9" t="str">
         <x:v>C02</x:v>
       </x:c>
@@ -10656,10 +10713,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S9" s="9" t="str">
-        <x:v>任务分资源投入×仿真费率；按资源计划逐日/分周投入计，不含一般管理分摊。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="70" customHeight="1">
+        <x:v>自下而上法：任务分资源投入×仿真费率；按资源计划逐日/分周投入计，不含一般管理分摊。 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="112" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>C03</x:v>
       </x:c>
@@ -10729,10 +10786,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S10" s="9" t="str">
-        <x:v>任务分资源投入×仿真费率；按资源计划逐日/分周投入计，不含一般管理分摊。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="70" customHeight="1">
+        <x:v>自下而上法：任务分资源投入×仿真费率；按资源计划逐日/分周投入计，不含一般管理分摊。 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="112" customHeight="1">
       <x:c r="A11" s="9" t="str">
         <x:v>C04</x:v>
       </x:c>
@@ -10802,10 +10859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S11" s="9" t="str">
-        <x:v>任务分资源投入×仿真费率；按资源计划逐日/分周投入计，不含一般管理分摊。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="70" customHeight="1">
+        <x:v>自下而上法：任务分资源投入×仿真费率；按资源计划逐日/分周投入计，不含一般管理分摊。 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="112" customHeight="1">
       <x:c r="A12" s="9" t="str">
         <x:v>C05</x:v>
       </x:c>
@@ -10875,10 +10932,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S12" s="9" t="str">
-        <x:v>R05明确停用，估算与预算为0。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="70" customHeight="1">
+        <x:v>自下而上法：R05明确停用，估算与预算为0。 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="112" customHeight="1">
       <x:c r="A13" s="9" t="str">
         <x:v>C06</x:v>
       </x:c>
@@ -10937,10 +10994,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S13" s="9" t="str">
-        <x:v>仿真周预算：W1–2小型环境；W3–5应用/数据库；W6–7独立压测与恢复资源；W8移交</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="70" customHeight="1">
+        <x:v>资源用量／固定额度法：仿真周预算：W1–2小型环境；W3–5应用/数据库；W6–7独立压测与恢复资源；W8移交 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="112" customHeight="1">
       <x:c r="A14" s="9" t="str">
         <x:v>C07</x:v>
       </x:c>
@@ -10948,7 +11005,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>AI算力与Token</x:v>
+        <x:v>自动化工具与算力额度</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
         <x:v>直接非人力</x:v>
@@ -10999,10 +11056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S14" s="9" t="str">
-        <x:v>仿真额度，按开发密度分周配置，不引用真实套餐价格</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="70" customHeight="1">
+        <x:v>资源用量／固定额度法：仿真额度，按开发密度分周配置，不引用真实套餐价格 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="112" customHeight="1">
       <x:c r="A15" s="9" t="str">
         <x:v>C08</x:v>
       </x:c>
@@ -11061,10 +11118,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S15" s="9" t="str">
-        <x:v>仿真项目许可费用储值1500元；现有Project授权和实际采购情况未确认，不代表产品报价或已采购</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="70" customHeight="1">
+        <x:v>资源用量／固定额度法：仿真项目许可费用储值1500元；现有Project授权和实际采购情况未确认，不代表产品报价或已采购 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="112" customHeight="1">
       <x:c r="A16" s="9" t="str">
         <x:v>C09</x:v>
       </x:c>
@@ -11123,10 +11180,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S16" s="9" t="str">
-        <x:v>仿真复用4台开发机，每台项目期折旧/租用分摊300元；不另行购买</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="70" customHeight="1">
+        <x:v>资源用量／固定额度法：仿真复用4台开发机，每台项目期折旧/租用分摊300元；不另行购买 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="112" customHeight="1">
       <x:c r="A17" s="9" t="str">
         <x:v>C10</x:v>
       </x:c>
@@ -11185,10 +11242,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S17" s="9" t="str">
-        <x:v>一次远程培训材料和会务400元；不安排差旅，授课人工已计任务人时</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="70" customHeight="1">
+        <x:v>资源用量／固定额度法：一次远程培训材料和会务400元；不安排差旅，授课人工已计任务人时 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="112" customHeight="1">
       <x:c r="A18" s="9" t="str">
         <x:v>C11</x:v>
       </x:c>
@@ -11256,10 +11313,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S18" s="9" t="str">
-        <x:v>直接人工的5%作为一般管理支持分摊；R01项目经理本人已计直接人工，不重复计算</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="70" customHeight="1">
+        <x:v>比例分摊法：直接人工的5%作为一般管理支持分摊；R01项目经理本人已计直接人工，不重复计算 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="112" customHeight="1">
       <x:c r="A19" s="9" t="str">
         <x:v>C12</x:v>
       </x:c>
@@ -11318,10 +11375,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S19" s="9" t="str">
-        <x:v>仿真4人共享空间8周，每周分摊300元，覆盖房租、水电及网络</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="70" customHeight="1">
+        <x:v>资源用量／固定额度法：仿真4人共享空间8周，每周分摊300元，覆盖房租、水电及网络 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="112" customHeight="1">
       <x:c r="A20" s="9" t="str">
         <x:v>C13</x:v>
       </x:c>
@@ -11380,10 +11437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S20" s="9" t="str">
-        <x:v>仿真共享打印、办公耗材及设施，每周100元；不含C09设备和C12房租水电</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="70" customHeight="1">
+        <x:v>资源用量／固定额度法：仿真共享打印、办公耗材及设施，每周100元；不含C09设备和C12房租水电 均为模拟参数，逐周检查适用前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="112" customHeight="1">
       <x:c r="A21" s="9" t="str">
         <x:v>C14</x:v>
       </x:c>
@@ -11444,7 +11501,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S21" s="9" t="str">
-        <x:v>仿真成本控制基准的10%；独立管理储备，W8列为额度预留而非已发生支出，不计入成本控制基准</x:v>
+        <x:v>成本基准的10%；仅用于未识别风险，经变更流程决定启用。W8为额度展示而非计划支出；不计入成本基准，不直接分配给RK01–RK05。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
@@ -11679,7 +11736,7 @@
     </x:row>
     <x:row r="29" ht="32" customHeight="1">
       <x:c r="A29" s="23" t="str">
-        <x:v>管理储备为控制基准的10%，单列于C14；成本控制基准不包含管理储备。</x:v>
+        <x:v>C14管理储备为成本基准的10%，用于未识别风险，不计入成本基准。已识别风险的应急储备尚未单列，金额待评估。</x:v>
       </x:c>
       <x:c r="B29" s="23"/>
       <x:c r="C29" s="23"/>
@@ -11725,7 +11782,7 @@
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
       <x:c r="A31" s="23" t="str">
-        <x:v>调整人时、费率和预算后重新复核8周资源可行性，并同步Project的计划版本。</x:v>
+        <x:v>每周复核估算前提、资源负荷及预算偏差；调整工时、费率、排期、预算或储备前办理变更并同步Project。</x:v>
       </x:c>
       <x:c r="B31" s="23"/>
       <x:c r="C31" s="23"/>
@@ -11748,7 +11805,7 @@
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
       <x:c r="A32" s="23" t="str">
-        <x:v>重复计算：分别界定成员直接工时、一般管理分摊和共享费用，避免同一费用计入两次。</x:v>
+        <x:v>管理、评审和测试人时已在活动中计入；不得再以比例重复计入质量人工。C11仅为一般管理支持分摊。</x:v>
       </x:c>
       <x:c r="B32" s="23"/>
       <x:c r="C32" s="23"/>
@@ -11811,49 +11868,1362 @@
       <x:c r="R34" s="4"/>
       <x:c r="S34" s="4"/>
     </x:row>
-    <x:row r="35" ht="30" customHeight="1">
-      <x:c r="A35" s="4"/>
-      <x:c r="B35" s="4"/>
-      <x:c r="C35" s="4"/>
-      <x:c r="D35" s="4"/>
-      <x:c r="E35" s="4"/>
-      <x:c r="F35" s="4"/>
-      <x:c r="G35" s="4"/>
-      <x:c r="H35" s="4"/>
-      <x:c r="I35" s="4"/>
-      <x:c r="J35" s="4"/>
-      <x:c r="K35" s="4"/>
-      <x:c r="L35" s="4"/>
-      <x:c r="M35" s="4"/>
-      <x:c r="N35" s="4"/>
-      <x:c r="O35" s="4"/>
-      <x:c r="P35" s="4"/>
-      <x:c r="Q35" s="4"/>
-      <x:c r="R35" s="4"/>
-      <x:c r="S35" s="4"/>
-    </x:row>
-    <x:row r="36" ht="30" customHeight="1">
-      <x:c r="A36" s="4"/>
-      <x:c r="B36" s="4"/>
-      <x:c r="C36" s="4"/>
-      <x:c r="D36" s="4"/>
-      <x:c r="E36" s="4"/>
-      <x:c r="F36" s="4"/>
-      <x:c r="G36" s="4"/>
-      <x:c r="H36" s="4"/>
-      <x:c r="I36" s="4"/>
-      <x:c r="J36" s="4"/>
-      <x:c r="K36" s="4"/>
-      <x:c r="L36" s="4"/>
-      <x:c r="M36" s="4"/>
-      <x:c r="N36" s="4"/>
-      <x:c r="O36" s="4"/>
-      <x:c r="P36" s="4"/>
-      <x:c r="Q36" s="4"/>
-      <x:c r="R36" s="4"/>
-      <x:c r="S36" s="4"/>
+    <x:row r="35" ht="28" customHeight="1">
+      <x:c r="A35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="B35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="C35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="D35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="E35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="F35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="G35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="H35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="I35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="J35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="K35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="L35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="M35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="N35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="O35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="P35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="Q35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="R35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+      <x:c r="S35" s="60" t="str">
+        <x:v>逐周成本控制（累计口径，人民币元）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="36" customHeight="1">
+      <x:c r="A36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="B36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="C36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="D36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="E36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="F36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="G36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="H36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="I36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="J36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="K36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="L36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="M36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="N36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="O36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="P36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="Q36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="R36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+      <x:c r="S36" s="63" t="str">
+        <x:v>PV取成本控制基准，不含C14。AC、EV及实际处理记录在真实执行后填写；未发生时留空。每周复核不另增加既有活动工时。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="48" customHeight="1">
+      <x:c r="A38" s="60" t="str">
+        <x:v>周次</x:v>
+      </x:c>
+      <x:c r="B38" s="60" t="str">
+        <x:v>开始日期</x:v>
+      </x:c>
+      <x:c r="C38" s="60" t="str">
+        <x:v>截止日期</x:v>
+      </x:c>
+      <x:c r="D38" s="60" t="str">
+        <x:v>当周PV</x:v>
+      </x:c>
+      <x:c r="E38" s="60" t="str">
+        <x:v>当周PV</x:v>
+      </x:c>
+      <x:c r="F38" s="60" t="str">
+        <x:v>累计PV</x:v>
+      </x:c>
+      <x:c r="G38" s="60" t="str">
+        <x:v>累计PV</x:v>
+      </x:c>
+      <x:c r="H38" s="60" t="str">
+        <x:v>累计实际成本AC</x:v>
+      </x:c>
+      <x:c r="I38" s="60" t="str">
+        <x:v>累计实际成本AC</x:v>
+      </x:c>
+      <x:c r="J38" s="60" t="str">
+        <x:v>完成工作预算EV</x:v>
+      </x:c>
+      <x:c r="K38" s="60" t="str">
+        <x:v>完成工作预算EV</x:v>
+      </x:c>
+      <x:c r="L38" s="60" t="str">
+        <x:v>进度偏差SV</x:v>
+      </x:c>
+      <x:c r="M38" s="60" t="str">
+        <x:v>进度偏差SV</x:v>
+      </x:c>
+      <x:c r="N38" s="60" t="str">
+        <x:v>成本偏差CV</x:v>
+      </x:c>
+      <x:c r="O38" s="60" t="str">
+        <x:v>成本偏差CV</x:v>
+      </x:c>
+      <x:c r="P38" s="60" t="str">
+        <x:v>成本绩效CPI</x:v>
+      </x:c>
+      <x:c r="Q38" s="60" t="str">
+        <x:v>成本绩效CPI</x:v>
+      </x:c>
+      <x:c r="R38" s="60" t="str">
+        <x:v>原因／措施／关联CR</x:v>
+      </x:c>
+      <x:c r="S38" s="60" t="str">
+        <x:v>原因／措施／关联CR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="44" customHeight="1">
+      <x:c r="A39" s="63" t="str">
+        <x:v>W1</x:v>
+      </x:c>
+      <x:c r="B39" s="69" t="d">
+        <x:v>2026-10-19T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C39" s="69" t="d">
+        <x:v>2026-10-25T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D39" s="70" t="n">
+        <x:f>I24</x:f>
+        <x:v>14903</x:v>
+      </x:c>
+      <x:c r="E39" s="70"/>
+      <x:c r="F39" s="70" t="n">
+        <x:f>SUM($D$39:D39)</x:f>
+        <x:v>14903</x:v>
+      </x:c>
+      <x:c r="G39" s="70"/>
+      <x:c r="H39" s="70"/>
+      <x:c r="I39" s="70"/>
+      <x:c r="J39" s="70"/>
+      <x:c r="K39" s="70"/>
+      <x:c r="L39" s="70" t="str">
+        <x:f>IF(COUNT(J39,F39)=2,J39-F39,"")</x:f>
+      </x:c>
+      <x:c r="M39" s="70"/>
+      <x:c r="N39" s="70" t="str">
+        <x:f>IF(COUNT(J39,H39)=2,J39-H39,"")</x:f>
+      </x:c>
+      <x:c r="O39" s="70"/>
+      <x:c r="P39" s="71" t="str">
+        <x:f>IF(COUNT(J39,H39)&lt;2,"",IF(H39=0,"",J39/H39))</x:f>
+      </x:c>
+      <x:c r="Q39" s="71"/>
+      <x:c r="R39" s="63"/>
+      <x:c r="S39" s="63"/>
+    </x:row>
+    <x:row r="40" ht="44" customHeight="1">
+      <x:c r="A40" s="63" t="str">
+        <x:v>W2</x:v>
+      </x:c>
+      <x:c r="B40" s="69" t="d">
+        <x:v>2026-10-26T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C40" s="69" t="d">
+        <x:v>2026-11-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D40" s="70" t="n">
+        <x:f>J24</x:f>
+        <x:v>10830.75</x:v>
+      </x:c>
+      <x:c r="E40" s="70"/>
+      <x:c r="F40" s="70" t="n">
+        <x:f>SUM($D$39:D40)</x:f>
+        <x:v>25733.75</x:v>
+      </x:c>
+      <x:c r="G40" s="70"/>
+      <x:c r="H40" s="70"/>
+      <x:c r="I40" s="70"/>
+      <x:c r="J40" s="70"/>
+      <x:c r="K40" s="70"/>
+      <x:c r="L40" s="70" t="str">
+        <x:f>IF(COUNT(J40,F40)=2,J40-F40,"")</x:f>
+      </x:c>
+      <x:c r="M40" s="70"/>
+      <x:c r="N40" s="70" t="str">
+        <x:f>IF(COUNT(J40,H40)=2,J40-H40,"")</x:f>
+      </x:c>
+      <x:c r="O40" s="70"/>
+      <x:c r="P40" s="71" t="str">
+        <x:f>IF(COUNT(J40,H40)&lt;2,"",IF(H40=0,"",J40/H40))</x:f>
+      </x:c>
+      <x:c r="Q40" s="71"/>
+      <x:c r="R40" s="63"/>
+      <x:c r="S40" s="63"/>
+    </x:row>
+    <x:row r="41" ht="44" customHeight="1">
+      <x:c r="A41" s="63" t="str">
+        <x:v>W3</x:v>
+      </x:c>
+      <x:c r="B41" s="69" t="d">
+        <x:v>2026-11-02T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C41" s="69" t="d">
+        <x:v>2026-11-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D41" s="70" t="n">
+        <x:f>K24</x:f>
+        <x:v>12440.75</x:v>
+      </x:c>
+      <x:c r="E41" s="70"/>
+      <x:c r="F41" s="70" t="n">
+        <x:f>SUM($D$39:D41)</x:f>
+        <x:v>38174.5</x:v>
+      </x:c>
+      <x:c r="G41" s="70"/>
+      <x:c r="H41" s="70"/>
+      <x:c r="I41" s="70"/>
+      <x:c r="J41" s="70"/>
+      <x:c r="K41" s="70"/>
+      <x:c r="L41" s="70" t="str">
+        <x:f>IF(COUNT(J41,F41)=2,J41-F41,"")</x:f>
+      </x:c>
+      <x:c r="M41" s="70"/>
+      <x:c r="N41" s="70" t="str">
+        <x:f>IF(COUNT(J41,H41)=2,J41-H41,"")</x:f>
+      </x:c>
+      <x:c r="O41" s="70"/>
+      <x:c r="P41" s="71" t="str">
+        <x:f>IF(COUNT(J41,H41)&lt;2,"",IF(H41=0,"",J41/H41))</x:f>
+      </x:c>
+      <x:c r="Q41" s="71"/>
+      <x:c r="R41" s="63"/>
+      <x:c r="S41" s="63"/>
+    </x:row>
+    <x:row r="42" ht="44" customHeight="1">
+      <x:c r="A42" s="63" t="str">
+        <x:v>W4</x:v>
+      </x:c>
+      <x:c r="B42" s="69" t="d">
+        <x:v>2026-11-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C42" s="69" t="d">
+        <x:v>2026-11-15T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D42" s="70" t="n">
+        <x:f>L24</x:f>
+        <x:v>14153.996666666666</x:v>
+      </x:c>
+      <x:c r="E42" s="70"/>
+      <x:c r="F42" s="70" t="n">
+        <x:f>SUM($D$39:D42)</x:f>
+        <x:v>52328.496666666666</x:v>
+      </x:c>
+      <x:c r="G42" s="70"/>
+      <x:c r="H42" s="70"/>
+      <x:c r="I42" s="70"/>
+      <x:c r="J42" s="70"/>
+      <x:c r="K42" s="70"/>
+      <x:c r="L42" s="70" t="str">
+        <x:f>IF(COUNT(J42,F42)=2,J42-F42,"")</x:f>
+      </x:c>
+      <x:c r="M42" s="70"/>
+      <x:c r="N42" s="70" t="str">
+        <x:f>IF(COUNT(J42,H42)=2,J42-H42,"")</x:f>
+      </x:c>
+      <x:c r="O42" s="70"/>
+      <x:c r="P42" s="71" t="str">
+        <x:f>IF(COUNT(J42,H42)&lt;2,"",IF(H42=0,"",J42/H42))</x:f>
+      </x:c>
+      <x:c r="Q42" s="71"/>
+      <x:c r="R42" s="63"/>
+      <x:c r="S42" s="63"/>
+    </x:row>
+    <x:row r="43" ht="44" customHeight="1">
+      <x:c r="A43" s="63" t="str">
+        <x:v>W5</x:v>
+      </x:c>
+      <x:c r="B43" s="69" t="d">
+        <x:v>2026-11-16T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C43" s="69" t="d">
+        <x:v>2026-11-22T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D43" s="70" t="n">
+        <x:f>M24</x:f>
+        <x:v>14098.003333333332</x:v>
+      </x:c>
+      <x:c r="E43" s="70"/>
+      <x:c r="F43" s="70" t="n">
+        <x:f>SUM($D$39:D43)</x:f>
+        <x:v>66426.5</x:v>
+      </x:c>
+      <x:c r="G43" s="70"/>
+      <x:c r="H43" s="70"/>
+      <x:c r="I43" s="70"/>
+      <x:c r="J43" s="70"/>
+      <x:c r="K43" s="70"/>
+      <x:c r="L43" s="70" t="str">
+        <x:f>IF(COUNT(J43,F43)=2,J43-F43,"")</x:f>
+      </x:c>
+      <x:c r="M43" s="70"/>
+      <x:c r="N43" s="70" t="str">
+        <x:f>IF(COUNT(J43,H43)=2,J43-H43,"")</x:f>
+      </x:c>
+      <x:c r="O43" s="70"/>
+      <x:c r="P43" s="71" t="str">
+        <x:f>IF(COUNT(J43,H43)&lt;2,"",IF(H43=0,"",J43/H43))</x:f>
+      </x:c>
+      <x:c r="Q43" s="71"/>
+      <x:c r="R43" s="63"/>
+      <x:c r="S43" s="63"/>
+    </x:row>
+    <x:row r="44" ht="44" customHeight="1">
+      <x:c r="A44" s="63" t="str">
+        <x:v>W6</x:v>
+      </x:c>
+      <x:c r="B44" s="69" t="d">
+        <x:v>2026-11-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C44" s="69" t="d">
+        <x:v>2026-11-29T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D44" s="70" t="n">
+        <x:f>N24</x:f>
+        <x:v>15284</x:v>
+      </x:c>
+      <x:c r="E44" s="70"/>
+      <x:c r="F44" s="70" t="n">
+        <x:f>SUM($D$39:D44)</x:f>
+        <x:v>81710.5</x:v>
+      </x:c>
+      <x:c r="G44" s="70"/>
+      <x:c r="H44" s="70"/>
+      <x:c r="I44" s="70"/>
+      <x:c r="J44" s="70"/>
+      <x:c r="K44" s="70"/>
+      <x:c r="L44" s="70" t="str">
+        <x:f>IF(COUNT(J44,F44)=2,J44-F44,"")</x:f>
+      </x:c>
+      <x:c r="M44" s="70"/>
+      <x:c r="N44" s="70" t="str">
+        <x:f>IF(COUNT(J44,H44)=2,J44-H44,"")</x:f>
+      </x:c>
+      <x:c r="O44" s="70"/>
+      <x:c r="P44" s="71" t="str">
+        <x:f>IF(COUNT(J44,H44)&lt;2,"",IF(H44=0,"",J44/H44))</x:f>
+      </x:c>
+      <x:c r="Q44" s="71"/>
+      <x:c r="R44" s="63"/>
+      <x:c r="S44" s="63"/>
+    </x:row>
+    <x:row r="45" ht="44" customHeight="1">
+      <x:c r="A45" s="63" t="str">
+        <x:v>W7</x:v>
+      </x:c>
+      <x:c r="B45" s="69" t="d">
+        <x:v>2026-11-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C45" s="69" t="d">
+        <x:v>2026-12-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D45" s="70" t="n">
+        <x:f>O24</x:f>
+        <x:v>14513.003333333332</x:v>
+      </x:c>
+      <x:c r="E45" s="70"/>
+      <x:c r="F45" s="70" t="n">
+        <x:f>SUM($D$39:D45)</x:f>
+        <x:v>96223.50333333333</x:v>
+      </x:c>
+      <x:c r="G45" s="70"/>
+      <x:c r="H45" s="70"/>
+      <x:c r="I45" s="70"/>
+      <x:c r="J45" s="70"/>
+      <x:c r="K45" s="70"/>
+      <x:c r="L45" s="70" t="str">
+        <x:f>IF(COUNT(J45,F45)=2,J45-F45,"")</x:f>
+      </x:c>
+      <x:c r="M45" s="70"/>
+      <x:c r="N45" s="70" t="str">
+        <x:f>IF(COUNT(J45,H45)=2,J45-H45,"")</x:f>
+      </x:c>
+      <x:c r="O45" s="70"/>
+      <x:c r="P45" s="71" t="str">
+        <x:f>IF(COUNT(J45,H45)&lt;2,"",IF(H45=0,"",J45/H45))</x:f>
+      </x:c>
+      <x:c r="Q45" s="71"/>
+      <x:c r="R45" s="63"/>
+      <x:c r="S45" s="63"/>
+    </x:row>
+    <x:row r="46" ht="44" customHeight="1">
+      <x:c r="A46" s="63" t="str">
+        <x:v>W8</x:v>
+      </x:c>
+      <x:c r="B46" s="69" t="d">
+        <x:v>2026-12-07T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C46" s="69" t="d">
+        <x:v>2026-12-13T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D46" s="70" t="n">
+        <x:f>P24</x:f>
+        <x:v>10628.996666666666</x:v>
+      </x:c>
+      <x:c r="E46" s="70"/>
+      <x:c r="F46" s="70" t="n">
+        <x:f>SUM($D$39:D46)</x:f>
+        <x:v>106852.5</x:v>
+      </x:c>
+      <x:c r="G46" s="70"/>
+      <x:c r="H46" s="70"/>
+      <x:c r="I46" s="70"/>
+      <x:c r="J46" s="70"/>
+      <x:c r="K46" s="70"/>
+      <x:c r="L46" s="70" t="str">
+        <x:f>IF(COUNT(J46,F46)=2,J46-F46,"")</x:f>
+      </x:c>
+      <x:c r="M46" s="70"/>
+      <x:c r="N46" s="70" t="str">
+        <x:f>IF(COUNT(J46,H46)=2,J46-H46,"")</x:f>
+      </x:c>
+      <x:c r="O46" s="70"/>
+      <x:c r="P46" s="71" t="str">
+        <x:f>IF(COUNT(J46,H46)&lt;2,"",IF(H46=0,"",J46/H46))</x:f>
+      </x:c>
+      <x:c r="Q46" s="71"/>
+      <x:c r="R46" s="63"/>
+      <x:c r="S46" s="63"/>
+    </x:row>
+    <x:row r="48" ht="44" customHeight="1">
+      <x:c r="A48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="B48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="C48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="D48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="E48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="F48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="G48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="H48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="I48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="J48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="K48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="L48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="M48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="N48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="O48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="P48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="Q48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="R48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+      <x:c r="S48" s="63" t="str">
+        <x:v>PV为计划完成工作预算；EV按已完成并可核验工作折算预算；AC为同一截止点累计实际成本。SV=EV−PV，CV=EV−AC，负值分别表示进度落后或相对已完成工作超支。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="40" customHeight="1">
+      <x:c r="A49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="B49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="C49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="D49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="E49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="F49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="G49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="H49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="I49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="J49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="K49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="L49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="M49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="N49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="O49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="P49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="Q49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="R49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+      <x:c r="S49" s="63" t="str">
+        <x:v>CPI=EV÷AC；AC为0时CPI留空，不以0代替无法计算。AC与PV的资金支出差异不得单独当作成本绩效。实际金额、完成程度和凭证未知时保持空白。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="44" customHeight="1">
+      <x:c r="A50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="B50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="C50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="D50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="E50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="F50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="G50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="H50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="I50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="J50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="K50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="L50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="M50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="N50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="O50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="P50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="Q50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="R50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+      <x:c r="S50" s="63" t="str">
+        <x:v>每周调查偏差原因，复核剩余工作和风险；先优化分工及依赖，必要时协商交付优先级。变更范围、日期、工时、费率、预算、储备或验收标准前办理CR并同步基线；不得通过取消必要测试抵销偏差。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="28" customHeight="1">
+      <x:c r="A53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="B53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="C53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="D53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="E53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="F53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="G53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="H53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="I53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="J53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="K53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="L53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="M53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="N53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="O53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="P53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="Q53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="R53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+      <x:c r="S53" s="60" t="str">
+        <x:v>储备分类与待评估额度（不计入本版已确定预算）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="40" customHeight="1">
+      <x:c r="A54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="B54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="C54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="D54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="E54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="F54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="G54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="H54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="I54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="J54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="K54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="L54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="M54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="N54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="O54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="P54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="Q54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="R54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+      <x:c r="S54" s="63" t="str">
+        <x:v>C14管理储备保持10,685.25元，仅用于未识别风险。已识别风险的常规防范工作已安排在基准任务／费用中；独立应急储备尚未量化，不能视为0或已落实。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="48" customHeight="1">
+      <x:c r="A56" s="60" t="str">
+        <x:v>风险ID</x:v>
+      </x:c>
+      <x:c r="B56" s="60" t="str">
+        <x:v>已识别风险</x:v>
+      </x:c>
+      <x:c r="C56" s="60" t="str">
+        <x:v>已识别风险</x:v>
+      </x:c>
+      <x:c r="D56" s="60" t="str">
+        <x:v>基准内已安排的响应工作</x:v>
+      </x:c>
+      <x:c r="E56" s="60" t="str">
+        <x:v>基准内已安排的响应工作</x:v>
+      </x:c>
+      <x:c r="F56" s="60" t="str">
+        <x:v>基准内已安排的响应工作</x:v>
+      </x:c>
+      <x:c r="G56" s="60" t="str">
+        <x:v>基准内已安排的响应工作</x:v>
+      </x:c>
+      <x:c r="H56" s="60" t="str">
+        <x:v>独立应急储备（元）</x:v>
+      </x:c>
+      <x:c r="I56" s="60" t="str">
+        <x:v>独立应急储备（元）</x:v>
+      </x:c>
+      <x:c r="J56" s="60" t="str">
+        <x:v>费用来源</x:v>
+      </x:c>
+      <x:c r="K56" s="60" t="str">
+        <x:v>费用来源</x:v>
+      </x:c>
+      <x:c r="L56" s="60" t="str">
+        <x:v>分配及变更规则</x:v>
+      </x:c>
+      <x:c r="M56" s="60" t="str">
+        <x:v>分配及变更规则</x:v>
+      </x:c>
+      <x:c r="N56" s="60" t="str">
+        <x:v>分配及变更规则</x:v>
+      </x:c>
+      <x:c r="O56" s="60" t="str">
+        <x:v>分配及变更规则</x:v>
+      </x:c>
+      <x:c r="P56" s="60" t="str">
+        <x:v>分配及变更规则</x:v>
+      </x:c>
+      <x:c r="Q56" s="60" t="str">
+        <x:v>额度状态</x:v>
+      </x:c>
+      <x:c r="R56" s="60" t="str">
+        <x:v>额度状态</x:v>
+      </x:c>
+      <x:c r="S56" s="60" t="str">
+        <x:v>额度状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="50" customHeight="1">
+      <x:c r="A57" s="63" t="str">
+        <x:v>RK01</x:v>
+      </x:c>
+      <x:c r="B57" s="63" t="str">
+        <x:v>效率假设未达到</x:v>
+      </x:c>
+      <x:c r="C57" s="63" t="str">
+        <x:v>效率假设未达到</x:v>
+      </x:c>
+      <x:c r="D57" s="63" t="str">
+        <x:v>复核分工及既有可用容量</x:v>
+      </x:c>
+      <x:c r="E57" s="63" t="str">
+        <x:v>复核分工及既有可用容量</x:v>
+      </x:c>
+      <x:c r="F57" s="63" t="str">
+        <x:v>复核分工及既有可用容量</x:v>
+      </x:c>
+      <x:c r="G57" s="63" t="str">
+        <x:v>复核分工及既有可用容量</x:v>
+      </x:c>
+      <x:c r="H57" s="70"/>
+      <x:c r="I57" s="70"/>
+      <x:c r="J57" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="K57" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="L57" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="M57" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="N57" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="O57" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="P57" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="Q57" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="R57" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="S57" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="50" customHeight="1">
+      <x:c r="A58" s="63" t="str">
+        <x:v>RK02</x:v>
+      </x:c>
+      <x:c r="B58" s="63" t="str">
+        <x:v>真实交换输入未具备</x:v>
+      </x:c>
+      <x:c r="C58" s="63" t="str">
+        <x:v>真实交换输入未具备</x:v>
+      </x:c>
+      <x:c r="D58" s="63" t="str">
+        <x:v>T2.4输入核对及交换适配／验证</x:v>
+      </x:c>
+      <x:c r="E58" s="63" t="str">
+        <x:v>T2.4输入核对及交换适配／验证</x:v>
+      </x:c>
+      <x:c r="F58" s="63" t="str">
+        <x:v>T2.4输入核对及交换适配／验证</x:v>
+      </x:c>
+      <x:c r="G58" s="63" t="str">
+        <x:v>T2.4输入核对及交换适配／验证</x:v>
+      </x:c>
+      <x:c r="H58" s="70"/>
+      <x:c r="I58" s="70"/>
+      <x:c r="J58" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="K58" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="L58" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="M58" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="N58" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="O58" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="P58" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="Q58" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="R58" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="S58" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="50" customHeight="1">
+      <x:c r="A59" s="63" t="str">
+        <x:v>RK03</x:v>
+      </x:c>
+      <x:c r="B59" s="63" t="str">
+        <x:v>负载与部署资源不足</x:v>
+      </x:c>
+      <x:c r="C59" s="63" t="str">
+        <x:v>负载与部署资源不足</x:v>
+      </x:c>
+      <x:c r="D59" s="63" t="str">
+        <x:v>C06及既有性能、恢复验证工作</x:v>
+      </x:c>
+      <x:c r="E59" s="63" t="str">
+        <x:v>C06及既有性能、恢复验证工作</x:v>
+      </x:c>
+      <x:c r="F59" s="63" t="str">
+        <x:v>C06及既有性能、恢复验证工作</x:v>
+      </x:c>
+      <x:c r="G59" s="63" t="str">
+        <x:v>C06及既有性能、恢复验证工作</x:v>
+      </x:c>
+      <x:c r="H59" s="70"/>
+      <x:c r="I59" s="70"/>
+      <x:c r="J59" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="K59" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="L59" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="M59" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="N59" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="O59" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="P59" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="Q59" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="R59" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="S59" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="50" customHeight="1">
+      <x:c r="A60" s="63" t="str">
+        <x:v>RK04</x:v>
+      </x:c>
+      <x:c r="B60" s="63" t="str">
+        <x:v>投入、费率或分摊变化</x:v>
+      </x:c>
+      <x:c r="C60" s="63" t="str">
+        <x:v>投入、费率或分摊变化</x:v>
+      </x:c>
+      <x:c r="D60" s="63" t="str">
+        <x:v>T2.5成本跟踪及逐周预算复核</x:v>
+      </x:c>
+      <x:c r="E60" s="63" t="str">
+        <x:v>T2.5成本跟踪及逐周预算复核</x:v>
+      </x:c>
+      <x:c r="F60" s="63" t="str">
+        <x:v>T2.5成本跟踪及逐周预算复核</x:v>
+      </x:c>
+      <x:c r="G60" s="63" t="str">
+        <x:v>T2.5成本跟踪及逐周预算复核</x:v>
+      </x:c>
+      <x:c r="H60" s="70"/>
+      <x:c r="I60" s="70"/>
+      <x:c r="J60" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="K60" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="L60" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="M60" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="N60" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="O60" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="P60" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="Q60" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="R60" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="S60" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="50" customHeight="1">
+      <x:c r="A61" s="63" t="str">
+        <x:v>RK05</x:v>
+      </x:c>
+      <x:c r="B61" s="63" t="str">
+        <x:v>复用条件未达预期</x:v>
+      </x:c>
+      <x:c r="C61" s="63" t="str">
+        <x:v>复用条件未达预期</x:v>
+      </x:c>
+      <x:c r="D61" s="63" t="str">
+        <x:v>现有需求设计复核及组件核验</x:v>
+      </x:c>
+      <x:c r="E61" s="63" t="str">
+        <x:v>现有需求设计复核及组件核验</x:v>
+      </x:c>
+      <x:c r="F61" s="63" t="str">
+        <x:v>现有需求设计复核及组件核验</x:v>
+      </x:c>
+      <x:c r="G61" s="63" t="str">
+        <x:v>现有需求设计复核及组件核验</x:v>
+      </x:c>
+      <x:c r="H61" s="70"/>
+      <x:c r="I61" s="70"/>
+      <x:c r="J61" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="K61" s="63" t="str">
+        <x:v>待评估</x:v>
+      </x:c>
+      <x:c r="L61" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="M61" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="N61" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="O61" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="P61" s="63" t="str">
+        <x:v>先量化风险响应费用；新增或重分类储备须办理CR。</x:v>
+      </x:c>
+      <x:c r="Q61" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="R61" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+      <x:c r="S61" s="63" t="str">
+        <x:v>未单列、金额待评估</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="44" customHeight="1">
+      <x:c r="A63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="B63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="C63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="D63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="E63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="F63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="G63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="H63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="I63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="J63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="K63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="L63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="M63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="N63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="O63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="P63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="Q63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="R63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+      <x:c r="S63" s="63" t="str">
+        <x:v>应急储备针对已识别风险，正式量化及批准后计入成本基准；管理储备位于基准之外。若从现有总预算内部重分类，须重新核算两类储备和成本基准并登记CR；本版不预置分配比例。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="40" customHeight="1">
+      <x:c r="A64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="B64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="C64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="D64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="E64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="F64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="G64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="H64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="I64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="J64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="K64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="L64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="M64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="N64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="O64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="P64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="Q64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="R64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+      <x:c r="S64" s="63" t="str">
+        <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A35:S35"/>
+    <x:mergeCell ref="A36:S36"/>
+    <x:mergeCell ref="D38:E38"/>
+    <x:mergeCell ref="F38:G38"/>
+    <x:mergeCell ref="H38:I38"/>
+    <x:mergeCell ref="J38:K38"/>
+    <x:mergeCell ref="L38:M38"/>
+    <x:mergeCell ref="N38:O38"/>
+    <x:mergeCell ref="P38:Q38"/>
+    <x:mergeCell ref="R38:S38"/>
+    <x:mergeCell ref="D39:E39"/>
+    <x:mergeCell ref="F39:G39"/>
+    <x:mergeCell ref="H39:I39"/>
+    <x:mergeCell ref="J39:K39"/>
+    <x:mergeCell ref="L39:M39"/>
+    <x:mergeCell ref="N39:O39"/>
+    <x:mergeCell ref="P39:Q39"/>
+    <x:mergeCell ref="R39:S39"/>
+    <x:mergeCell ref="D40:E40"/>
+    <x:mergeCell ref="F40:G40"/>
+    <x:mergeCell ref="H40:I40"/>
+    <x:mergeCell ref="J40:K40"/>
+    <x:mergeCell ref="L40:M40"/>
+    <x:mergeCell ref="N40:O40"/>
+    <x:mergeCell ref="P40:Q40"/>
+    <x:mergeCell ref="R40:S40"/>
+    <x:mergeCell ref="D41:E41"/>
+    <x:mergeCell ref="F41:G41"/>
+    <x:mergeCell ref="H41:I41"/>
+    <x:mergeCell ref="J41:K41"/>
+    <x:mergeCell ref="L41:M41"/>
+    <x:mergeCell ref="N41:O41"/>
+    <x:mergeCell ref="P41:Q41"/>
+    <x:mergeCell ref="R41:S41"/>
+    <x:mergeCell ref="D42:E42"/>
+    <x:mergeCell ref="F42:G42"/>
+    <x:mergeCell ref="H42:I42"/>
+    <x:mergeCell ref="J42:K42"/>
+    <x:mergeCell ref="L42:M42"/>
+    <x:mergeCell ref="N42:O42"/>
+    <x:mergeCell ref="P42:Q42"/>
+    <x:mergeCell ref="R42:S42"/>
+    <x:mergeCell ref="D43:E43"/>
+    <x:mergeCell ref="F43:G43"/>
+    <x:mergeCell ref="H43:I43"/>
+    <x:mergeCell ref="J43:K43"/>
+    <x:mergeCell ref="L43:M43"/>
+    <x:mergeCell ref="N43:O43"/>
+    <x:mergeCell ref="P43:Q43"/>
+    <x:mergeCell ref="R43:S43"/>
+    <x:mergeCell ref="D44:E44"/>
+    <x:mergeCell ref="F44:G44"/>
+    <x:mergeCell ref="H44:I44"/>
+    <x:mergeCell ref="J44:K44"/>
+    <x:mergeCell ref="L44:M44"/>
+    <x:mergeCell ref="N44:O44"/>
+    <x:mergeCell ref="P44:Q44"/>
+    <x:mergeCell ref="R44:S44"/>
+    <x:mergeCell ref="D45:E45"/>
+    <x:mergeCell ref="F45:G45"/>
+    <x:mergeCell ref="H45:I45"/>
+    <x:mergeCell ref="J45:K45"/>
+    <x:mergeCell ref="L45:M45"/>
+    <x:mergeCell ref="N45:O45"/>
+    <x:mergeCell ref="P45:Q45"/>
+    <x:mergeCell ref="R45:S45"/>
+    <x:mergeCell ref="D46:E46"/>
+    <x:mergeCell ref="F46:G46"/>
+    <x:mergeCell ref="H46:I46"/>
+    <x:mergeCell ref="J46:K46"/>
+    <x:mergeCell ref="L46:M46"/>
+    <x:mergeCell ref="N46:O46"/>
+    <x:mergeCell ref="P46:Q46"/>
+    <x:mergeCell ref="R46:S46"/>
+    <x:mergeCell ref="A48:S48"/>
+    <x:mergeCell ref="A49:S49"/>
+    <x:mergeCell ref="A50:S50"/>
+    <x:mergeCell ref="A53:S53"/>
+    <x:mergeCell ref="A54:S54"/>
+    <x:mergeCell ref="B56:C56"/>
+    <x:mergeCell ref="D56:G56"/>
+    <x:mergeCell ref="H56:I56"/>
+    <x:mergeCell ref="J56:K56"/>
+    <x:mergeCell ref="L56:P56"/>
+    <x:mergeCell ref="Q56:S56"/>
+    <x:mergeCell ref="B57:C57"/>
+    <x:mergeCell ref="D57:G57"/>
+    <x:mergeCell ref="H57:I57"/>
+    <x:mergeCell ref="J57:K57"/>
+    <x:mergeCell ref="L57:P57"/>
+    <x:mergeCell ref="Q57:S57"/>
+    <x:mergeCell ref="B58:C58"/>
+    <x:mergeCell ref="D58:G58"/>
+    <x:mergeCell ref="H58:I58"/>
+    <x:mergeCell ref="J58:K58"/>
+    <x:mergeCell ref="L58:P58"/>
+    <x:mergeCell ref="Q58:S58"/>
+    <x:mergeCell ref="B59:C59"/>
+    <x:mergeCell ref="D59:G59"/>
+    <x:mergeCell ref="H59:I59"/>
+    <x:mergeCell ref="J59:K59"/>
+    <x:mergeCell ref="L59:P59"/>
+    <x:mergeCell ref="Q59:S59"/>
+    <x:mergeCell ref="B60:C60"/>
+    <x:mergeCell ref="D60:G60"/>
+    <x:mergeCell ref="H60:I60"/>
+    <x:mergeCell ref="J60:K60"/>
+    <x:mergeCell ref="L60:P60"/>
+    <x:mergeCell ref="Q60:S60"/>
+    <x:mergeCell ref="B61:C61"/>
+    <x:mergeCell ref="D61:G61"/>
+    <x:mergeCell ref="H61:I61"/>
+    <x:mergeCell ref="J61:K61"/>
+    <x:mergeCell ref="L61:P61"/>
+    <x:mergeCell ref="Q61:S61"/>
+    <x:mergeCell ref="A63:S63"/>
+    <x:mergeCell ref="A64:S64"/>
+  </x:mergeCells>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="B13:B21">
       <x:formula1>"是,否"</x:formula1>
@@ -12583,13 +13953,13 @@
         <x:v>W2</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>随设计细化WBS与估算</x:v>
+        <x:v>WBS、估算依据与已识别风险细化</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>细化任务依赖、资源和费用</x:v>
+        <x:v>复核需求、工作量假设、储备缺口和资源负荷</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>V1.1（拟定）</x:v>
+        <x:v>按实际修订登记</x:v>
       </x:c>
       <x:c r="E26" s="9"/>
       <x:c r="F26" s="9" t="str">
@@ -12609,13 +13979,13 @@
         <x:v>W4</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>主业务链阶段复核</x:v>
+        <x:v>主业务链与成本基准阶段复核</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>更新进度、负荷、质量和成本</x:v>
+        <x:v>复核剩余工作、累计PV与真实执行数据</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>V1.2（拟定）</x:v>
+        <x:v>按实际修订登记</x:v>
       </x:c>
       <x:c r="E27" s="9"/>
       <x:c r="F27" s="9" t="str">
@@ -12635,13 +14005,13 @@
         <x:v>W6</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>本地集成及外部条件复核</x:v>
+        <x:v>集成、质量成本与外部条件复核</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>复核剩余任务与真实交换影响</x:v>
+        <x:v>复核风险响应、验证成本及剩余任务</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>V1.3（拟定）</x:v>
+        <x:v>按实际修订登记</x:v>
       </x:c>
       <x:c r="E28" s="9"/>
       <x:c r="F28" s="9" t="str">
@@ -12661,13 +14031,13 @@
         <x:v>W8</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>汇总模拟过程并定稿</x:v>
+        <x:v>最终计划与真实版本证据复核</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>完整项目计划及迭代说明</x:v>
+        <x:v>最终计划、变更单及提交历史截图</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>V1.4（拟定）</x:v>
+        <x:v>按实际修订登记</x:v>
       </x:c>
       <x:c r="E29" s="9"/>
       <x:c r="F29" s="9" t="str">
@@ -12733,13 +14103,13 @@
         <x:v>RK01</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>人员能力或AI效率低于假设</x:v>
+        <x:v>人员能力或自动化辅助效率低于假设</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
         <x:v>开发投入上升，8周计划可能失效</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>W2/W4复核效率，优先调分工和资源；必要时重排，不降低验收标准</x:v>
+        <x:v>逐周复核效率；W2/W4重点复核。优先调整分工与可用容量；影响基线时办理CR，不降低验收标准。</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
         <x:v>R01</x:v>
@@ -12748,7 +14118,7 @@
         <x:v>利用任务时差与未分配容量</x:v>
       </x:c>
       <x:c r="G33" s="9" t="str">
-        <x:v>共享C14储备</x:v>
+        <x:v>应急储备未单列；额度待评估，见成本预算储备登记。</x:v>
       </x:c>
       <x:c r="H33" s="9" t="str">
         <x:v>仿真假设，实际情况待确认</x:v>
@@ -12765,7 +14135,7 @@
         <x:v>REAL适配、AC-10B和验收延迟</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>W2核对外部输入；缺失则记录影响并重排，不用MOCK算通过</x:v>
+        <x:v>W2核对外部输入；缺失时记录范围、进度、成本影响并办理CR，不用MOCK算通过。</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
         <x:v>R01/R02</x:v>
@@ -12774,7 +14144,7 @@
         <x:v>以Project重算为准</x:v>
       </x:c>
       <x:c r="G34" s="9" t="str">
-        <x:v>共享C14储备</x:v>
+        <x:v>应急储备未单列；额度待评估，见成本预算储备登记。</x:v>
       </x:c>
       <x:c r="H34" s="9" t="str">
         <x:v>已假设W2可用，未声明实际具备</x:v>
@@ -12800,7 +14170,7 @@
         <x:v>利用任务时差</x:v>
       </x:c>
       <x:c r="G35" s="9" t="str">
-        <x:v>共享C14储备</x:v>
+        <x:v>应急储备未单列；额度待评估，见成本预算储备登记。</x:v>
       </x:c>
       <x:c r="H35" s="9" t="str">
         <x:v>资源费用为仿真估算</x:v>
@@ -12817,7 +14187,7 @@
         <x:v>实际成本偏离预算</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>按任务工时和分周预算持续对比，偏差触发版本调整</x:v>
+        <x:v>每周以累计PV、AC和EV分析偏差与原因；基线变化办理CR，不能只以支出少认定成本绩效良好。</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
         <x:v>R01</x:v>
@@ -12826,7 +14196,7 @@
         <x:v>不增加固定期限</x:v>
       </x:c>
       <x:c r="G36" s="9" t="str">
-        <x:v>共享C14储备</x:v>
+        <x:v>应急储备未单列；额度待评估，见成本预算储备登记。</x:v>
       </x:c>
       <x:c r="H36" s="9" t="str">
         <x:v>实际成本与偏差尚未发生</x:v>
@@ -12852,7 +14222,7 @@
         <x:v>重排并评估8周可行性</x:v>
       </x:c>
       <x:c r="G37" s="9" t="str">
-        <x:v>共享C14储备</x:v>
+        <x:v>应急储备未单列；额度待评估，见成本预算储备登记。</x:v>
       </x:c>
       <x:c r="H37" s="9" t="str">
         <x:v>不将离线原型视为正式功能已完成</x:v>
@@ -12930,15 +14300,31 @@
         <x:v>仅完成仿真计划编制，不是软件执行成果</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="30" customHeight="1">
-      <x:c r="A42" s="4"/>
-      <x:c r="B42" s="4"/>
-      <x:c r="C42" s="4"/>
-      <x:c r="D42" s="4"/>
-      <x:c r="E42" s="4"/>
-      <x:c r="F42" s="4"/>
-      <x:c r="G42" s="4"/>
-      <x:c r="H42" s="4"/>
+    <x:row r="42" ht="96" customHeight="1">
+      <x:c r="A42" s="63" t="str">
+        <x:v>V1.0→V1.1</x:v>
+      </x:c>
+      <x:c r="B42" s="69" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C42" s="63" t="str">
+        <x:v>V1.1 / CM-R3</x:v>
+      </x:c>
+      <x:c r="D42" s="63" t="str">
+        <x:v>R01（计划编制角色）</x:v>
+      </x:c>
+      <x:c r="E42" s="63" t="str">
+        <x:v>完善逐周控制，排期不变</x:v>
+      </x:c>
+      <x:c r="F42" s="63" t="str">
+        <x:v>4人及877人时不变</x:v>
+      </x:c>
+      <x:c r="G42" s="63" t="str">
+        <x:v>分类及控制口径完善，金额不变</x:v>
+      </x:c>
+      <x:c r="H42" s="63" t="str">
+        <x:v>CR-003已修订计划；实际软件执行、支出及未来迭代结果不预填。</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="30" customHeight="1">
       <x:c r="A43" s="4"/>
@@ -12950,27 +14336,408 @@
       <x:c r="G43" s="4"/>
       <x:c r="H43" s="4"/>
     </x:row>
-    <x:row r="44" ht="30" customHeight="1">
-      <x:c r="A44" s="4"/>
-      <x:c r="B44" s="4"/>
-      <x:c r="C44" s="4"/>
-      <x:c r="D44" s="4"/>
-      <x:c r="E44" s="4"/>
-      <x:c r="F44" s="4"/>
-      <x:c r="G44" s="4"/>
-      <x:c r="H44" s="4"/>
-    </x:row>
-    <x:row r="45" ht="30" customHeight="1">
-      <x:c r="A45" s="4"/>
-      <x:c r="B45" s="4"/>
-      <x:c r="C45" s="4"/>
-      <x:c r="D45" s="4"/>
-      <x:c r="E45" s="4"/>
-      <x:c r="F45" s="4"/>
-      <x:c r="G45" s="4"/>
-      <x:c r="H45" s="4"/>
+    <x:row r="44" ht="28" customHeight="1">
+      <x:c r="A44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="B44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="C44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="D44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="E44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="F44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="G44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="H44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="I44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="J44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+      <x:c r="K44" s="60" t="str">
+        <x:v>W1–W8逐周计划复核与证据登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="44" customHeight="1">
+      <x:c r="A45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="B45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="C45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="D45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="E45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="F45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="G45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="H45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="I45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="J45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+      <x:c r="K45" s="63" t="str">
+        <x:v>每轮为周一至周日7个自然日，沿用既定任务排期；W2/W4/W6/W8保留阶段重点复核。实际完成日期、结论、提交和变更编号只在发生后登记，不预填未来历史。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="54" customHeight="1">
+      <x:c r="A47" s="60" t="str">
+        <x:v>迭代</x:v>
+      </x:c>
+      <x:c r="B47" s="60" t="str">
+        <x:v>计划窗口</x:v>
+      </x:c>
+      <x:c r="C47" s="60" t="str">
+        <x:v>复核与细化重点</x:v>
+      </x:c>
+      <x:c r="D47" s="60" t="str">
+        <x:v>预定产出</x:v>
+      </x:c>
+      <x:c r="E47" s="60" t="str">
+        <x:v>责任角色</x:v>
+      </x:c>
+      <x:c r="F47" s="60" t="str">
+        <x:v>实际完成日期</x:v>
+      </x:c>
+      <x:c r="G47" s="60" t="str">
+        <x:v>实际复核结论</x:v>
+      </x:c>
+      <x:c r="H47" s="60" t="str">
+        <x:v>版本／提交／证据</x:v>
+      </x:c>
+      <x:c r="I47" s="60" t="str">
+        <x:v>关联CR</x:v>
+      </x:c>
+      <x:c r="J47" s="60" t="str">
+        <x:v>转入周次</x:v>
+      </x:c>
+      <x:c r="K47" s="60" t="str">
+        <x:v>遗留事项</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="84" customHeight="1">
+      <x:c r="A48" s="63" t="str">
+        <x:v>W1</x:v>
+      </x:c>
+      <x:c r="B48" s="63" t="str">
+        <x:v>2026-10-19 至 2026-10-25</x:v>
+      </x:c>
+      <x:c r="C48" s="63" t="str">
+        <x:v>需求／WBS与估算方法对应，识别成本与储备边界</x:v>
+      </x:c>
+      <x:c r="D48" s="63" t="str">
+        <x:v>估算依据、成本控制与版本记录</x:v>
+      </x:c>
+      <x:c r="E48" s="63" t="str">
+        <x:v>R01编制／R04复核（模拟角色）</x:v>
+      </x:c>
+      <x:c r="F48" s="69"/>
+      <x:c r="G48" s="63"/>
+      <x:c r="H48" s="63"/>
+      <x:c r="I48" s="63"/>
+      <x:c r="J48" s="63"/>
+      <x:c r="K48" s="63"/>
+    </x:row>
+    <x:row r="49" ht="84" customHeight="1">
+      <x:c r="A49" s="63" t="str">
+        <x:v>W2</x:v>
+      </x:c>
+      <x:c r="B49" s="63" t="str">
+        <x:v>2026-10-26 至 2026-11-01</x:v>
+      </x:c>
+      <x:c r="C49" s="63" t="str">
+        <x:v>细化WBS、外部协议条件及不确定性，检查资源和储备缺口</x:v>
+      </x:c>
+      <x:c r="D49" s="63" t="str">
+        <x:v>阶段重点复核与风险响应说明</x:v>
+      </x:c>
+      <x:c r="E49" s="63" t="str">
+        <x:v>R01编制／R04复核（模拟角色）</x:v>
+      </x:c>
+      <x:c r="F49" s="69"/>
+      <x:c r="G49" s="63"/>
+      <x:c r="H49" s="63"/>
+      <x:c r="I49" s="63"/>
+      <x:c r="J49" s="63"/>
+      <x:c r="K49" s="63"/>
+    </x:row>
+    <x:row r="50" ht="84" customHeight="1">
+      <x:c r="A50" s="63" t="str">
+        <x:v>W3</x:v>
+      </x:c>
+      <x:c r="B50" s="63" t="str">
+        <x:v>2026-11-02 至 2026-11-08</x:v>
+      </x:c>
+      <x:c r="C50" s="63" t="str">
+        <x:v>检查业务活动投入与预期产出，复核剩余工作估算</x:v>
+      </x:c>
+      <x:c r="D50" s="63" t="str">
+        <x:v>周复核结论及实际偏差原因</x:v>
+      </x:c>
+      <x:c r="E50" s="63" t="str">
+        <x:v>R01编制／R04复核（模拟角色）</x:v>
+      </x:c>
+      <x:c r="F50" s="69"/>
+      <x:c r="G50" s="63"/>
+      <x:c r="H50" s="63"/>
+      <x:c r="I50" s="63"/>
+      <x:c r="J50" s="63"/>
+      <x:c r="K50" s="63"/>
+    </x:row>
+    <x:row r="51" ht="84" customHeight="1">
+      <x:c r="A51" s="63" t="str">
+        <x:v>W4</x:v>
+      </x:c>
+      <x:c r="B51" s="63" t="str">
+        <x:v>2026-11-09 至 2026-11-15</x:v>
+      </x:c>
+      <x:c r="C51" s="63" t="str">
+        <x:v>复核主业务链、累计成本基准和完成工作预算口径</x:v>
+      </x:c>
+      <x:c r="D51" s="63" t="str">
+        <x:v>阶段重点复核与受控修订</x:v>
+      </x:c>
+      <x:c r="E51" s="63" t="str">
+        <x:v>R01编制／R04复核（模拟角色）</x:v>
+      </x:c>
+      <x:c r="F51" s="69"/>
+      <x:c r="G51" s="63"/>
+      <x:c r="H51" s="63"/>
+      <x:c r="I51" s="63"/>
+      <x:c r="J51" s="63"/>
+      <x:c r="K51" s="63"/>
+    </x:row>
+    <x:row r="52" ht="84" customHeight="1">
+      <x:c r="A52" s="63" t="str">
+        <x:v>W5</x:v>
+      </x:c>
+      <x:c r="B52" s="63" t="str">
+        <x:v>2026-11-16 至 2026-11-22</x:v>
+      </x:c>
+      <x:c r="C52" s="63" t="str">
+        <x:v>复核模块集成、剩余工作量及外部条件变化</x:v>
+      </x:c>
+      <x:c r="D52" s="63" t="str">
+        <x:v>集成阶段估算前提与风险说明</x:v>
+      </x:c>
+      <x:c r="E52" s="63" t="str">
+        <x:v>R01编制／R04复核（模拟角色）</x:v>
+      </x:c>
+      <x:c r="F52" s="69"/>
+      <x:c r="G52" s="63"/>
+      <x:c r="H52" s="63"/>
+      <x:c r="I52" s="63"/>
+      <x:c r="J52" s="63"/>
+      <x:c r="K52" s="63"/>
+    </x:row>
+    <x:row r="53" ht="84" customHeight="1">
+      <x:c r="A53" s="63" t="str">
+        <x:v>W6</x:v>
+      </x:c>
+      <x:c r="B53" s="63" t="str">
+        <x:v>2026-11-23 至 2026-11-29</x:v>
+      </x:c>
+      <x:c r="C53" s="63" t="str">
+        <x:v>复核质量活动、验证费用及真实交换条件</x:v>
+      </x:c>
+      <x:c r="D53" s="63" t="str">
+        <x:v>阶段重点复核与成本预测</x:v>
+      </x:c>
+      <x:c r="E53" s="63" t="str">
+        <x:v>R01编制／R04复核（模拟角色）</x:v>
+      </x:c>
+      <x:c r="F53" s="69"/>
+      <x:c r="G53" s="63"/>
+      <x:c r="H53" s="63"/>
+      <x:c r="I53" s="63"/>
+      <x:c r="J53" s="63"/>
+      <x:c r="K53" s="63"/>
+    </x:row>
+    <x:row r="54" ht="84" customHeight="1">
+      <x:c r="A54" s="63" t="str">
+        <x:v>W7</x:v>
+      </x:c>
+      <x:c r="B54" s="63" t="str">
+        <x:v>2026-11-30 至 2026-12-06</x:v>
+      </x:c>
+      <x:c r="C54" s="63" t="str">
+        <x:v>复核验证、缺陷修复和交付准备的进度成本影响</x:v>
+      </x:c>
+      <x:c r="D54" s="63" t="str">
+        <x:v>缺陷及成本偏差处理记录</x:v>
+      </x:c>
+      <x:c r="E54" s="63" t="str">
+        <x:v>R01编制／R04复核（模拟角色）</x:v>
+      </x:c>
+      <x:c r="F54" s="69"/>
+      <x:c r="G54" s="63"/>
+      <x:c r="H54" s="63"/>
+      <x:c r="I54" s="63"/>
+      <x:c r="J54" s="63"/>
+      <x:c r="K54" s="63"/>
+    </x:row>
+    <x:row r="55" ht="84" customHeight="1">
+      <x:c r="A55" s="63" t="str">
+        <x:v>W8</x:v>
+      </x:c>
+      <x:c r="B55" s="63" t="str">
+        <x:v>2026-12-07 至 2026-12-13</x:v>
+      </x:c>
+      <x:c r="C55" s="63" t="str">
+        <x:v>复核最终计划、范围质量覆盖与全部真实变更证据</x:v>
+      </x:c>
+      <x:c r="D55" s="63" t="str">
+        <x:v>最终计划、变更单与提交历史截图</x:v>
+      </x:c>
+      <x:c r="E55" s="63" t="str">
+        <x:v>R01编制／R04复核（模拟角色）</x:v>
+      </x:c>
+      <x:c r="F55" s="69"/>
+      <x:c r="G55" s="63"/>
+      <x:c r="H55" s="63"/>
+      <x:c r="I55" s="63"/>
+      <x:c r="J55" s="63"/>
+      <x:c r="K55" s="63"/>
+    </x:row>
+    <x:row r="57" ht="44" customHeight="1">
+      <x:c r="A57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="B57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="C57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="D57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="E57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="F57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="G57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="H57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="I57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="J57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+      <x:c r="K57" s="63" t="str">
+        <x:v>每轮保存可审阅的真实修改及其影响；形成受控基线修订时同步提交变更单源与PDF、两种计划及版本记录。无基线变化时记录实际复核结论即可，不为凑版本制造CR。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="44" customHeight="1">
+      <x:c r="A58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="B58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="C58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="D58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="E58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="F58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="G58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="H58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="I58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="J58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+      <x:c r="K58" s="63" t="str">
+        <x:v>未完成事项如实登记原因、影响和转入周次；不延长本轮7日窗口、不倒签时间。最终提交计划终版、变更申请单和真实提交历史截图，平台及格式以正式通知为准。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="44" customHeight="1">
+      <x:c r="A59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="B59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="C59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="D59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="E59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="F59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="G59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="H59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="I59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="J59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+      <x:c r="K59" s="63" t="str">
+        <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A44:K44"/>
+    <x:mergeCell ref="A45:K45"/>
+    <x:mergeCell ref="A57:K57"/>
+    <x:mergeCell ref="A58:K58"/>
+    <x:mergeCell ref="A59:K59"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>

--- a/项目计划/提交文件/项目计划表_四人仿真.xlsx
+++ b/项目计划/提交文件/项目计划表_四人仿真.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目总表" sheetId="1" r:id="Ra7b3c7cf53924a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务与甘特" sheetId="2" r:id="R3ccd34fa917d489a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源计划" sheetId="3" r:id="R86089b04b3b24999"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本预算" sheetId="4" r:id="Rf705290a8ae345ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="质量与变更" sheetId="5" r:id="R499151838b3a4181"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日期甘特" sheetId="6" r:id="R22acb462c5ba4035"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目总表" sheetId="1" r:id="R080707031d3c481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务与甘特" sheetId="2" r:id="Rca938fb9ad454ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源计划" sheetId="3" r:id="R1a6c1dc13bd7489b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本预算" sheetId="4" r:id="Rce1153716ef248e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="质量与变更" sheetId="5" r:id="R74a953418367483b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日期甘特" sheetId="6" r:id="R0f567543554d4aa4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -29,7 +29,7 @@
     <x:numFmt numFmtId="207" formatCode="0"/>
     <x:numFmt numFmtId="208" formatCode="m/d"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -80,13 +80,23 @@
       <x:color rgb="FF111111"/>
       <x:name val="SimSun"/>
     </x:font>
+    <x:font>
+      <x:sz val="10.5"/>
+      <x:color rgb="FF111111"/>
+      <x:name val="SimSun"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -131,7 +141,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="76">
+  <x:cellXfs count="92">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -337,6 +347,44 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -554,7 +602,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>项目计划表（4人8周仿真，V1.1）</x:v>
+        <x:v>项目计划表（4人8周仿真，V1.2）</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -876,18 +924,18 @@
         <x:v>日期为仿真，参数修改后重新核验依赖和Project</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="66" customHeight="1">
+    <x:row r="28" ht="72" customHeight="1">
       <x:c r="A28" s="9" t="str">
         <x:v>资源</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>4人，项目经理兼需求与开发、后端、前端、测试部署兼工具开发</x:v>
+        <x:v>4人原有分工及投入不变；44项活动明确责任、参与和非作者交叉复核安排。</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
         <x:v>资源计划</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>实际人员身份未确认；分配为明确模拟角色</x:v>
+        <x:v>实际成员及外部发起人未确认；不将兼岗复核称为独立质量部门。</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="66" customHeight="1">
@@ -918,32 +966,32 @@
         <x:v>基准、储备与实际支出分别管理；储备调整须办理基线变更。</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="66" customHeight="1">
+    <x:row r="31" ht="72" customHeight="1">
       <x:c r="A31" s="9" t="str">
         <x:v>质量</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>16项质量标准有对应任务、仿真负责人、计划日期和证据要求</x:v>
+        <x:v>保留16项产品质量标准，补充8项全过程质量活动、6项度量口径和缺陷闭环。</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
         <x:v>质量与变更</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>实际测试日期、结果及接收凭据继续留空</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="66" customHeight="1">
+        <x:v>实际审计、测试、复测、支出及验收结论在发生后登记。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="72" customHeight="1">
       <x:c r="A32" s="9" t="str">
         <x:v>迭代</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>W1–W8每周复核并记录；W2/W4/W6/W8开展阶段重点复核。</x:v>
+        <x:v>W1–W8每周复核质量、估算和风险；W2/W4/W6/W8保留阶段重点复核。</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
         <x:v>质量与变更</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>逐轮记录真实产出、估算细化、偏差及版本；无基线变化时不制造修订。</x:v>
+        <x:v>保留真实版本及CR；未解决问题登记责任和转入轮次，不延长本轮。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="66" customHeight="1">
@@ -1152,18 +1200,18 @@
         <x:v>用于范围与质量标准</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="60" customHeight="1">
+    <x:row r="50" ht="72" customHeight="1">
       <x:c r="A50" s="9" t="str">
         <x:v>暂时性实施规划</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>沿用既有任务与投入，按周细化估算假设、外部条件、成本偏差和风险响应。</x:v>
+        <x:v>质量活动与交叉复核嵌入既有需求、设计、开发、测试及计划维护投入；逐周核对可行性。</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
         <x:v>本版计划基线</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>每轮7个自然日；变更同步两种计划、变更单、版本记录及真实提交证据。</x:v>
+        <x:v>不额外增加任务、工时、费用或周末投入；超过现有容量时分析影响并办理CR。</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
@@ -1180,18 +1228,18 @@
         <x:v>依据或使用说明</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="58" customHeight="1">
+    <x:row r="52" ht="66" customHeight="1">
       <x:c r="A52" s="29" t="str">
         <x:v>计划版本</x:v>
       </x:c>
       <x:c r="B52" s="29" t="str">
-        <x:v>V1.1</x:v>
+        <x:v>V1.2</x:v>
       </x:c>
       <x:c r="C52" s="29" t="str">
-        <x:v>CM-R3修订</x:v>
+        <x:v>CM-R4修订</x:v>
       </x:c>
       <x:c r="D52" s="29" t="str">
-        <x:v>CR-003完善估算、储备边界和逐周控制；预算、工时与排期沿用原值。</x:v>
+        <x:v>CR-004补充质量保证、成果控制、职责及质量费用口径；原参数保持一致。</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
@@ -1400,9 +1448,9 @@
       <x:c r="C70" s="36"/>
       <x:c r="D70" s="36"/>
     </x:row>
-    <x:row r="71">
+    <x:row r="71" ht="48" customHeight="1">
       <x:c r="A71" s="36" t="str">
-        <x:v>W1–W8按周复核并保留真实版本记录；W2/W4/W6/W8为阶段重点复核，不预填未来完成结果。</x:v>
+        <x:v>质量活动贯穿需求、设计、开发和测试，在原任务投入内开展交叉复核；W1–W8逐周复核，W2/W4/W6/W8阶段重点复核。</x:v>
       </x:c>
       <x:c r="B71" s="36"/>
       <x:c r="C71" s="36"/>
@@ -8147,7 +8195,7 @@
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>R01–R04为4名明确仿真成员，R05停用。测试部署成员兼工具开发；无实际人员工时记录。</x:v>
+        <x:v>R01–R04为4名明确仿真成员，R05停用。原分配内开展成果交接与非作者交叉复核；实际成员履历和执行结果留空。</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -8832,7 +8880,7 @@
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
       <x:c r="A21" s="23" t="str">
-        <x:v>日期和投入修改后须重新核验业务依赖及Project；实际假期和个人日程未确认。</x:v>
+        <x:v>交叉复核按具体成果避开作者；兼岗成员互核，不认定存在独立质量部门。日期、投入变化须办理CR并重核负荷。</x:v>
       </x:c>
       <x:c r="B21" s="23"/>
       <x:c r="C21" s="23"/>
@@ -10344,7 +10392,3161 @@
         <x:v>未超上限</x:v>
       </x:c>
     </x:row>
+    <x:row r="71" ht="28" customHeight="1">
+      <x:c r="A71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="B71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="C71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="D71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="E71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="F71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="G71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="H71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="I71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="J71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="K71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="L71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="M71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="N71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="O71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="P71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="Q71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="R71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+      <x:c r="S71" s="86" t="str">
+        <x:v>任务责任、参与与交叉复核矩阵</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="44" customHeight="1">
+      <x:c r="A72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="B72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="C72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="D72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="E72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="F72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="G72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="H72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="I72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="J72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="K72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="L72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="M72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="N72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="O72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="P72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="Q72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="R72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+      <x:c r="S72" s="79" t="str">
+        <x:v>R01统筹计划、需求与协调；R02后端与数据；R03前端；R04测试部署兼工具开发。A/R为原责任人并执行，R为已有正工时参与者，I为知会且原任务未分配工时。交接对象引用原交付物。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="46" customHeight="1">
+      <x:c r="A74" s="86" t="str">
+        <x:v>WBS</x:v>
+      </x:c>
+      <x:c r="B74" s="86" t="str">
+        <x:v>任务</x:v>
+      </x:c>
+      <x:c r="C74" s="86" t="str">
+        <x:v>任务</x:v>
+      </x:c>
+      <x:c r="D74" s="86" t="str">
+        <x:v>任务</x:v>
+      </x:c>
+      <x:c r="E74" s="86" t="str">
+        <x:v>原责任人</x:v>
+      </x:c>
+      <x:c r="F74" s="86" t="str">
+        <x:v>原责任人</x:v>
+      </x:c>
+      <x:c r="G74" s="86" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="H74" s="86" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="I74" s="86" t="str">
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="J74" s="86" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="K74" s="86" t="str">
+        <x:v>牵头交叉复核</x:v>
+      </x:c>
+      <x:c r="L74" s="86" t="str">
+        <x:v>牵头交叉复核</x:v>
+      </x:c>
+      <x:c r="M74" s="86" t="str">
+        <x:v>复核重点</x:v>
+      </x:c>
+      <x:c r="N74" s="86" t="str">
+        <x:v>复核重点</x:v>
+      </x:c>
+      <x:c r="O74" s="86" t="str">
+        <x:v>复核重点</x:v>
+      </x:c>
+      <x:c r="P74" s="86" t="str">
+        <x:v>复核重点</x:v>
+      </x:c>
+      <x:c r="Q74" s="86" t="str">
+        <x:v>交接/复核对象</x:v>
+      </x:c>
+      <x:c r="R74" s="86" t="str">
+        <x:v>交接/复核对象</x:v>
+      </x:c>
+      <x:c r="S74" s="86" t="str">
+        <x:v>交接/复核对象</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="72" customHeight="1">
+      <x:c r="A75" s="79" t="str">
+        <x:f>'任务与甘特'!A7</x:f>
+        <x:v>T1.1</x:v>
+      </x:c>
+      <x:c r="B75" s="79" t="str">
+        <x:f>'任务与甘特'!B7</x:f>
+        <x:v>核对需求范围与覆盖</x:v>
+      </x:c>
+      <x:c r="C75" s="79"/>
+      <x:c r="D75" s="79"/>
+      <x:c r="E75" s="79" t="str">
+        <x:f>'任务与甘特'!R7</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F75" s="79"/>
+      <x:c r="G75" s="79" t="str">
+        <x:f>IF($E75="R01","A/R",IF(ISNUMBER('任务与甘特'!Y7),IF('任务与甘特'!Y7&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H75" s="79" t="str">
+        <x:f>IF($E75="R02","A/R",IF(ISNUMBER('任务与甘特'!Z7),IF('任务与甘特'!Z7&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I75" s="79" t="str">
+        <x:f>IF($E75="R03","A/R",IF(ISNUMBER('任务与甘特'!AA7),IF('任务与甘特'!AA7&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J75" s="79" t="str">
+        <x:f>IF($E75="R04","A/R",IF(ISNUMBER('任务与甘特'!AB7),IF('任务与甘特'!AB7&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K75" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L75" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M75" s="79" t="str">
+        <x:v>逐项核对43项需求、WBS和AC；登记歧义及决定。</x:v>
+      </x:c>
+      <x:c r="N75" s="79" t="str">
+        <x:v>逐项核对43项需求、WBS和AC；登记歧义及决定。</x:v>
+      </x:c>
+      <x:c r="O75" s="79" t="str">
+        <x:v>逐项核对43项需求、WBS和AC；登记歧义及决定。</x:v>
+      </x:c>
+      <x:c r="P75" s="79" t="str">
+        <x:v>逐项核对43项需求、WBS和AC；登记歧义及决定。</x:v>
+      </x:c>
+      <x:c r="Q75" s="79" t="str">
+        <x:f>'任务与甘特'!P7</x:f>
+        <x:v>范围说明与需求覆盖矩阵</x:v>
+      </x:c>
+      <x:c r="R75" s="79"/>
+      <x:c r="S75" s="79"/>
+    </x:row>
+    <x:row r="76" ht="72" customHeight="1">
+      <x:c r="A76" s="79" t="str">
+        <x:f>'任务与甘特'!A8</x:f>
+        <x:v>T1.2</x:v>
+      </x:c>
+      <x:c r="B76" s="79" t="str">
+        <x:f>'任务与甘特'!B8</x:f>
+        <x:v>形成WBS与项目计划初稿</x:v>
+      </x:c>
+      <x:c r="C76" s="79"/>
+      <x:c r="D76" s="79"/>
+      <x:c r="E76" s="79" t="str">
+        <x:f>'任务与甘特'!R8</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F76" s="79"/>
+      <x:c r="G76" s="79" t="str">
+        <x:f>IF($E76="R01","A/R",IF(ISNUMBER('任务与甘特'!Y8),IF('任务与甘特'!Y8&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H76" s="79" t="str">
+        <x:f>IF($E76="R02","A/R",IF(ISNUMBER('任务与甘特'!Z8),IF('任务与甘特'!Z8&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I76" s="79" t="str">
+        <x:f>IF($E76="R03","A/R",IF(ISNUMBER('任务与甘特'!AA8),IF('任务与甘特'!AA8&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J76" s="79" t="str">
+        <x:f>IF($E76="R04","A/R",IF(ISNUMBER('任务与甘特'!AB8),IF('任务与甘特'!AB8&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K76" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L76" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M76" s="79" t="str">
+        <x:v>计划明确质量目标、活动、责任、证据及容量假设。</x:v>
+      </x:c>
+      <x:c r="N76" s="79" t="str">
+        <x:v>计划明确质量目标、活动、责任、证据及容量假设。</x:v>
+      </x:c>
+      <x:c r="O76" s="79" t="str">
+        <x:v>计划明确质量目标、活动、责任、证据及容量假设。</x:v>
+      </x:c>
+      <x:c r="P76" s="79" t="str">
+        <x:v>计划明确质量目标、活动、责任、证据及容量假设。</x:v>
+      </x:c>
+      <x:c r="Q76" s="79" t="str">
+        <x:f>'任务与甘特'!P8</x:f>
+        <x:v>范围、进度、资源、成本、质量计划</x:v>
+      </x:c>
+      <x:c r="R76" s="79"/>
+      <x:c r="S76" s="79"/>
+    </x:row>
+    <x:row r="77" ht="72" customHeight="1">
+      <x:c r="A77" s="79" t="str">
+        <x:f>'任务与甘特'!A9</x:f>
+        <x:v>T1.3</x:v>
+      </x:c>
+      <x:c r="B77" s="79" t="str">
+        <x:f>'任务与甘特'!B9</x:f>
+        <x:v>编写测试大纲与合成数据方案</x:v>
+      </x:c>
+      <x:c r="C77" s="79"/>
+      <x:c r="D77" s="79"/>
+      <x:c r="E77" s="79" t="str">
+        <x:f>'任务与甘特'!R9</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F77" s="79"/>
+      <x:c r="G77" s="79" t="str">
+        <x:f>IF($E77="R01","A/R",IF(ISNUMBER('任务与甘特'!Y9),IF('任务与甘特'!Y9&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H77" s="79" t="str">
+        <x:f>IF($E77="R02","A/R",IF(ISNUMBER('任务与甘特'!Z9),IF('任务与甘特'!Z9&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I77" s="79" t="str">
+        <x:f>IF($E77="R03","A/R",IF(ISNUMBER('任务与甘特'!AA9),IF('任务与甘特'!AA9&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J77" s="79" t="str">
+        <x:f>IF($E77="R04","A/R",IF(ISNUMBER('任务与甘特'!AB9),IF('任务与甘特'!AB9&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K77" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="L77" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="M77" s="79" t="str">
+        <x:v>实现前评审测试大纲、数据、必需用例与证据规则。</x:v>
+      </x:c>
+      <x:c r="N77" s="79" t="str">
+        <x:v>实现前评审测试大纲、数据、必需用例与证据规则。</x:v>
+      </x:c>
+      <x:c r="O77" s="79" t="str">
+        <x:v>实现前评审测试大纲、数据、必需用例与证据规则。</x:v>
+      </x:c>
+      <x:c r="P77" s="79" t="str">
+        <x:v>实现前评审测试大纲、数据、必需用例与证据规则。</x:v>
+      </x:c>
+      <x:c r="Q77" s="79" t="str">
+        <x:f>'任务与甘特'!P9</x:f>
+        <x:v>测试大纲、验收数据与预期答案</x:v>
+      </x:c>
+      <x:c r="R77" s="79"/>
+      <x:c r="S77" s="79"/>
+    </x:row>
+    <x:row r="78" ht="72" customHeight="1">
+      <x:c r="A78" s="79" t="str">
+        <x:f>'任务与甘特'!A10</x:f>
+        <x:v>T2.1</x:v>
+      </x:c>
+      <x:c r="B78" s="79" t="str">
+        <x:f>'任务与甘特'!B10</x:f>
+        <x:v>总体架构与模块设计</x:v>
+      </x:c>
+      <x:c r="C78" s="79"/>
+      <x:c r="D78" s="79"/>
+      <x:c r="E78" s="79" t="str">
+        <x:f>'任务与甘特'!R10</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F78" s="79"/>
+      <x:c r="G78" s="79" t="str">
+        <x:f>IF($E78="R01","A/R",IF(ISNUMBER('任务与甘特'!Y10),IF('任务与甘特'!Y10&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H78" s="79" t="str">
+        <x:f>IF($E78="R02","A/R",IF(ISNUMBER('任务与甘特'!Z10),IF('任务与甘特'!Z10&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I78" s="79" t="str">
+        <x:f>IF($E78="R03","A/R",IF(ISNUMBER('任务与甘特'!AA10),IF('任务与甘特'!AA10&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J78" s="79" t="str">
+        <x:f>IF($E78="R04","A/R",IF(ISNUMBER('任务与甘特'!AB10),IF('任务与甘特'!AB10&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K78" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L78" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M78" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="N78" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="O78" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="P78" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="Q78" s="79" t="str">
+        <x:f>'任务与甘特'!P10</x:f>
+        <x:v>总体设计与模块接口说明</x:v>
+      </x:c>
+      <x:c r="R78" s="79"/>
+      <x:c r="S78" s="79"/>
+    </x:row>
+    <x:row r="79" ht="72" customHeight="1">
+      <x:c r="A79" s="79" t="str">
+        <x:f>'任务与甘特'!A11</x:f>
+        <x:v>T2.2</x:v>
+      </x:c>
+      <x:c r="B79" s="79" t="str">
+        <x:f>'任务与甘特'!B11</x:f>
+        <x:v>数据模型、版本与事务设计</x:v>
+      </x:c>
+      <x:c r="C79" s="79"/>
+      <x:c r="D79" s="79"/>
+      <x:c r="E79" s="79" t="str">
+        <x:f>'任务与甘特'!R11</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F79" s="79"/>
+      <x:c r="G79" s="79" t="str">
+        <x:f>IF($E79="R01","A/R",IF(ISNUMBER('任务与甘特'!Y11),IF('任务与甘特'!Y11&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H79" s="79" t="str">
+        <x:f>IF($E79="R02","A/R",IF(ISNUMBER('任务与甘特'!Z11),IF('任务与甘特'!Z11&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I79" s="79" t="str">
+        <x:f>IF($E79="R03","A/R",IF(ISNUMBER('任务与甘特'!AA11),IF('任务与甘特'!AA11&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J79" s="79" t="str">
+        <x:f>IF($E79="R04","A/R",IF(ISNUMBER('任务与甘特'!AB11),IF('任务与甘特'!AB11&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="K79" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="L79" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="M79" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="N79" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="O79" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="P79" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="Q79" s="79" t="str">
+        <x:f>'任务与甘特'!P11</x:f>
+        <x:v>数据模型、迁移与快照审计设计</x:v>
+      </x:c>
+      <x:c r="R79" s="79"/>
+      <x:c r="S79" s="79"/>
+    </x:row>
+    <x:row r="80" ht="72" customHeight="1">
+      <x:c r="A80" s="79" t="str">
+        <x:f>'任务与甘特'!A12</x:f>
+        <x:v>T2.3</x:v>
+      </x:c>
+      <x:c r="B80" s="79" t="str">
+        <x:f>'任务与甘特'!B12</x:f>
+        <x:v>内部接口与导出契约设计</x:v>
+      </x:c>
+      <x:c r="C80" s="79"/>
+      <x:c r="D80" s="79"/>
+      <x:c r="E80" s="79" t="str">
+        <x:f>'任务与甘特'!R12</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F80" s="79"/>
+      <x:c r="G80" s="79" t="str">
+        <x:f>IF($E80="R01","A/R",IF(ISNUMBER('任务与甘特'!Y12),IF('任务与甘特'!Y12&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H80" s="79" t="str">
+        <x:f>IF($E80="R02","A/R",IF(ISNUMBER('任务与甘特'!Z12),IF('任务与甘特'!Z12&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I80" s="79" t="str">
+        <x:f>IF($E80="R03","A/R",IF(ISNUMBER('任务与甘特'!AA12),IF('任务与甘特'!AA12&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J80" s="79" t="str">
+        <x:f>IF($E80="R04","A/R",IF(ISNUMBER('任务与甘特'!AB12),IF('任务与甘特'!AB12&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K80" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L80" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M80" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="N80" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="O80" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="P80" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="Q80" s="79" t="str">
+        <x:f>'任务与甘特'!P12</x:f>
+        <x:v>内部API、导出、监控和MOCK契约</x:v>
+      </x:c>
+      <x:c r="R80" s="79"/>
+      <x:c r="S80" s="79"/>
+    </x:row>
+    <x:row r="81" ht="72" customHeight="1">
+      <x:c r="A81" s="79" t="str">
+        <x:f>'任务与甘特'!A13</x:f>
+        <x:v>T2.4</x:v>
+      </x:c>
+      <x:c r="B81" s="79" t="str">
+        <x:f>'任务与甘特'!B13</x:f>
+        <x:v>确认国家真实交换输入</x:v>
+      </x:c>
+      <x:c r="C81" s="79"/>
+      <x:c r="D81" s="79"/>
+      <x:c r="E81" s="79" t="str">
+        <x:f>'任务与甘特'!R13</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F81" s="79"/>
+      <x:c r="G81" s="79" t="str">
+        <x:f>IF($E81="R01","A/R",IF(ISNUMBER('任务与甘特'!Y13),IF('任务与甘特'!Y13&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H81" s="79" t="str">
+        <x:f>IF($E81="R02","A/R",IF(ISNUMBER('任务与甘特'!Z13),IF('任务与甘特'!Z13&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I81" s="79" t="str">
+        <x:f>IF($E81="R03","A/R",IF(ISNUMBER('任务与甘特'!AA13),IF('任务与甘特'!AA13&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J81" s="79" t="str">
+        <x:f>IF($E81="R04","A/R",IF(ISNUMBER('任务与甘特'!AB13),IF('任务与甘特'!AB13&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="K81" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="L81" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="M81" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="N81" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="O81" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="P81" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="Q81" s="79" t="str">
+        <x:f>'任务与甘特'!P13</x:f>
+        <x:v>协议版本、端点用途、认证与字段编码映射</x:v>
+      </x:c>
+      <x:c r="R81" s="79"/>
+      <x:c r="S81" s="79"/>
+    </x:row>
+    <x:row r="82" ht="72" customHeight="1">
+      <x:c r="A82" s="79" t="str">
+        <x:f>'任务与甘特'!A14</x:f>
+        <x:v>T2.5</x:v>
+      </x:c>
+      <x:c r="B82" s="79" t="str">
+        <x:f>'任务与甘特'!B14</x:f>
+        <x:v>维护计划与配置版本</x:v>
+      </x:c>
+      <x:c r="C82" s="79"/>
+      <x:c r="D82" s="79"/>
+      <x:c r="E82" s="79" t="str">
+        <x:f>'任务与甘特'!R14</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F82" s="79"/>
+      <x:c r="G82" s="79" t="str">
+        <x:f>IF($E82="R01","A/R",IF(ISNUMBER('任务与甘特'!Y14),IF('任务与甘特'!Y14&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H82" s="79" t="str">
+        <x:f>IF($E82="R02","A/R",IF(ISNUMBER('任务与甘特'!Z14),IF('任务与甘特'!Z14&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I82" s="79" t="str">
+        <x:f>IF($E82="R03","A/R",IF(ISNUMBER('任务与甘特'!AA14),IF('任务与甘特'!AA14&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J82" s="79" t="str">
+        <x:f>IF($E82="R04","A/R",IF(ISNUMBER('任务与甘特'!AB14),IF('任务与甘特'!AB14&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="K82" s="79" t="str">
+        <x:v>原阶段评审中抽查</x:v>
+      </x:c>
+      <x:c r="L82" s="79" t="str">
+        <x:v>原阶段评审中抽查</x:v>
+      </x:c>
+      <x:c r="M82" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="N82" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="O82" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="P82" s="79" t="str">
+        <x:v>设计、接口、状态、权限及性能前提交叉复核；版本/CR真实对应。</x:v>
+      </x:c>
+      <x:c r="Q82" s="79" t="str">
+        <x:f>'任务与甘特'!P14</x:f>
+        <x:v>计划修订记录、配置和文档版本</x:v>
+      </x:c>
+      <x:c r="R82" s="79"/>
+      <x:c r="S82" s="79"/>
+    </x:row>
+    <x:row r="83" ht="72" customHeight="1">
+      <x:c r="A83" s="79" t="str">
+        <x:f>'任务与甘特'!A15</x:f>
+        <x:v>T3.1</x:v>
+      </x:c>
+      <x:c r="B83" s="79" t="str">
+        <x:f>'任务与甘特'!B15</x:f>
+        <x:v>建立开发与本地集成环境</x:v>
+      </x:c>
+      <x:c r="C83" s="79"/>
+      <x:c r="D83" s="79"/>
+      <x:c r="E83" s="79" t="str">
+        <x:f>'任务与甘特'!R15</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F83" s="79"/>
+      <x:c r="G83" s="79" t="str">
+        <x:f>IF($E83="R01","A/R",IF(ISNUMBER('任务与甘特'!Y15),IF('任务与甘特'!Y15&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H83" s="79" t="str">
+        <x:f>IF($E83="R02","A/R",IF(ISNUMBER('任务与甘特'!Z15),IF('任务与甘特'!Z15&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I83" s="79" t="str">
+        <x:f>IF($E83="R03","A/R",IF(ISNUMBER('任务与甘特'!AA15),IF('任务与甘特'!AA15&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J83" s="79" t="str">
+        <x:f>IF($E83="R04","A/R",IF(ISNUMBER('任务与甘特'!AB15),IF('任务与甘特'!AB15&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K83" s="79" t="str">
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="L83" s="79" t="str">
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="M83" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N83" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O83" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P83" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q83" s="79" t="str">
+        <x:f>'任务与甘特'!P15</x:f>
+        <x:v>项目骨架、锁定依赖与启动说明</x:v>
+      </x:c>
+      <x:c r="R83" s="79"/>
+      <x:c r="S83" s="79"/>
+    </x:row>
+    <x:row r="84" ht="72" customHeight="1">
+      <x:c r="A84" s="79" t="str">
+        <x:f>'任务与甘特'!A16</x:f>
+        <x:v>T3.2</x:v>
+      </x:c>
+      <x:c r="B84" s="79" t="str">
+        <x:f>'任务与甘特'!B16</x:f>
+        <x:v>实现认证、权限和角色基础</x:v>
+      </x:c>
+      <x:c r="C84" s="79"/>
+      <x:c r="D84" s="79"/>
+      <x:c r="E84" s="79" t="str">
+        <x:f>'任务与甘特'!R16</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F84" s="79"/>
+      <x:c r="G84" s="79" t="str">
+        <x:f>IF($E84="R01","A/R",IF(ISNUMBER('任务与甘特'!Y16),IF('任务与甘特'!Y16&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H84" s="79" t="str">
+        <x:f>IF($E84="R02","A/R",IF(ISNUMBER('任务与甘特'!Z16),IF('任务与甘特'!Z16&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I84" s="79" t="str">
+        <x:f>IF($E84="R03","A/R",IF(ISNUMBER('任务与甘特'!AA16),IF('任务与甘特'!AA16&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J84" s="79" t="str">
+        <x:f>IF($E84="R04","A/R",IF(ISNUMBER('任务与甘特'!AB16),IF('任务与甘特'!AB16&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K84" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L84" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M84" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N84" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O84" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P84" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q84" s="79" t="str">
+        <x:f>'任务与甘特'!P16</x:f>
+        <x:v>会话、范围鉴权、TOTP与角色管理</x:v>
+      </x:c>
+      <x:c r="R84" s="79"/>
+      <x:c r="S84" s="79"/>
+    </x:row>
+    <x:row r="85" ht="72" customHeight="1">
+      <x:c r="A85" s="79" t="str">
+        <x:f>'任务与甘特'!A17</x:f>
+        <x:v>T3.3</x:v>
+      </x:c>
+      <x:c r="B85" s="79" t="str">
+        <x:f>'任务与甘特'!B17</x:f>
+        <x:v>实现字典、地区和基准管理</x:v>
+      </x:c>
+      <x:c r="C85" s="79"/>
+      <x:c r="D85" s="79"/>
+      <x:c r="E85" s="79" t="str">
+        <x:f>'任务与甘特'!R17</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F85" s="79"/>
+      <x:c r="G85" s="79" t="str">
+        <x:f>IF($E85="R01","A/R",IF(ISNUMBER('任务与甘特'!Y17),IF('任务与甘特'!Y17&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H85" s="79" t="str">
+        <x:f>IF($E85="R02","A/R",IF(ISNUMBER('任务与甘特'!Z17),IF('任务与甘特'!Z17&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I85" s="79" t="str">
+        <x:f>IF($E85="R03","A/R",IF(ISNUMBER('任务与甘特'!AA17),IF('任务与甘特'!AA17&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J85" s="79" t="str">
+        <x:f>IF($E85="R04","A/R",IF(ISNUMBER('任务与甘特'!AB17),IF('任务与甘特'!AB17&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="K85" s="79" t="str">
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="L85" s="79" t="str">
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="M85" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N85" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O85" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P85" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q85" s="79" t="str">
+        <x:f>'任务与甘特'!P17</x:f>
+        <x:v>字典地区种子与基准版本功能</x:v>
+      </x:c>
+      <x:c r="R85" s="79"/>
+      <x:c r="S85" s="79"/>
+    </x:row>
+    <x:row r="86" ht="72" customHeight="1">
+      <x:c r="A86" s="79" t="str">
+        <x:f>'任务与甘特'!A18</x:f>
+        <x:v>T3.4</x:v>
+      </x:c>
+      <x:c r="B86" s="79" t="str">
+        <x:f>'任务与甘特'!B18</x:f>
+        <x:v>实现企业资料与备案审批</x:v>
+      </x:c>
+      <x:c r="C86" s="79"/>
+      <x:c r="D86" s="79"/>
+      <x:c r="E86" s="79" t="str">
+        <x:f>'任务与甘特'!R18</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F86" s="79"/>
+      <x:c r="G86" s="79" t="str">
+        <x:f>IF($E86="R01","A/R",IF(ISNUMBER('任务与甘特'!Y18),IF('任务与甘特'!Y18&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H86" s="79" t="str">
+        <x:f>IF($E86="R02","A/R",IF(ISNUMBER('任务与甘特'!Z18),IF('任务与甘特'!Z18&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I86" s="79" t="str">
+        <x:f>IF($E86="R03","A/R",IF(ISNUMBER('任务与甘特'!AA18),IF('任务与甘特'!AA18&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J86" s="79" t="str">
+        <x:f>IF($E86="R04","A/R",IF(ISNUMBER('任务与甘特'!AB18),IF('任务与甘特'!AB18&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K86" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L86" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M86" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N86" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O86" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P86" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q86" s="79" t="str">
+        <x:f>'任务与甘特'!P18</x:f>
+        <x:v>资料草稿、变更备案与版本查询</x:v>
+      </x:c>
+      <x:c r="R86" s="79"/>
+      <x:c r="S86" s="79"/>
+    </x:row>
+    <x:row r="87" ht="72" customHeight="1">
+      <x:c r="A87" s="79" t="str">
+        <x:f>'任务与甘特'!A19</x:f>
+        <x:v>T3.5</x:v>
+      </x:c>
+      <x:c r="B87" s="79" t="str">
+        <x:f>'任务与甘特'!B19</x:f>
+        <x:v>实现月报草稿、校验与提交</x:v>
+      </x:c>
+      <x:c r="C87" s="79"/>
+      <x:c r="D87" s="79"/>
+      <x:c r="E87" s="79" t="str">
+        <x:f>'任务与甘特'!R19</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F87" s="79"/>
+      <x:c r="G87" s="79" t="str">
+        <x:f>IF($E87="R01","A/R",IF(ISNUMBER('任务与甘特'!Y19),IF('任务与甘特'!Y19&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H87" s="79" t="str">
+        <x:f>IF($E87="R02","A/R",IF(ISNUMBER('任务与甘特'!Z19),IF('任务与甘特'!Z19&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I87" s="79" t="str">
+        <x:f>IF($E87="R03","A/R",IF(ISNUMBER('任务与甘特'!AA19),IF('任务与甘特'!AA19&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J87" s="79" t="str">
+        <x:f>IF($E87="R04","A/R",IF(ISNUMBER('任务与甘特'!AB19),IF('任务与甘特'!AB19&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K87" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L87" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M87" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N87" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O87" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P87" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q87" s="79" t="str">
+        <x:f>'任务与甘特'!P19</x:f>
+        <x:v>月报、幂等提交与冻结快照</x:v>
+      </x:c>
+      <x:c r="R87" s="79"/>
+      <x:c r="S87" s="79"/>
+    </x:row>
+    <x:row r="88" ht="72" customHeight="1">
+      <x:c r="A88" s="79" t="str">
+        <x:f>'任务与甘特'!A20</x:f>
+        <x:v>T3.6</x:v>
+      </x:c>
+      <x:c r="B88" s="79" t="str">
+        <x:f>'任务与甘特'!B20</x:f>
+        <x:v>实现市省审核与退回重提</x:v>
+      </x:c>
+      <x:c r="C88" s="79"/>
+      <x:c r="D88" s="79"/>
+      <x:c r="E88" s="79" t="str">
+        <x:f>'任务与甘特'!R20</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F88" s="79"/>
+      <x:c r="G88" s="79" t="str">
+        <x:f>IF($E88="R01","A/R",IF(ISNUMBER('任务与甘特'!Y20),IF('任务与甘特'!Y20&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H88" s="79" t="str">
+        <x:f>IF($E88="R02","A/R",IF(ISNUMBER('任务与甘特'!Z20),IF('任务与甘特'!Z20&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I88" s="79" t="str">
+        <x:f>IF($E88="R03","A/R",IF(ISNUMBER('任务与甘特'!AA20),IF('任务与甘特'!AA20&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J88" s="79" t="str">
+        <x:f>IF($E88="R04","A/R",IF(ISNUMBER('任务与甘特'!AB20),IF('任务与甘特'!AB20&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K88" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L88" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M88" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N88" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O88" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P88" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q88" s="79" t="str">
+        <x:f>'任务与甘特'!P20</x:f>
+        <x:v>审核状态链、退回重提与审计</x:v>
+      </x:c>
+      <x:c r="R88" s="79"/>
+      <x:c r="S88" s="79"/>
+    </x:row>
+    <x:row r="89" ht="72" customHeight="1">
+      <x:c r="A89" s="79" t="str">
+        <x:f>'任务与甘特'!A21</x:f>
+        <x:v>T3.7</x:v>
+      </x:c>
+      <x:c r="B89" s="79" t="str">
+        <x:f>'任务与甘特'!B21</x:f>
+        <x:v>实现调查期与补报授权</x:v>
+      </x:c>
+      <x:c r="C89" s="79"/>
+      <x:c r="D89" s="79"/>
+      <x:c r="E89" s="79" t="str">
+        <x:f>'任务与甘特'!R21</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F89" s="79"/>
+      <x:c r="G89" s="79" t="str">
+        <x:f>IF($E89="R01","A/R",IF(ISNUMBER('任务与甘特'!Y21),IF('任务与甘特'!Y21&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H89" s="79" t="str">
+        <x:f>IF($E89="R02","A/R",IF(ISNUMBER('任务与甘特'!Z21),IF('任务与甘特'!Z21&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I89" s="79" t="str">
+        <x:f>IF($E89="R03","A/R",IF(ISNUMBER('任务与甘特'!AA21),IF('任务与甘特'!AA21&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J89" s="79" t="str">
+        <x:f>IF($E89="R04","A/R",IF(ISNUMBER('任务与甘特'!AB21),IF('任务与甘特'!AB21&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K89" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L89" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M89" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N89" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O89" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P89" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q89" s="79" t="str">
+        <x:f>'任务与甘特'!P21</x:f>
+        <x:v>调查期配置与补报窗口控制</x:v>
+      </x:c>
+      <x:c r="R89" s="79"/>
+      <x:c r="S89" s="79"/>
+    </x:row>
+    <x:row r="90" ht="72" customHeight="1">
+      <x:c r="A90" s="79" t="str">
+        <x:f>'任务与甘特'!A22</x:f>
+        <x:v>T3.8</x:v>
+      </x:c>
+      <x:c r="B90" s="79" t="str">
+        <x:f>'任务与甘特'!B22</x:f>
+        <x:v>实现独立修订与撤销链</x:v>
+      </x:c>
+      <x:c r="C90" s="79"/>
+      <x:c r="D90" s="79"/>
+      <x:c r="E90" s="79" t="str">
+        <x:f>'任务与甘特'!R22</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F90" s="79"/>
+      <x:c r="G90" s="79" t="str">
+        <x:f>IF($E90="R01","A/R",IF(ISNUMBER('任务与甘特'!Y22),IF('任务与甘特'!Y22&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H90" s="79" t="str">
+        <x:f>IF($E90="R02","A/R",IF(ISNUMBER('任务与甘特'!Z22),IF('任务与甘特'!Z22&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I90" s="79" t="str">
+        <x:f>IF($E90="R03","A/R",IF(ISNUMBER('任务与甘特'!AA22),IF('任务与甘特'!AA22&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J90" s="79" t="str">
+        <x:f>IF($E90="R04","A/R",IF(ISNUMBER('任务与甘特'!AB22),IF('任务与甘特'!AB22&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K90" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L90" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M90" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N90" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O90" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P90" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q90" s="79" t="str">
+        <x:f>'任务与甘特'!P22</x:f>
+        <x:v>修订另存、生效、撤销与日志</x:v>
+      </x:c>
+      <x:c r="R90" s="79"/>
+      <x:c r="S90" s="79"/>
+    </x:row>
+    <x:row r="91" ht="72" customHeight="1">
+      <x:c r="A91" s="79" t="str">
+        <x:f>'任务与甘特'!A23</x:f>
+        <x:v>T3.9</x:v>
+      </x:c>
+      <x:c r="B91" s="79" t="str">
+        <x:f>'任务与甘特'!B23</x:f>
+        <x:v>实现历史浏览和快照查询</x:v>
+      </x:c>
+      <x:c r="C91" s="79"/>
+      <x:c r="D91" s="79"/>
+      <x:c r="E91" s="79" t="str">
+        <x:f>'任务与甘特'!R23</x:f>
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="F91" s="79"/>
+      <x:c r="G91" s="79" t="str">
+        <x:f>IF($E91="R01","A/R",IF(ISNUMBER('任务与甘特'!Y23),IF('任务与甘特'!Y23&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H91" s="79" t="str">
+        <x:f>IF($E91="R02","A/R",IF(ISNUMBER('任务与甘特'!Z23),IF('任务与甘特'!Z23&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I91" s="79" t="str">
+        <x:f>IF($E91="R03","A/R",IF(ISNUMBER('任务与甘特'!AA23),IF('任务与甘特'!AA23&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="J91" s="79" t="str">
+        <x:f>IF($E91="R04","A/R",IF(ISNUMBER('任务与甘特'!AB23),IF('任务与甘特'!AB23&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K91" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L91" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M91" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N91" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O91" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P91" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q91" s="79" t="str">
+        <x:f>'任务与甘特'!P23</x:f>
+        <x:v>历史版本与正式提交标记查询</x:v>
+      </x:c>
+      <x:c r="R91" s="79"/>
+      <x:c r="S91" s="79"/>
+    </x:row>
+    <x:row r="92" ht="72" customHeight="1">
+      <x:c r="A92" s="79" t="str">
+        <x:f>'任务与甘特'!A24</x:f>
+        <x:v>T3.10</x:v>
+      </x:c>
+      <x:c r="B92" s="79" t="str">
+        <x:f>'任务与甘特'!B24</x:f>
+        <x:v>实现汇总指标与统计口径</x:v>
+      </x:c>
+      <x:c r="C92" s="79"/>
+      <x:c r="D92" s="79"/>
+      <x:c r="E92" s="79" t="str">
+        <x:f>'任务与甘特'!R24</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F92" s="79"/>
+      <x:c r="G92" s="79" t="str">
+        <x:f>IF($E92="R01","A/R",IF(ISNUMBER('任务与甘特'!Y24),IF('任务与甘特'!Y24&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H92" s="79" t="str">
+        <x:f>IF($E92="R02","A/R",IF(ISNUMBER('任务与甘特'!Z24),IF('任务与甘特'!Z24&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I92" s="79" t="str">
+        <x:f>IF($E92="R03","A/R",IF(ISNUMBER('任务与甘特'!AA24),IF('任务与甘特'!AA24&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J92" s="79" t="str">
+        <x:f>IF($E92="R04","A/R",IF(ISNUMBER('任务与甘特'!AB24),IF('任务与甘特'!AB24&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K92" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L92" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M92" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N92" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O92" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P92" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q92" s="79" t="str">
+        <x:f>'任务与甘特'!P24</x:f>
+        <x:v>原始/修订口径汇总与公式复算</x:v>
+      </x:c>
+      <x:c r="R92" s="79"/>
+      <x:c r="S92" s="79"/>
+    </x:row>
+    <x:row r="93" ht="72" customHeight="1">
+      <x:c r="A93" s="79" t="str">
+        <x:f>'任务与甘特'!A25</x:f>
+        <x:v>T3.11</x:v>
+      </x:c>
+      <x:c r="B93" s="79" t="str">
+        <x:f>'任务与甘特'!B25</x:f>
+        <x:v>实现条件查询与XLSX导出</x:v>
+      </x:c>
+      <x:c r="C93" s="79"/>
+      <x:c r="D93" s="79"/>
+      <x:c r="E93" s="79" t="str">
+        <x:f>'任务与甘特'!R25</x:f>
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="F93" s="79"/>
+      <x:c r="G93" s="79" t="str">
+        <x:f>IF($E93="R01","A/R",IF(ISNUMBER('任务与甘特'!Y25),IF('任务与甘特'!Y25&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H93" s="79" t="str">
+        <x:f>IF($E93="R02","A/R",IF(ISNUMBER('任务与甘特'!Z25),IF('任务与甘特'!Z25&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I93" s="79" t="str">
+        <x:f>IF($E93="R03","A/R",IF(ISNUMBER('任务与甘特'!AA25),IF('任务与甘特'!AA25&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="J93" s="79" t="str">
+        <x:f>IF($E93="R04","A/R",IF(ISNUMBER('任务与甘特'!AB25),IF('任务与甘特'!AB25&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K93" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L93" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M93" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N93" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O93" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P93" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q93" s="79" t="str">
+        <x:f>'任务与甘特'!P25</x:f>
+        <x:v>13条件查询、异步导出与鉴权下载</x:v>
+      </x:c>
+      <x:c r="R93" s="79"/>
+      <x:c r="S93" s="79"/>
+    </x:row>
+    <x:row r="94" ht="72" customHeight="1">
+      <x:c r="A94" s="79" t="str">
+        <x:f>'任务与甘特'!A26</x:f>
+        <x:v>T3.12</x:v>
+      </x:c>
+      <x:c r="B94" s="79" t="str">
+        <x:f>'任务与甘特'!B26</x:f>
+        <x:v>实现各市取样与地区筛选</x:v>
+      </x:c>
+      <x:c r="C94" s="79"/>
+      <x:c r="D94" s="79"/>
+      <x:c r="E94" s="79" t="str">
+        <x:f>'任务与甘特'!R26</x:f>
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="F94" s="79"/>
+      <x:c r="G94" s="79" t="str">
+        <x:f>IF($E94="R01","A/R",IF(ISNUMBER('任务与甘特'!Y26),IF('任务与甘特'!Y26&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H94" s="79" t="str">
+        <x:f>IF($E94="R02","A/R",IF(ISNUMBER('任务与甘特'!Z26),IF('任务与甘特'!Z26&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I94" s="79" t="str">
+        <x:f>IF($E94="R03","A/R",IF(ISNUMBER('任务与甘特'!AA26),IF('任务与甘特'!AA26&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="J94" s="79" t="str">
+        <x:f>IF($E94="R04","A/R",IF(ISNUMBER('任务与甘特'!AB26),IF('任务与甘特'!AB26&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K94" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L94" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M94" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N94" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O94" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P94" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q94" s="79" t="str">
+        <x:f>'任务与甘特'!P26</x:f>
+        <x:v>备案/有效上报取样与同源图表</x:v>
+      </x:c>
+      <x:c r="R94" s="79"/>
+      <x:c r="S94" s="79"/>
+    </x:row>
+    <x:row r="95" ht="72" customHeight="1">
+      <x:c r="A95" s="79" t="str">
+        <x:f>'任务与甘特'!A27</x:f>
+        <x:v>T3.13</x:v>
+      </x:c>
+      <x:c r="B95" s="79" t="str">
+        <x:f>'任务与甘特'!B27</x:f>
+        <x:v>实现两期比较与连续期趋势</x:v>
+      </x:c>
+      <x:c r="C95" s="79"/>
+      <x:c r="D95" s="79"/>
+      <x:c r="E95" s="79" t="str">
+        <x:f>'任务与甘特'!R27</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F95" s="79"/>
+      <x:c r="G95" s="79" t="str">
+        <x:f>IF($E95="R01","A/R",IF(ISNUMBER('任务与甘特'!Y27),IF('任务与甘特'!Y27&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H95" s="79" t="str">
+        <x:f>IF($E95="R02","A/R",IF(ISNUMBER('任务与甘特'!Z27),IF('任务与甘特'!Z27&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I95" s="79" t="str">
+        <x:f>IF($E95="R03","A/R",IF(ISNUMBER('任务与甘特'!AA27),IF('任务与甘特'!AA27&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J95" s="79" t="str">
+        <x:f>IF($E95="R04","A/R",IF(ISNUMBER('任务与甘特'!AB27),IF('任务与甘特'!AB27&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K95" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L95" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M95" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N95" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O95" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P95" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q95" s="79" t="str">
+        <x:f>'任务与甘特'!P27</x:f>
+        <x:v>样本比较、趋势和缺失语义</x:v>
+      </x:c>
+      <x:c r="R95" s="79"/>
+      <x:c r="S95" s="79"/>
+    </x:row>
+    <x:row r="96" ht="72" customHeight="1">
+      <x:c r="A96" s="79" t="str">
+        <x:f>'任务与甘特'!A28</x:f>
+        <x:v>T3.14</x:v>
+      </x:c>
+      <x:c r="B96" s="79" t="str">
+        <x:f>'任务与甘特'!B28</x:f>
+        <x:v>实现通知与用户管理界面</x:v>
+      </x:c>
+      <x:c r="C96" s="79"/>
+      <x:c r="D96" s="79"/>
+      <x:c r="E96" s="79" t="str">
+        <x:f>'任务与甘特'!R28</x:f>
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="F96" s="79"/>
+      <x:c r="G96" s="79" t="str">
+        <x:f>IF($E96="R01","A/R",IF(ISNUMBER('任务与甘特'!Y28),IF('任务与甘特'!Y28&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H96" s="79" t="str">
+        <x:f>IF($E96="R02","A/R",IF(ISNUMBER('任务与甘特'!Z28),IF('任务与甘特'!Z28&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I96" s="79" t="str">
+        <x:f>IF($E96="R03","A/R",IF(ISNUMBER('任务与甘特'!AA28),IF('任务与甘特'!AA28&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="J96" s="79" t="str">
+        <x:f>IF($E96="R04","A/R",IF(ISNUMBER('任务与甘特'!AB28),IF('任务与甘特'!AB28&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K96" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L96" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M96" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N96" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O96" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P96" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q96" s="79" t="str">
+        <x:f>'任务与甘特'!P28</x:f>
+        <x:v>通知可见范围与用户角色管理</x:v>
+      </x:c>
+      <x:c r="R96" s="79"/>
+      <x:c r="S96" s="79"/>
+    </x:row>
+    <x:row r="97" ht="72" customHeight="1">
+      <x:c r="A97" s="79" t="str">
+        <x:f>'任务与甘特'!A29</x:f>
+        <x:v>T3.15</x:v>
+      </x:c>
+      <x:c r="B97" s="79" t="str">
+        <x:f>'任务与甘特'!B29</x:f>
+        <x:v>实现删除恢复、脱敏与审计</x:v>
+      </x:c>
+      <x:c r="C97" s="79"/>
+      <x:c r="D97" s="79"/>
+      <x:c r="E97" s="79" t="str">
+        <x:f>'任务与甘特'!R29</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F97" s="79"/>
+      <x:c r="G97" s="79" t="str">
+        <x:f>IF($E97="R01","A/R",IF(ISNUMBER('任务与甘特'!Y29),IF('任务与甘特'!Y29&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H97" s="79" t="str">
+        <x:f>IF($E97="R02","A/R",IF(ISNUMBER('任务与甘特'!Z29),IF('任务与甘特'!Z29&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I97" s="79" t="str">
+        <x:f>IF($E97="R03","A/R",IF(ISNUMBER('任务与甘特'!AA29),IF('任务与甘特'!AA29&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J97" s="79" t="str">
+        <x:f>IF($E97="R04","A/R",IF(ISNUMBER('任务与甘特'!AB29),IF('任务与甘特'!AB29&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K97" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L97" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M97" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N97" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O97" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P97" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q97" s="79" t="str">
+        <x:f>'任务与甘特'!P29</x:f>
+        <x:v>删除恢复、保留计时与事件链</x:v>
+      </x:c>
+      <x:c r="R97" s="79"/>
+      <x:c r="S97" s="79"/>
+    </x:row>
+    <x:row r="98" ht="72" customHeight="1">
+      <x:c r="A98" s="79" t="str">
+        <x:f>'任务与甘特'!A30</x:f>
+        <x:v>T3.16</x:v>
+      </x:c>
+      <x:c r="B98" s="79" t="str">
+        <x:f>'任务与甘特'!B30</x:f>
+        <x:v>实现运行监控与指标采集</x:v>
+      </x:c>
+      <x:c r="C98" s="79"/>
+      <x:c r="D98" s="79"/>
+      <x:c r="E98" s="79" t="str">
+        <x:f>'任务与甘特'!R30</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F98" s="79"/>
+      <x:c r="G98" s="79" t="str">
+        <x:f>IF($E98="R01","A/R",IF(ISNUMBER('任务与甘特'!Y30),IF('任务与甘特'!Y30&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H98" s="79" t="str">
+        <x:f>IF($E98="R02","A/R",IF(ISNUMBER('任务与甘特'!Z30),IF('任务与甘特'!Z30&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I98" s="79" t="str">
+        <x:f>IF($E98="R03","A/R",IF(ISNUMBER('任务与甘特'!AA30),IF('任务与甘特'!AA30&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J98" s="79" t="str">
+        <x:f>IF($E98="R04","A/R",IF(ISNUMBER('任务与甘特'!AB30),IF('任务与甘特'!AB30&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K98" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="L98" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="M98" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N98" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O98" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P98" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q98" s="79" t="str">
+        <x:f>'任务与甘特'!P30</x:f>
+        <x:v>宿主机指标、服务状态与过期标识</x:v>
+      </x:c>
+      <x:c r="R98" s="79"/>
+      <x:c r="S98" s="79"/>
+    </x:row>
+    <x:row r="99" ht="72" customHeight="1">
+      <x:c r="A99" s="79" t="str">
+        <x:f>'任务与甘特'!A31</x:f>
+        <x:v>T3.17</x:v>
+      </x:c>
+      <x:c r="B99" s="79" t="str">
+        <x:f>'任务与甘特'!B31</x:f>
+        <x:v>实现批次冻结与MOCK交换</x:v>
+      </x:c>
+      <x:c r="C99" s="79"/>
+      <x:c r="D99" s="79"/>
+      <x:c r="E99" s="79" t="str">
+        <x:f>'任务与甘特'!R31</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F99" s="79"/>
+      <x:c r="G99" s="79" t="str">
+        <x:f>IF($E99="R01","A/R",IF(ISNUMBER('任务与甘特'!Y31),IF('任务与甘特'!Y31&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H99" s="79" t="str">
+        <x:f>IF($E99="R02","A/R",IF(ISNUMBER('任务与甘特'!Z31),IF('任务与甘特'!Z31&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I99" s="79" t="str">
+        <x:f>IF($E99="R03","A/R",IF(ISNUMBER('任务与甘特'!AA31),IF('任务与甘特'!AA31&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J99" s="79" t="str">
+        <x:f>IF($E99="R04","A/R",IF(ISNUMBER('任务与甘特'!AB31),IF('任务与甘特'!AB31&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K99" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L99" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M99" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N99" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O99" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P99" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q99" s="79" t="str">
+        <x:f>'任务与甘特'!P31</x:f>
+        <x:v>批次、摘要、MOCK回执与恢复</x:v>
+      </x:c>
+      <x:c r="R99" s="79"/>
+      <x:c r="S99" s="79"/>
+    </x:row>
+    <x:row r="100" ht="72" customHeight="1">
+      <x:c r="A100" s="79" t="str">
+        <x:f>'任务与甘特'!A32</x:f>
+        <x:v>T3.18</x:v>
+      </x:c>
+      <x:c r="B100" s="79" t="str">
+        <x:f>'任务与甘特'!B32</x:f>
+        <x:v>实现实际REAL协议适配</x:v>
+      </x:c>
+      <x:c r="C100" s="79"/>
+      <x:c r="D100" s="79"/>
+      <x:c r="E100" s="79" t="str">
+        <x:f>'任务与甘特'!R32</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F100" s="79"/>
+      <x:c r="G100" s="79" t="str">
+        <x:f>IF($E100="R01","A/R",IF(ISNUMBER('任务与甘特'!Y32),IF('任务与甘特'!Y32&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H100" s="79" t="str">
+        <x:f>IF($E100="R02","A/R",IF(ISNUMBER('任务与甘特'!Z32),IF('任务与甘特'!Z32&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I100" s="79" t="str">
+        <x:f>IF($E100="R03","A/R",IF(ISNUMBER('任务与甘特'!AA32),IF('任务与甘特'!AA32&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J100" s="79" t="str">
+        <x:f>IF($E100="R04","A/R",IF(ISNUMBER('任务与甘特'!AB32),IF('任务与甘特'!AB32&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K100" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L100" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M100" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N100" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O100" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P100" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q100" s="79" t="str">
+        <x:f>'任务与甘特'!P32</x:f>
+        <x:v>实际认证、字段映射与传输适配</x:v>
+      </x:c>
+      <x:c r="R100" s="79"/>
+      <x:c r="S100" s="79"/>
+    </x:row>
+    <x:row r="101" ht="72" customHeight="1">
+      <x:c r="A101" s="79" t="str">
+        <x:f>'任务与甘特'!A33</x:f>
+        <x:v>T3.19</x:v>
+      </x:c>
+      <x:c r="B101" s="79" t="str">
+        <x:f>'任务与甘特'!B33</x:f>
+        <x:v>编写配置、部署、备份与回滚</x:v>
+      </x:c>
+      <x:c r="C101" s="79"/>
+      <x:c r="D101" s="79"/>
+      <x:c r="E101" s="79" t="str">
+        <x:f>'任务与甘特'!R33</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F101" s="79"/>
+      <x:c r="G101" s="79" t="str">
+        <x:f>IF($E101="R01","A/R",IF(ISNUMBER('任务与甘特'!Y33),IF('任务与甘特'!Y33&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H101" s="79" t="str">
+        <x:f>IF($E101="R02","A/R",IF(ISNUMBER('任务与甘特'!Z33),IF('任务与甘特'!Z33&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I101" s="79" t="str">
+        <x:f>IF($E101="R03","A/R",IF(ISNUMBER('任务与甘特'!AA33),IF('任务与甘特'!AA33&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J101" s="79" t="str">
+        <x:f>IF($E101="R04","A/R",IF(ISNUMBER('任务与甘特'!AB33),IF('任务与甘特'!AB33&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K101" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="L101" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="M101" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="N101" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="O101" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="P101" s="79" t="str">
+        <x:v>小批量提交与集成；非作者复核代码/配置并验证相关失败及边界场景。</x:v>
+      </x:c>
+      <x:c r="Q101" s="79" t="str">
+        <x:f>'任务与甘特'!P33</x:f>
+        <x:v>运行脚本、备份恢复与配置说明</x:v>
+      </x:c>
+      <x:c r="R101" s="79"/>
+      <x:c r="S101" s="79"/>
+    </x:row>
+    <x:row r="102" ht="72" customHeight="1">
+      <x:c r="A102" s="79" t="str">
+        <x:f>'任务与甘特'!A34</x:f>
+        <x:v>T4.1</x:v>
+      </x:c>
+      <x:c r="B102" s="79" t="str">
+        <x:f>'任务与甘特'!B34</x:f>
+        <x:v>评审主业务链阶段成果</x:v>
+      </x:c>
+      <x:c r="C102" s="79"/>
+      <x:c r="D102" s="79"/>
+      <x:c r="E102" s="79" t="str">
+        <x:f>'任务与甘特'!R34</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F102" s="79"/>
+      <x:c r="G102" s="79" t="str">
+        <x:f>IF($E102="R01","A/R",IF(ISNUMBER('任务与甘特'!Y34),IF('任务与甘特'!Y34&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H102" s="79" t="str">
+        <x:f>IF($E102="R02","A/R",IF(ISNUMBER('任务与甘特'!Z34),IF('任务与甘特'!Z34&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I102" s="79" t="str">
+        <x:f>IF($E102="R03","A/R",IF(ISNUMBER('任务与甘特'!AA34),IF('任务与甘特'!AA34&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J102" s="79" t="str">
+        <x:f>IF($E102="R04","A/R",IF(ISNUMBER('任务与甘特'!AB34),IF('任务与甘特'!AB34&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K102" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L102" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M102" s="79" t="str">
+        <x:v>对照AC演示、检查集成契约和遗留问题；结果不符则登记处置。</x:v>
+      </x:c>
+      <x:c r="N102" s="79" t="str">
+        <x:v>对照AC演示、检查集成契约和遗留问题；结果不符则登记处置。</x:v>
+      </x:c>
+      <x:c r="O102" s="79" t="str">
+        <x:v>对照AC演示、检查集成契约和遗留问题；结果不符则登记处置。</x:v>
+      </x:c>
+      <x:c r="P102" s="79" t="str">
+        <x:v>对照AC演示、检查集成契约和遗留问题；结果不符则登记处置。</x:v>
+      </x:c>
+      <x:c r="Q102" s="79" t="str">
+        <x:f>'任务与甘特'!P34</x:f>
+        <x:v>主业务链阶段评审记录</x:v>
+      </x:c>
+      <x:c r="R102" s="79"/>
+      <x:c r="S102" s="79"/>
+    </x:row>
+    <x:row r="103" ht="72" customHeight="1">
+      <x:c r="A103" s="79" t="str">
+        <x:f>'任务与甘特'!A35</x:f>
+        <x:v>T4.2</x:v>
+      </x:c>
+      <x:c r="B103" s="79" t="str">
+        <x:f>'任务与甘特'!B35</x:f>
+        <x:v>完成本地模块集成</x:v>
+      </x:c>
+      <x:c r="C103" s="79"/>
+      <x:c r="D103" s="79"/>
+      <x:c r="E103" s="79" t="str">
+        <x:f>'任务与甘特'!R35</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F103" s="79"/>
+      <x:c r="G103" s="79" t="str">
+        <x:f>IF($E103="R01","A/R",IF(ISNUMBER('任务与甘特'!Y35),IF('任务与甘特'!Y35&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H103" s="79" t="str">
+        <x:f>IF($E103="R02","A/R",IF(ISNUMBER('任务与甘特'!Z35),IF('任务与甘特'!Z35&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I103" s="79" t="str">
+        <x:f>IF($E103="R03","A/R",IF(ISNUMBER('任务与甘特'!AA35),IF('任务与甘特'!AA35&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J103" s="79" t="str">
+        <x:f>IF($E103="R04","A/R",IF(ISNUMBER('任务与甘特'!AB35),IF('任务与甘特'!AB35&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K103" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L103" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M103" s="79" t="str">
+        <x:v>对照AC演示、检查集成契约和遗留问题；结果不符则登记处置。</x:v>
+      </x:c>
+      <x:c r="N103" s="79" t="str">
+        <x:v>对照AC演示、检查集成契约和遗留问题；结果不符则登记处置。</x:v>
+      </x:c>
+      <x:c r="O103" s="79" t="str">
+        <x:v>对照AC演示、检查集成契约和遗留问题；结果不符则登记处置。</x:v>
+      </x:c>
+      <x:c r="P103" s="79" t="str">
+        <x:v>对照AC演示、检查集成契约和遗留问题；结果不符则登记处置。</x:v>
+      </x:c>
+      <x:c r="Q103" s="79" t="str">
+        <x:f>'任务与甘特'!P35</x:f>
+        <x:v>可构建本地集成版本</x:v>
+      </x:c>
+      <x:c r="R103" s="79"/>
+      <x:c r="S103" s="79"/>
+    </x:row>
+    <x:row r="104" ht="72" customHeight="1">
+      <x:c r="A104" s="79" t="str">
+        <x:f>'任务与甘特'!A36</x:f>
+        <x:v>T4.3</x:v>
+      </x:c>
+      <x:c r="B104" s="79" t="str">
+        <x:f>'任务与甘特'!B36</x:f>
+        <x:v>执行业务功能与边界测试</x:v>
+      </x:c>
+      <x:c r="C104" s="79"/>
+      <x:c r="D104" s="79"/>
+      <x:c r="E104" s="79" t="str">
+        <x:f>'任务与甘特'!R36</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F104" s="79"/>
+      <x:c r="G104" s="79" t="str">
+        <x:f>IF($E104="R01","A/R",IF(ISNUMBER('任务与甘特'!Y36),IF('任务与甘特'!Y36&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H104" s="79" t="str">
+        <x:f>IF($E104="R02","A/R",IF(ISNUMBER('任务与甘特'!Z36),IF('任务与甘特'!Z36&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I104" s="79" t="str">
+        <x:f>IF($E104="R03","A/R",IF(ISNUMBER('任务与甘特'!AA36),IF('任务与甘特'!AA36&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J104" s="79" t="str">
+        <x:f>IF($E104="R04","A/R",IF(ISNUMBER('任务与甘特'!AB36),IF('任务与甘特'!AB36&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K104" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="L104" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="M104" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="N104" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="O104" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="P104" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="Q104" s="79" t="str">
+        <x:f>'任务与甘特'!P36</x:f>
+        <x:v>AC-01～09结果与缺陷记录</x:v>
+      </x:c>
+      <x:c r="R104" s="79"/>
+      <x:c r="S104" s="79"/>
+    </x:row>
+    <x:row r="105" ht="72" customHeight="1">
+      <x:c r="A105" s="79" t="str">
+        <x:f>'任务与甘特'!A37</x:f>
+        <x:v>T4.4</x:v>
+      </x:c>
+      <x:c r="B105" s="79" t="str">
+        <x:f>'任务与甘特'!B37</x:f>
+        <x:v>验证MOCK回执与黄金摘要</x:v>
+      </x:c>
+      <x:c r="C105" s="79"/>
+      <x:c r="D105" s="79"/>
+      <x:c r="E105" s="79" t="str">
+        <x:f>'任务与甘特'!R37</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F105" s="79"/>
+      <x:c r="G105" s="79" t="str">
+        <x:f>IF($E105="R01","A/R",IF(ISNUMBER('任务与甘特'!Y37),IF('任务与甘特'!Y37&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H105" s="79" t="str">
+        <x:f>IF($E105="R02","A/R",IF(ISNUMBER('任务与甘特'!Z37),IF('任务与甘特'!Z37&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I105" s="79" t="str">
+        <x:f>IF($E105="R03","A/R",IF(ISNUMBER('任务与甘特'!AA37),IF('任务与甘特'!AA37&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J105" s="79" t="str">
+        <x:f>IF($E105="R04","A/R",IF(ISNUMBER('任务与甘特'!AB37),IF('任务与甘特'!AB37&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K105" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="L105" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="M105" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="N105" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="O105" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="P105" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="Q105" s="79" t="str">
+        <x:f>'任务与甘特'!P37</x:f>
+        <x:v>跨语言摘要、回执及异常恢复证据</x:v>
+      </x:c>
+      <x:c r="R105" s="79"/>
+      <x:c r="S105" s="79"/>
+    </x:row>
+    <x:row r="106" ht="72" customHeight="1">
+      <x:c r="A106" s="79" t="str">
+        <x:f>'任务与甘特'!A38</x:f>
+        <x:v>T4.5</x:v>
+      </x:c>
+      <x:c r="B106" s="79" t="str">
+        <x:f>'任务与甘特'!B38</x:f>
+        <x:v>完成实际国家交换验证</x:v>
+      </x:c>
+      <x:c r="C106" s="79"/>
+      <x:c r="D106" s="79"/>
+      <x:c r="E106" s="79" t="str">
+        <x:f>'任务与甘特'!R38</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F106" s="79"/>
+      <x:c r="G106" s="79" t="str">
+        <x:f>IF($E106="R01","A/R",IF(ISNUMBER('任务与甘特'!Y38),IF('任务与甘特'!Y38&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H106" s="79" t="str">
+        <x:f>IF($E106="R02","A/R",IF(ISNUMBER('任务与甘特'!Z38),IF('任务与甘特'!Z38&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I106" s="79" t="str">
+        <x:f>IF($E106="R03","A/R",IF(ISNUMBER('任务与甘特'!AA38),IF('任务与甘特'!AA38&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J106" s="79" t="str">
+        <x:f>IF($E106="R04","A/R",IF(ISNUMBER('任务与甘特'!AB38),IF('任务与甘特'!AB38&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K106" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="L106" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="M106" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="N106" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="O106" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="P106" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="Q106" s="79" t="str">
+        <x:f>'任务与甘特'!P38</x:f>
+        <x:v>实际接收凭据与AC-10B记录</x:v>
+      </x:c>
+      <x:c r="R106" s="79"/>
+      <x:c r="S106" s="79"/>
+    </x:row>
+    <x:row r="107" ht="72" customHeight="1">
+      <x:c r="A107" s="79" t="str">
+        <x:f>'任务与甘特'!A39</x:f>
+        <x:v>T4.6</x:v>
+      </x:c>
+      <x:c r="B107" s="79" t="str">
+        <x:f>'任务与甘特'!B39</x:f>
+        <x:v>验证安全、认证和并发一致性</x:v>
+      </x:c>
+      <x:c r="C107" s="79"/>
+      <x:c r="D107" s="79"/>
+      <x:c r="E107" s="79" t="str">
+        <x:f>'任务与甘特'!R39</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F107" s="79"/>
+      <x:c r="G107" s="79" t="str">
+        <x:f>IF($E107="R01","A/R",IF(ISNUMBER('任务与甘特'!Y39),IF('任务与甘特'!Y39&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H107" s="79" t="str">
+        <x:f>IF($E107="R02","A/R",IF(ISNUMBER('任务与甘特'!Z39),IF('任务与甘特'!Z39&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I107" s="79" t="str">
+        <x:f>IF($E107="R03","A/R",IF(ISNUMBER('任务与甘特'!AA39),IF('任务与甘特'!AA39&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J107" s="79" t="str">
+        <x:f>IF($E107="R04","A/R",IF(ISNUMBER('任务与甘特'!AB39),IF('任务与甘特'!AB39&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K107" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="L107" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="M107" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="N107" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="O107" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="P107" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="Q107" s="79" t="str">
+        <x:f>'任务与甘特'!P39</x:f>
+        <x:v>越权、漏洞、限流与并发证据</x:v>
+      </x:c>
+      <x:c r="R107" s="79"/>
+      <x:c r="S107" s="79"/>
+    </x:row>
+    <x:row r="108" ht="72" customHeight="1">
+      <x:c r="A108" s="79" t="str">
+        <x:f>'任务与甘特'!A40</x:f>
+        <x:v>T4.7</x:v>
+      </x:c>
+      <x:c r="B108" s="79" t="str">
+        <x:f>'任务与甘特'!B40</x:f>
+        <x:v>执行容量、性能与导出测试</x:v>
+      </x:c>
+      <x:c r="C108" s="79"/>
+      <x:c r="D108" s="79"/>
+      <x:c r="E108" s="79" t="str">
+        <x:f>'任务与甘特'!R40</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F108" s="79"/>
+      <x:c r="G108" s="79" t="str">
+        <x:f>IF($E108="R01","A/R",IF(ISNUMBER('任务与甘特'!Y40),IF('任务与甘特'!Y40&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H108" s="79" t="str">
+        <x:f>IF($E108="R02","A/R",IF(ISNUMBER('任务与甘特'!Z40),IF('任务与甘特'!Z40&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I108" s="79" t="str">
+        <x:f>IF($E108="R03","A/R",IF(ISNUMBER('任务与甘特'!AA40),IF('任务与甘特'!AA40&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J108" s="79" t="str">
+        <x:f>IF($E108="R04","A/R",IF(ISNUMBER('任务与甘特'!AB40),IF('任务与甘特'!AB40&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K108" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="L108" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="M108" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="N108" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="O108" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="P108" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="Q108" s="79" t="str">
+        <x:f>'任务与甘特'!P40</x:f>
+        <x:v>负载、P95、成功率和导出报告</x:v>
+      </x:c>
+      <x:c r="R108" s="79"/>
+      <x:c r="S108" s="79"/>
+    </x:row>
+    <x:row r="109" ht="72" customHeight="1">
+      <x:c r="A109" s="79" t="str">
+        <x:f>'任务与甘特'!A41</x:f>
+        <x:v>T4.8</x:v>
+      </x:c>
+      <x:c r="B109" s="79" t="str">
+        <x:f>'任务与甘特'!B41</x:f>
+        <x:v>验证备份恢复与72小时运行</x:v>
+      </x:c>
+      <x:c r="C109" s="79"/>
+      <x:c r="D109" s="79"/>
+      <x:c r="E109" s="79" t="str">
+        <x:f>'任务与甘特'!R41</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F109" s="79"/>
+      <x:c r="G109" s="79" t="str">
+        <x:f>IF($E109="R01","A/R",IF(ISNUMBER('任务与甘特'!Y41),IF('任务与甘特'!Y41&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H109" s="79" t="str">
+        <x:f>IF($E109="R02","A/R",IF(ISNUMBER('任务与甘特'!Z41),IF('任务与甘特'!Z41&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I109" s="79" t="str">
+        <x:f>IF($E109="R03","A/R",IF(ISNUMBER('任务与甘特'!AA41),IF('任务与甘特'!AA41&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J109" s="79" t="str">
+        <x:f>IF($E109="R04","A/R",IF(ISNUMBER('任务与甘特'!AB41),IF('任务与甘特'!AB41&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K109" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="L109" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="M109" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="N109" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="O109" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="P109" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="Q109" s="79" t="str">
+        <x:f>'任务与甘特'!P41</x:f>
+        <x:v>恢复、重启与72小时运行记录</x:v>
+      </x:c>
+      <x:c r="R109" s="79"/>
+      <x:c r="S109" s="79"/>
+    </x:row>
+    <x:row r="110" ht="72" customHeight="1">
+      <x:c r="A110" s="79" t="str">
+        <x:f>'任务与甘特'!A42</x:f>
+        <x:v>T4.9</x:v>
+      </x:c>
+      <x:c r="B110" s="79" t="str">
+        <x:f>'任务与甘特'!B42</x:f>
+        <x:v>验证兼容、部署与监控</x:v>
+      </x:c>
+      <x:c r="C110" s="79"/>
+      <x:c r="D110" s="79"/>
+      <x:c r="E110" s="79" t="str">
+        <x:f>'任务与甘特'!R42</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F110" s="79"/>
+      <x:c r="G110" s="79" t="str">
+        <x:f>IF($E110="R01","A/R",IF(ISNUMBER('任务与甘特'!Y42),IF('任务与甘特'!Y42&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="H110" s="79" t="str">
+        <x:f>IF($E110="R02","A/R",IF(ISNUMBER('任务与甘特'!Z42),IF('任务与甘特'!Z42&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I110" s="79" t="str">
+        <x:f>IF($E110="R03","A/R",IF(ISNUMBER('任务与甘特'!AA42),IF('任务与甘特'!AA42&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J110" s="79" t="str">
+        <x:f>IF($E110="R04","A/R",IF(ISNUMBER('任务与甘特'!AB42),IF('任务与甘特'!AB42&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K110" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="L110" s="79" t="str">
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="M110" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="N110" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="O110" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="P110" s="79" t="str">
+        <x:v>按Q01–Q15对应范围记录环境、版本、预期/实际、失败和可核验证据。</x:v>
+      </x:c>
+      <x:c r="Q110" s="79" t="str">
+        <x:f>'任务与甘特'!P42</x:f>
+        <x:v>浏览器、表格软件和部署证据</x:v>
+      </x:c>
+      <x:c r="R110" s="79"/>
+      <x:c r="S110" s="79"/>
+    </x:row>
+    <x:row r="111" ht="72" customHeight="1">
+      <x:c r="A111" s="79" t="str">
+        <x:f>'任务与甘特'!A43</x:f>
+        <x:v>T4.10</x:v>
+      </x:c>
+      <x:c r="B111" s="79" t="str">
+        <x:f>'任务与甘特'!B43</x:f>
+        <x:v>修复缺陷并复核需求覆盖</x:v>
+      </x:c>
+      <x:c r="C111" s="79"/>
+      <x:c r="D111" s="79"/>
+      <x:c r="E111" s="79" t="str">
+        <x:f>'任务与甘特'!R43</x:f>
+        <x:v>R02</x:v>
+      </x:c>
+      <x:c r="F111" s="79"/>
+      <x:c r="G111" s="79" t="str">
+        <x:f>IF($E111="R01","A/R",IF(ISNUMBER('任务与甘特'!Y43),IF('任务与甘特'!Y43&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H111" s="79" t="str">
+        <x:f>IF($E111="R02","A/R",IF(ISNUMBER('任务与甘特'!Z43),IF('任务与甘特'!Z43&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="I111" s="79" t="str">
+        <x:f>IF($E111="R03","A/R",IF(ISNUMBER('任务与甘特'!AA43),IF('任务与甘特'!AA43&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J111" s="79" t="str">
+        <x:f>IF($E111="R04","A/R",IF(ISNUMBER('任务与甘特'!AB43),IF('任务与甘特'!AB43&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K111" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L111" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M111" s="79" t="str">
+        <x:v>按缺陷号修复、记录根因及版本；非作者复测，失败重开。</x:v>
+      </x:c>
+      <x:c r="N111" s="79" t="str">
+        <x:v>按缺陷号修复、记录根因及版本；非作者复测，失败重开。</x:v>
+      </x:c>
+      <x:c r="O111" s="79" t="str">
+        <x:v>按缺陷号修复、记录根因及版本；非作者复测，失败重开。</x:v>
+      </x:c>
+      <x:c r="P111" s="79" t="str">
+        <x:v>按缺陷号修复、记录根因及版本；非作者复测，失败重开。</x:v>
+      </x:c>
+      <x:c r="Q111" s="79" t="str">
+        <x:f>'任务与甘特'!P43</x:f>
+        <x:v>缺陷修复、回归与未执行项记录</x:v>
+      </x:c>
+      <x:c r="R111" s="79"/>
+      <x:c r="S111" s="79"/>
+    </x:row>
+    <x:row r="112" ht="72" customHeight="1">
+      <x:c r="A112" s="79" t="str">
+        <x:f>'任务与甘特'!A44</x:f>
+        <x:v>T5.1</x:v>
+      </x:c>
+      <x:c r="B112" s="79" t="str">
+        <x:f>'任务与甘特'!B44</x:f>
+        <x:v>部署拟定试运行环境</x:v>
+      </x:c>
+      <x:c r="C112" s="79"/>
+      <x:c r="D112" s="79"/>
+      <x:c r="E112" s="79" t="str">
+        <x:f>'任务与甘特'!R44</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F112" s="79"/>
+      <x:c r="G112" s="79" t="str">
+        <x:f>IF($E112="R01","A/R",IF(ISNUMBER('任务与甘特'!Y44),IF('任务与甘特'!Y44&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H112" s="79" t="str">
+        <x:f>IF($E112="R02","A/R",IF(ISNUMBER('任务与甘特'!Z44),IF('任务与甘特'!Z44&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I112" s="79" t="str">
+        <x:f>IF($E112="R03","A/R",IF(ISNUMBER('任务与甘特'!AA44),IF('任务与甘特'!AA44&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J112" s="79" t="str">
+        <x:f>IF($E112="R04","A/R",IF(ISNUMBER('任务与甘特'!AB44),IF('任务与甘特'!AB44&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K112" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L112" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M112" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="N112" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="O112" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="P112" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="Q112" s="79" t="str">
+        <x:f>'任务与甘特'!P44</x:f>
+        <x:v>部署配置、迁移与回滚记录</x:v>
+      </x:c>
+      <x:c r="R112" s="79"/>
+      <x:c r="S112" s="79"/>
+    </x:row>
+    <x:row r="113" ht="72" customHeight="1">
+      <x:c r="A113" s="79" t="str">
+        <x:f>'任务与甘特'!A45</x:f>
+        <x:v>T5.2</x:v>
+      </x:c>
+      <x:c r="B113" s="79" t="str">
+        <x:f>'任务与甘特'!B45</x:f>
+        <x:v>安排业务试运行与反馈</x:v>
+      </x:c>
+      <x:c r="C113" s="79"/>
+      <x:c r="D113" s="79"/>
+      <x:c r="E113" s="79" t="str">
+        <x:f>'任务与甘特'!R45</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F113" s="79"/>
+      <x:c r="G113" s="79" t="str">
+        <x:f>IF($E113="R01","A/R",IF(ISNUMBER('任务与甘特'!Y45),IF('任务与甘特'!Y45&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H113" s="79" t="str">
+        <x:f>IF($E113="R02","A/R",IF(ISNUMBER('任务与甘特'!Z45),IF('任务与甘特'!Z45&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I113" s="79" t="str">
+        <x:f>IF($E113="R03","A/R",IF(ISNUMBER('任务与甘特'!AA45),IF('任务与甘特'!AA45&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J113" s="79" t="str">
+        <x:f>IF($E113="R04","A/R",IF(ISNUMBER('任务与甘特'!AB45),IF('任务与甘特'!AB45&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K113" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L113" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M113" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="N113" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="O113" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="P113" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="Q113" s="79" t="str">
+        <x:f>'任务与甘特'!P45</x:f>
+        <x:v>试运行记录与反馈处理</x:v>
+      </x:c>
+      <x:c r="R113" s="79"/>
+      <x:c r="S113" s="79"/>
+    </x:row>
+    <x:row r="114" ht="72" customHeight="1">
+      <x:c r="A114" s="79" t="str">
+        <x:f>'任务与甘特'!A46</x:f>
+        <x:v>T5.3</x:v>
+      </x:c>
+      <x:c r="B114" s="79" t="str">
+        <x:f>'任务与甘特'!B46</x:f>
+        <x:v>编写操作与开发维护说明</x:v>
+      </x:c>
+      <x:c r="C114" s="79"/>
+      <x:c r="D114" s="79"/>
+      <x:c r="E114" s="79" t="str">
+        <x:f>'任务与甘特'!R46</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F114" s="79"/>
+      <x:c r="G114" s="79" t="str">
+        <x:f>IF($E114="R01","A/R",IF(ISNUMBER('任务与甘特'!Y46),IF('任务与甘特'!Y46&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H114" s="79" t="str">
+        <x:f>IF($E114="R02","A/R",IF(ISNUMBER('任务与甘特'!Z46),IF('任务与甘特'!Z46&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I114" s="79" t="str">
+        <x:f>IF($E114="R03","A/R",IF(ISNUMBER('任务与甘特'!AA46),IF('任务与甘特'!AA46&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J114" s="79" t="str">
+        <x:f>IF($E114="R04","A/R",IF(ISNUMBER('任务与甘特'!AB46),IF('任务与甘特'!AB46&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K114" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L114" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M114" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="N114" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="O114" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="P114" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="Q114" s="79" t="str">
+        <x:f>'任务与甘特'!P46</x:f>
+        <x:v>企业、市、省和技术管理操作说明</x:v>
+      </x:c>
+      <x:c r="R114" s="79"/>
+      <x:c r="S114" s="79"/>
+    </x:row>
+    <x:row r="115" ht="72" customHeight="1">
+      <x:c r="A115" s="79" t="str">
+        <x:f>'任务与甘特'!A47</x:f>
+        <x:v>T5.4</x:v>
+      </x:c>
+      <x:c r="B115" s="79" t="str">
+        <x:f>'任务与甘特'!B47</x:f>
+        <x:v>安排操作培训与演示</x:v>
+      </x:c>
+      <x:c r="C115" s="79"/>
+      <x:c r="D115" s="79"/>
+      <x:c r="E115" s="79" t="str">
+        <x:f>'任务与甘特'!R47</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F115" s="79"/>
+      <x:c r="G115" s="79" t="str">
+        <x:f>IF($E115="R01","A/R",IF(ISNUMBER('任务与甘特'!Y47),IF('任务与甘特'!Y47&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H115" s="79" t="str">
+        <x:f>IF($E115="R02","A/R",IF(ISNUMBER('任务与甘特'!Z47),IF('任务与甘特'!Z47&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I115" s="79" t="str">
+        <x:f>IF($E115="R03","A/R",IF(ISNUMBER('任务与甘特'!AA47),IF('任务与甘特'!AA47&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J115" s="79" t="str">
+        <x:f>IF($E115="R04","A/R",IF(ISNUMBER('任务与甘特'!AB47),IF('任务与甘特'!AB47&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K115" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L115" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M115" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="N115" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="O115" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="P115" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="Q115" s="79" t="str">
+        <x:f>'任务与甘特'!P47</x:f>
+        <x:v>培训资料、演示与反馈</x:v>
+      </x:c>
+      <x:c r="R115" s="79"/>
+      <x:c r="S115" s="79"/>
+    </x:row>
+    <x:row r="116" ht="72" customHeight="1">
+      <x:c r="A116" s="79" t="str">
+        <x:f>'任务与甘特'!A48</x:f>
+        <x:v>T5.5</x:v>
+      </x:c>
+      <x:c r="B116" s="79" t="str">
+        <x:f>'任务与甘特'!B48</x:f>
+        <x:v>整理代码、配置和验证证据</x:v>
+      </x:c>
+      <x:c r="C116" s="79"/>
+      <x:c r="D116" s="79"/>
+      <x:c r="E116" s="79" t="str">
+        <x:f>'任务与甘特'!R48</x:f>
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="F116" s="79"/>
+      <x:c r="G116" s="79" t="str">
+        <x:f>IF($E116="R01","A/R",IF(ISNUMBER('任务与甘特'!Y48),IF('任务与甘特'!Y48&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H116" s="79" t="str">
+        <x:f>IF($E116="R02","A/R",IF(ISNUMBER('任务与甘特'!Z48),IF('任务与甘特'!Z48&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I116" s="79" t="str">
+        <x:f>IF($E116="R03","A/R",IF(ISNUMBER('任务与甘特'!AA48),IF('任务与甘特'!AA48&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J116" s="79" t="str">
+        <x:f>IF($E116="R04","A/R",IF(ISNUMBER('任务与甘特'!AB48),IF('任务与甘特'!AB48&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="K116" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="L116" s="79" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="M116" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="N116" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="O116" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="P116" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="Q116" s="79" t="str">
+        <x:f>'任务与甘特'!P48</x:f>
+        <x:v>构建代码、运行脚本与证据包</x:v>
+      </x:c>
+      <x:c r="R116" s="79"/>
+      <x:c r="S116" s="79"/>
+    </x:row>
+    <x:row r="117" ht="72" customHeight="1">
+      <x:c r="A117" s="79" t="str">
+        <x:f>'任务与甘特'!A49</x:f>
+        <x:v>T5.6</x:v>
+      </x:c>
+      <x:c r="B117" s="79" t="str">
+        <x:f>'任务与甘特'!B49</x:f>
+        <x:v>完成最终项目验收</x:v>
+      </x:c>
+      <x:c r="C117" s="79"/>
+      <x:c r="D117" s="79"/>
+      <x:c r="E117" s="79" t="str">
+        <x:f>'任务与甘特'!R49</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F117" s="79"/>
+      <x:c r="G117" s="79" t="str">
+        <x:f>IF($E117="R01","A/R",IF(ISNUMBER('任务与甘特'!Y49),IF('任务与甘特'!Y49&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H117" s="79" t="str">
+        <x:f>IF($E117="R02","A/R",IF(ISNUMBER('任务与甘特'!Z49),IF('任务与甘特'!Z49&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="I117" s="79" t="str">
+        <x:f>IF($E117="R03","A/R",IF(ISNUMBER('任务与甘特'!AA49),IF('任务与甘特'!AA49&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="J117" s="79" t="str">
+        <x:f>IF($E117="R04","A/R",IF(ISNUMBER('任务与甘特'!AB49),IF('任务与甘特'!AB49&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K117" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L117" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M117" s="79" t="str">
+        <x:v>按SRS 9.4–9.5及Q16核对全部证据；AC-10B缺失不标为全部通过。</x:v>
+      </x:c>
+      <x:c r="N117" s="79" t="str">
+        <x:v>按SRS 9.4–9.5及Q16核对全部证据；AC-10B缺失不标为全部通过。</x:v>
+      </x:c>
+      <x:c r="O117" s="79" t="str">
+        <x:v>按SRS 9.4–9.5及Q16核对全部证据；AC-10B缺失不标为全部通过。</x:v>
+      </x:c>
+      <x:c r="P117" s="79" t="str">
+        <x:v>按SRS 9.4–9.5及Q16核对全部证据；AC-10B缺失不标为全部通过。</x:v>
+      </x:c>
+      <x:c r="Q117" s="79" t="str">
+        <x:f>'任务与甘特'!P49</x:f>
+        <x:v>完整需求证据与实际交换接收凭据</x:v>
+      </x:c>
+      <x:c r="R117" s="79"/>
+      <x:c r="S117" s="79"/>
+    </x:row>
+    <x:row r="118" ht="72" customHeight="1">
+      <x:c r="A118" s="79" t="str">
+        <x:f>'任务与甘特'!A50</x:f>
+        <x:v>T5.7</x:v>
+      </x:c>
+      <x:c r="B118" s="79" t="str">
+        <x:f>'任务与甘特'!B50</x:f>
+        <x:v>汇总8周模拟的最终项目计划</x:v>
+      </x:c>
+      <x:c r="C118" s="79"/>
+      <x:c r="D118" s="79"/>
+      <x:c r="E118" s="79" t="str">
+        <x:f>'任务与甘特'!R50</x:f>
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="F118" s="79"/>
+      <x:c r="G118" s="79" t="str">
+        <x:f>IF($E118="R01","A/R",IF(ISNUMBER('任务与甘特'!Y50),IF('任务与甘特'!Y50&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>A/R</x:v>
+      </x:c>
+      <x:c r="H118" s="79" t="str">
+        <x:f>IF($E118="R02","A/R",IF(ISNUMBER('任务与甘特'!Z50),IF('任务与甘特'!Z50&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I118" s="79" t="str">
+        <x:f>IF($E118="R03","A/R",IF(ISNUMBER('任务与甘特'!AA50),IF('任务与甘特'!AA50&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="J118" s="79" t="str">
+        <x:f>IF($E118="R04","A/R",IF(ISNUMBER('任务与甘特'!AB50),IF('任务与甘特'!AB50&gt;0,"R","I"),"待确认"))</x:f>
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="K118" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="L118" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="M118" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="N118" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="O118" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="P118" s="79" t="str">
+        <x:v>核对交付版本、操作资料、用户反馈和未完成项；不预填实际结论。</x:v>
+      </x:c>
+      <x:c r="Q118" s="79" t="str">
+        <x:f>'任务与甘特'!P50</x:f>
+        <x:v>完整项目计划与迭代说明</x:v>
+      </x:c>
+      <x:c r="R118" s="79"/>
+      <x:c r="S118" s="79"/>
+    </x:row>
+    <x:row r="120" ht="44" customHeight="1">
+      <x:c r="A120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="B120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="C120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="D120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="E120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="F120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="G120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="H120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="I120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="J120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="K120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="L120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="M120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="N120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="O120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="P120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="Q120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="R120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+      <x:c r="S120" s="79" t="str">
+        <x:v>复核按具体成果避开作者。R04参与实现或部署的产物由其他既有参与者互核；若列出的牵头复核人同为作者，在原分配中换人，并在质量记录中登记实际复核人和证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="44" customHeight="1">
+      <x:c r="A121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="B121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="C121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="D121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="E121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="F121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="G121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="H121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="I121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="J121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="K121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="L121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="M121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="N121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="O121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="P121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="Q121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="R121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+      <x:c r="S121" s="79" t="str">
+        <x:v>T2.5的36人时仍全部为R01。日常版本、问题和质量跟踪由R01登记，R04在T1.2/T4.1/T5.7等已有评审分配内抽查；该矩阵不另行增加人时、会议或资源费用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="44" customHeight="1">
+      <x:c r="A122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="B122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="C122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="D122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="E122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="F122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="G122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="H122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="I122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="J122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="K122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="L122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="M122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="N122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="O122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="P122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="Q122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="R122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+      <x:c r="S122" s="79" t="str">
+        <x:v>在既有工作交接中简述已完成事项、下一步和阻塞；每轮结合现有维护任务复核成果及改进措施。无法在现有容量内完成时记录影响、责任和期限，必要时办理CR，不默默增加投入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="44" customHeight="1">
+      <x:c r="A123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="B123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="C123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="D123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="E123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="F123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="G123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="H123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="I123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="J123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="K123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="L123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="M123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="N123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="O123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="P123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="Q123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="R123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+      <x:c r="S123" s="79" t="str">
+        <x:v>实际项目发起人、需求确认人与验收代表及其授权尚未确定，姓名和签字不代填。模拟团队及交叉复核安排不构成实际参与证明；原责任或投入变化后应重新核对本矩阵。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A71:S71"/>
+    <x:mergeCell ref="A72:S72"/>
+    <x:mergeCell ref="B74:D74"/>
+    <x:mergeCell ref="E74:F74"/>
+    <x:mergeCell ref="K74:L74"/>
+    <x:mergeCell ref="M74:P74"/>
+    <x:mergeCell ref="Q74:S74"/>
+    <x:mergeCell ref="B75:D75"/>
+    <x:mergeCell ref="E75:F75"/>
+    <x:mergeCell ref="Q75:S75"/>
+    <x:mergeCell ref="K75:L75"/>
+    <x:mergeCell ref="M75:P75"/>
+    <x:mergeCell ref="B76:D76"/>
+    <x:mergeCell ref="E76:F76"/>
+    <x:mergeCell ref="Q76:S76"/>
+    <x:mergeCell ref="K76:L76"/>
+    <x:mergeCell ref="M76:P76"/>
+    <x:mergeCell ref="B77:D77"/>
+    <x:mergeCell ref="E77:F77"/>
+    <x:mergeCell ref="Q77:S77"/>
+    <x:mergeCell ref="K77:L77"/>
+    <x:mergeCell ref="M77:P77"/>
+    <x:mergeCell ref="B78:D78"/>
+    <x:mergeCell ref="E78:F78"/>
+    <x:mergeCell ref="Q78:S78"/>
+    <x:mergeCell ref="K78:L78"/>
+    <x:mergeCell ref="M78:P78"/>
+    <x:mergeCell ref="B79:D79"/>
+    <x:mergeCell ref="E79:F79"/>
+    <x:mergeCell ref="Q79:S79"/>
+    <x:mergeCell ref="K79:L79"/>
+    <x:mergeCell ref="M79:P79"/>
+    <x:mergeCell ref="B80:D80"/>
+    <x:mergeCell ref="E80:F80"/>
+    <x:mergeCell ref="Q80:S80"/>
+    <x:mergeCell ref="K80:L80"/>
+    <x:mergeCell ref="M80:P80"/>
+    <x:mergeCell ref="B81:D81"/>
+    <x:mergeCell ref="E81:F81"/>
+    <x:mergeCell ref="Q81:S81"/>
+    <x:mergeCell ref="K81:L81"/>
+    <x:mergeCell ref="M81:P81"/>
+    <x:mergeCell ref="B82:D82"/>
+    <x:mergeCell ref="E82:F82"/>
+    <x:mergeCell ref="Q82:S82"/>
+    <x:mergeCell ref="K82:L82"/>
+    <x:mergeCell ref="M82:P82"/>
+    <x:mergeCell ref="B83:D83"/>
+    <x:mergeCell ref="E83:F83"/>
+    <x:mergeCell ref="Q83:S83"/>
+    <x:mergeCell ref="K83:L83"/>
+    <x:mergeCell ref="M83:P83"/>
+    <x:mergeCell ref="B84:D84"/>
+    <x:mergeCell ref="E84:F84"/>
+    <x:mergeCell ref="Q84:S84"/>
+    <x:mergeCell ref="K84:L84"/>
+    <x:mergeCell ref="M84:P84"/>
+    <x:mergeCell ref="B85:D85"/>
+    <x:mergeCell ref="E85:F85"/>
+    <x:mergeCell ref="Q85:S85"/>
+    <x:mergeCell ref="K85:L85"/>
+    <x:mergeCell ref="M85:P85"/>
+    <x:mergeCell ref="B86:D86"/>
+    <x:mergeCell ref="E86:F86"/>
+    <x:mergeCell ref="Q86:S86"/>
+    <x:mergeCell ref="K86:L86"/>
+    <x:mergeCell ref="M86:P86"/>
+    <x:mergeCell ref="B87:D87"/>
+    <x:mergeCell ref="E87:F87"/>
+    <x:mergeCell ref="Q87:S87"/>
+    <x:mergeCell ref="K87:L87"/>
+    <x:mergeCell ref="M87:P87"/>
+    <x:mergeCell ref="B88:D88"/>
+    <x:mergeCell ref="E88:F88"/>
+    <x:mergeCell ref="Q88:S88"/>
+    <x:mergeCell ref="K88:L88"/>
+    <x:mergeCell ref="M88:P88"/>
+    <x:mergeCell ref="B89:D89"/>
+    <x:mergeCell ref="E89:F89"/>
+    <x:mergeCell ref="Q89:S89"/>
+    <x:mergeCell ref="K89:L89"/>
+    <x:mergeCell ref="M89:P89"/>
+    <x:mergeCell ref="B90:D90"/>
+    <x:mergeCell ref="E90:F90"/>
+    <x:mergeCell ref="Q90:S90"/>
+    <x:mergeCell ref="K90:L90"/>
+    <x:mergeCell ref="M90:P90"/>
+    <x:mergeCell ref="B91:D91"/>
+    <x:mergeCell ref="E91:F91"/>
+    <x:mergeCell ref="Q91:S91"/>
+    <x:mergeCell ref="K91:L91"/>
+    <x:mergeCell ref="M91:P91"/>
+    <x:mergeCell ref="B92:D92"/>
+    <x:mergeCell ref="E92:F92"/>
+    <x:mergeCell ref="Q92:S92"/>
+    <x:mergeCell ref="K92:L92"/>
+    <x:mergeCell ref="M92:P92"/>
+    <x:mergeCell ref="B93:D93"/>
+    <x:mergeCell ref="E93:F93"/>
+    <x:mergeCell ref="Q93:S93"/>
+    <x:mergeCell ref="K93:L93"/>
+    <x:mergeCell ref="M93:P93"/>
+    <x:mergeCell ref="B94:D94"/>
+    <x:mergeCell ref="E94:F94"/>
+    <x:mergeCell ref="Q94:S94"/>
+    <x:mergeCell ref="K94:L94"/>
+    <x:mergeCell ref="M94:P94"/>
+    <x:mergeCell ref="B95:D95"/>
+    <x:mergeCell ref="E95:F95"/>
+    <x:mergeCell ref="Q95:S95"/>
+    <x:mergeCell ref="K95:L95"/>
+    <x:mergeCell ref="M95:P95"/>
+    <x:mergeCell ref="B96:D96"/>
+    <x:mergeCell ref="E96:F96"/>
+    <x:mergeCell ref="Q96:S96"/>
+    <x:mergeCell ref="K96:L96"/>
+    <x:mergeCell ref="M96:P96"/>
+    <x:mergeCell ref="B97:D97"/>
+    <x:mergeCell ref="E97:F97"/>
+    <x:mergeCell ref="Q97:S97"/>
+    <x:mergeCell ref="K97:L97"/>
+    <x:mergeCell ref="M97:P97"/>
+    <x:mergeCell ref="B98:D98"/>
+    <x:mergeCell ref="E98:F98"/>
+    <x:mergeCell ref="Q98:S98"/>
+    <x:mergeCell ref="K98:L98"/>
+    <x:mergeCell ref="M98:P98"/>
+    <x:mergeCell ref="B99:D99"/>
+    <x:mergeCell ref="E99:F99"/>
+    <x:mergeCell ref="Q99:S99"/>
+    <x:mergeCell ref="K99:L99"/>
+    <x:mergeCell ref="M99:P99"/>
+    <x:mergeCell ref="B100:D100"/>
+    <x:mergeCell ref="E100:F100"/>
+    <x:mergeCell ref="Q100:S100"/>
+    <x:mergeCell ref="K100:L100"/>
+    <x:mergeCell ref="M100:P100"/>
+    <x:mergeCell ref="B101:D101"/>
+    <x:mergeCell ref="E101:F101"/>
+    <x:mergeCell ref="Q101:S101"/>
+    <x:mergeCell ref="K101:L101"/>
+    <x:mergeCell ref="M101:P101"/>
+    <x:mergeCell ref="B102:D102"/>
+    <x:mergeCell ref="E102:F102"/>
+    <x:mergeCell ref="Q102:S102"/>
+    <x:mergeCell ref="K102:L102"/>
+    <x:mergeCell ref="M102:P102"/>
+    <x:mergeCell ref="B103:D103"/>
+    <x:mergeCell ref="E103:F103"/>
+    <x:mergeCell ref="Q103:S103"/>
+    <x:mergeCell ref="K103:L103"/>
+    <x:mergeCell ref="M103:P103"/>
+    <x:mergeCell ref="B104:D104"/>
+    <x:mergeCell ref="E104:F104"/>
+    <x:mergeCell ref="Q104:S104"/>
+    <x:mergeCell ref="K104:L104"/>
+    <x:mergeCell ref="M104:P104"/>
+    <x:mergeCell ref="B105:D105"/>
+    <x:mergeCell ref="E105:F105"/>
+    <x:mergeCell ref="Q105:S105"/>
+    <x:mergeCell ref="K105:L105"/>
+    <x:mergeCell ref="M105:P105"/>
+    <x:mergeCell ref="B106:D106"/>
+    <x:mergeCell ref="E106:F106"/>
+    <x:mergeCell ref="Q106:S106"/>
+    <x:mergeCell ref="K106:L106"/>
+    <x:mergeCell ref="M106:P106"/>
+    <x:mergeCell ref="B107:D107"/>
+    <x:mergeCell ref="E107:F107"/>
+    <x:mergeCell ref="Q107:S107"/>
+    <x:mergeCell ref="K107:L107"/>
+    <x:mergeCell ref="M107:P107"/>
+    <x:mergeCell ref="B108:D108"/>
+    <x:mergeCell ref="E108:F108"/>
+    <x:mergeCell ref="Q108:S108"/>
+    <x:mergeCell ref="K108:L108"/>
+    <x:mergeCell ref="M108:P108"/>
+    <x:mergeCell ref="B109:D109"/>
+    <x:mergeCell ref="E109:F109"/>
+    <x:mergeCell ref="Q109:S109"/>
+    <x:mergeCell ref="K109:L109"/>
+    <x:mergeCell ref="M109:P109"/>
+    <x:mergeCell ref="B110:D110"/>
+    <x:mergeCell ref="E110:F110"/>
+    <x:mergeCell ref="Q110:S110"/>
+    <x:mergeCell ref="K110:L110"/>
+    <x:mergeCell ref="M110:P110"/>
+    <x:mergeCell ref="B111:D111"/>
+    <x:mergeCell ref="E111:F111"/>
+    <x:mergeCell ref="Q111:S111"/>
+    <x:mergeCell ref="K111:L111"/>
+    <x:mergeCell ref="M111:P111"/>
+    <x:mergeCell ref="B112:D112"/>
+    <x:mergeCell ref="E112:F112"/>
+    <x:mergeCell ref="Q112:S112"/>
+    <x:mergeCell ref="K112:L112"/>
+    <x:mergeCell ref="M112:P112"/>
+    <x:mergeCell ref="B113:D113"/>
+    <x:mergeCell ref="E113:F113"/>
+    <x:mergeCell ref="Q113:S113"/>
+    <x:mergeCell ref="K113:L113"/>
+    <x:mergeCell ref="M113:P113"/>
+    <x:mergeCell ref="B114:D114"/>
+    <x:mergeCell ref="E114:F114"/>
+    <x:mergeCell ref="Q114:S114"/>
+    <x:mergeCell ref="K114:L114"/>
+    <x:mergeCell ref="M114:P114"/>
+    <x:mergeCell ref="B115:D115"/>
+    <x:mergeCell ref="E115:F115"/>
+    <x:mergeCell ref="Q115:S115"/>
+    <x:mergeCell ref="K115:L115"/>
+    <x:mergeCell ref="M115:P115"/>
+    <x:mergeCell ref="B116:D116"/>
+    <x:mergeCell ref="E116:F116"/>
+    <x:mergeCell ref="Q116:S116"/>
+    <x:mergeCell ref="K116:L116"/>
+    <x:mergeCell ref="M116:P116"/>
+    <x:mergeCell ref="B117:D117"/>
+    <x:mergeCell ref="E117:F117"/>
+    <x:mergeCell ref="Q117:S117"/>
+    <x:mergeCell ref="K117:L117"/>
+    <x:mergeCell ref="M117:P117"/>
+    <x:mergeCell ref="B118:D118"/>
+    <x:mergeCell ref="E118:F118"/>
+    <x:mergeCell ref="Q118:S118"/>
+    <x:mergeCell ref="K118:L118"/>
+    <x:mergeCell ref="M118:P118"/>
+    <x:mergeCell ref="A120:S120"/>
+    <x:mergeCell ref="A121:S121"/>
+    <x:mergeCell ref="A122:S122"/>
+    <x:mergeCell ref="A123:S123"/>
+  </x:mergeCells>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="A8:A12">
       <x:formula1>"是,否"</x:formula1>
@@ -13102,6 +16304,462 @@
       </x:c>
       <x:c r="S64" s="63" t="str">
         <x:v>本版保留原成本基准106,852.50元、管理储备10,685.25元及总预算117,537.75元。风险独立应急储备未落实属于待处理计划条件，不表示现有管理储备已承诺覆盖全部风险。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="28" customHeight="1">
+      <x:c r="A67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="B67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="C67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="D67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="E67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="F67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="G67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="H67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="I67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="J67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="K67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="L67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="M67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="N67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="O67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="P67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="Q67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="R67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+      <x:c r="S67" s="86" t="str">
+        <x:v>质量成本分类与记录（沿用原预算）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="40" customHeight="1">
+      <x:c r="A68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="B68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="C68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="D68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="E68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="F68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="G68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="H68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="I68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="J68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="K68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="L68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="M68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="N68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="O68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="P68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="Q68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="R68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+      <x:c r="S68" s="79" t="str">
+        <x:v>质量成本是既有费用的用途分类，不是新增预算。混合活动尚未拆分纯质量费用；同一人时和资源费用只计一次，实际发生额未知时留空。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="46" customHeight="1">
+      <x:c r="A70" s="86" t="str">
+        <x:v>类别</x:v>
+      </x:c>
+      <x:c r="B70" s="86" t="str">
+        <x:v>类别</x:v>
+      </x:c>
+      <x:c r="C70" s="86" t="str">
+        <x:v>活动或发生条件</x:v>
+      </x:c>
+      <x:c r="D70" s="86" t="str">
+        <x:v>活动或发生条件</x:v>
+      </x:c>
+      <x:c r="E70" s="86" t="str">
+        <x:v>活动或发生条件</x:v>
+      </x:c>
+      <x:c r="F70" s="86" t="str">
+        <x:v>活动或发生条件</x:v>
+      </x:c>
+      <x:c r="G70" s="86" t="str">
+        <x:v>对应任务</x:v>
+      </x:c>
+      <x:c r="H70" s="86" t="str">
+        <x:v>对应任务</x:v>
+      </x:c>
+      <x:c r="I70" s="86" t="str">
+        <x:v>对应任务</x:v>
+      </x:c>
+      <x:c r="J70" s="86" t="str">
+        <x:v>原预算归属</x:v>
+      </x:c>
+      <x:c r="K70" s="86" t="str">
+        <x:v>原预算归属</x:v>
+      </x:c>
+      <x:c r="L70" s="86" t="str">
+        <x:v>原预算归属</x:v>
+      </x:c>
+      <x:c r="M70" s="86" t="str">
+        <x:v>原预算归属</x:v>
+      </x:c>
+      <x:c r="N70" s="86" t="str">
+        <x:v>实际金额（元）</x:v>
+      </x:c>
+      <x:c r="O70" s="86" t="str">
+        <x:v>实际金额（元）</x:v>
+      </x:c>
+      <x:c r="P70" s="86" t="str">
+        <x:v>记录与控制</x:v>
+      </x:c>
+      <x:c r="Q70" s="86" t="str">
+        <x:v>记录与控制</x:v>
+      </x:c>
+      <x:c r="R70" s="86" t="str">
+        <x:v>记录与控制</x:v>
+      </x:c>
+      <x:c r="S70" s="86" t="str">
+        <x:v>记录与控制</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="86" customHeight="1">
+      <x:c r="A71" s="79" t="str">
+        <x:v>预防</x:v>
+      </x:c>
+      <x:c r="B71" s="79" t="str">
+        <x:v>预防</x:v>
+      </x:c>
+      <x:c r="C71" s="79" t="str">
+        <x:v>需求/设计复核、测试设计、规范交底及开发过程中的预防措施</x:v>
+      </x:c>
+      <x:c r="D71" s="79" t="str">
+        <x:v>需求/设计复核、测试设计、规范交底及开发过程中的预防措施</x:v>
+      </x:c>
+      <x:c r="E71" s="79" t="str">
+        <x:v>需求/设计复核、测试设计、规范交底及开发过程中的预防措施</x:v>
+      </x:c>
+      <x:c r="F71" s="79" t="str">
+        <x:v>需求/设计复核、测试设计、规范交底及开发过程中的预防措施</x:v>
+      </x:c>
+      <x:c r="G71" s="79" t="str">
+        <x:v>T1.1/T1.3/T2/T3及原评审</x:v>
+      </x:c>
+      <x:c r="H71" s="79" t="str">
+        <x:v>T1.1/T1.3/T2/T3及原评审</x:v>
+      </x:c>
+      <x:c r="I71" s="79" t="str">
+        <x:v>T1.1/T1.3/T2/T3及原评审</x:v>
+      </x:c>
+      <x:c r="J71" s="79" t="str">
+        <x:v>原任务人工与C06–C09等；混合任务未作纯质量费用分摊。</x:v>
+      </x:c>
+      <x:c r="K71" s="79" t="str">
+        <x:v>原任务人工与C06–C09等；混合任务未作纯质量费用分摊。</x:v>
+      </x:c>
+      <x:c r="L71" s="79" t="str">
+        <x:v>原任务人工与C06–C09等；混合任务未作纯质量费用分摊。</x:v>
+      </x:c>
+      <x:c r="M71" s="79" t="str">
+        <x:v>原任务人工与C06–C09等；混合任务未作纯质量费用分摊。</x:v>
+      </x:c>
+      <x:c r="N71" s="91"/>
+      <x:c r="O71" s="91"/>
+      <x:c r="P71" s="79" t="str">
+        <x:v>沿用既有预算；不将整项设计或开发成本全部另算为质量成本。</x:v>
+      </x:c>
+      <x:c r="Q71" s="79" t="str">
+        <x:v>沿用既有预算；不将整项设计或开发成本全部另算为质量成本。</x:v>
+      </x:c>
+      <x:c r="R71" s="79" t="str">
+        <x:v>沿用既有预算；不将整项设计或开发成本全部另算为质量成本。</x:v>
+      </x:c>
+      <x:c r="S71" s="79" t="str">
+        <x:v>沿用既有预算；不将整项设计或开发成本全部另算为质量成本。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="86" customHeight="1">
+      <x:c r="A72" s="79" t="str">
+        <x:v>评估</x:v>
+      </x:c>
+      <x:c r="B72" s="79" t="str">
+        <x:v>评估</x:v>
+      </x:c>
+      <x:c r="C72" s="79" t="str">
+        <x:v>技术评审、功能/性能/安全/恢复/兼容检查和最终验收</x:v>
+      </x:c>
+      <x:c r="D72" s="79" t="str">
+        <x:v>技术评审、功能/性能/安全/恢复/兼容检查和最终验收</x:v>
+      </x:c>
+      <x:c r="E72" s="79" t="str">
+        <x:v>技术评审、功能/性能/安全/恢复/兼容检查和最终验收</x:v>
+      </x:c>
+      <x:c r="F72" s="79" t="str">
+        <x:v>技术评审、功能/性能/安全/恢复/兼容检查和最终验收</x:v>
+      </x:c>
+      <x:c r="G72" s="79" t="str">
+        <x:v>T4.1/T4.3–T4.9/T5.6</x:v>
+      </x:c>
+      <x:c r="H72" s="79" t="str">
+        <x:v>T4.1/T4.3–T4.9/T5.6</x:v>
+      </x:c>
+      <x:c r="I72" s="79" t="str">
+        <x:v>T4.1/T4.3–T4.9/T5.6</x:v>
+      </x:c>
+      <x:c r="J72" s="79" t="str">
+        <x:v>原任务人工及开发/测试部署资源。</x:v>
+      </x:c>
+      <x:c r="K72" s="79" t="str">
+        <x:v>原任务人工及开发/测试部署资源。</x:v>
+      </x:c>
+      <x:c r="L72" s="79" t="str">
+        <x:v>原任务人工及开发/测试部署资源。</x:v>
+      </x:c>
+      <x:c r="M72" s="79" t="str">
+        <x:v>原任务人工及开发/测试部署资源。</x:v>
+      </x:c>
+      <x:c r="N72" s="91"/>
+      <x:c r="O72" s="91"/>
+      <x:c r="P72" s="79" t="str">
+        <x:v>检验和测试发现缺陷；修复及再次验证另按具体事项归类。</x:v>
+      </x:c>
+      <x:c r="Q72" s="79" t="str">
+        <x:v>检验和测试发现缺陷；修复及再次验证另按具体事项归类。</x:v>
+      </x:c>
+      <x:c r="R72" s="79" t="str">
+        <x:v>检验和测试发现缺陷；修复及再次验证另按具体事项归类。</x:v>
+      </x:c>
+      <x:c r="S72" s="79" t="str">
+        <x:v>检验和测试发现缺陷；修复及再次验证另按具体事项归类。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="86" customHeight="1">
+      <x:c r="A73" s="79" t="str">
+        <x:v>内部缺陷</x:v>
+      </x:c>
+      <x:c r="B73" s="79" t="str">
+        <x:v>内部缺陷</x:v>
+      </x:c>
+      <x:c r="C73" s="79" t="str">
+        <x:v>正式交付前的缺陷定位、修复和相关回归</x:v>
+      </x:c>
+      <x:c r="D73" s="79" t="str">
+        <x:v>正式交付前的缺陷定位、修复和相关回归</x:v>
+      </x:c>
+      <x:c r="E73" s="79" t="str">
+        <x:v>正式交付前的缺陷定位、修复和相关回归</x:v>
+      </x:c>
+      <x:c r="F73" s="79" t="str">
+        <x:v>正式交付前的缺陷定位、修复和相关回归</x:v>
+      </x:c>
+      <x:c r="G73" s="79" t="str">
+        <x:v>T4.10及原开发/试运行活动</x:v>
+      </x:c>
+      <x:c r="H73" s="79" t="str">
+        <x:v>T4.10及原开发/试运行活动</x:v>
+      </x:c>
+      <x:c r="I73" s="79" t="str">
+        <x:v>T4.10及原开发/试运行活动</x:v>
+      </x:c>
+      <x:c r="J73" s="79" t="str">
+        <x:v>T4.10已含56人时修复与回归；原任务费用不重复加算。</x:v>
+      </x:c>
+      <x:c r="K73" s="79" t="str">
+        <x:v>T4.10已含56人时修复与回归；原任务费用不重复加算。</x:v>
+      </x:c>
+      <x:c r="L73" s="79" t="str">
+        <x:v>T4.10已含56人时修复与回归；原任务费用不重复加算。</x:v>
+      </x:c>
+      <x:c r="M73" s="79" t="str">
+        <x:v>T4.10已含56人时修复与回归；原任务费用不重复加算。</x:v>
+      </x:c>
+      <x:c r="N73" s="91"/>
+      <x:c r="O73" s="91"/>
+      <x:c r="P73" s="79" t="str">
+        <x:v>实际发生时区分修复与评估，记录缺陷号、投入及凭证；未知值留空。</x:v>
+      </x:c>
+      <x:c r="Q73" s="79" t="str">
+        <x:v>实际发生时区分修复与评估，记录缺陷号、投入及凭证；未知值留空。</x:v>
+      </x:c>
+      <x:c r="R73" s="79" t="str">
+        <x:v>实际发生时区分修复与评估，记录缺陷号、投入及凭证；未知值留空。</x:v>
+      </x:c>
+      <x:c r="S73" s="79" t="str">
+        <x:v>实际发生时区分修复与评估，记录缺陷号、投入及凭证；未知值留空。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="86" customHeight="1">
+      <x:c r="A74" s="79" t="str">
+        <x:v>外部缺陷</x:v>
+      </x:c>
+      <x:c r="B74" s="79" t="str">
+        <x:v>外部缺陷</x:v>
+      </x:c>
+      <x:c r="C74" s="79" t="str">
+        <x:v>正式交付后的返修、支持及其他缺陷影响</x:v>
+      </x:c>
+      <x:c r="D74" s="79" t="str">
+        <x:v>正式交付后的返修、支持及其他缺陷影响</x:v>
+      </x:c>
+      <x:c r="E74" s="79" t="str">
+        <x:v>正式交付后的返修、支持及其他缺陷影响</x:v>
+      </x:c>
+      <x:c r="F74" s="79" t="str">
+        <x:v>正式交付后的返修、支持及其他缺陷影响</x:v>
+      </x:c>
+      <x:c r="G74" s="79" t="str">
+        <x:v>本版未设独立交付后维护活动</x:v>
+      </x:c>
+      <x:c r="H74" s="79" t="str">
+        <x:v>本版未设独立交付后维护活动</x:v>
+      </x:c>
+      <x:c r="I74" s="79" t="str">
+        <x:v>本版未设独立交付后维护活动</x:v>
+      </x:c>
+      <x:c r="J74" s="79" t="str">
+        <x:v>独立金额及实际支出留空；不承诺由C14覆盖。</x:v>
+      </x:c>
+      <x:c r="K74" s="79" t="str">
+        <x:v>独立金额及实际支出留空；不承诺由C14覆盖。</x:v>
+      </x:c>
+      <x:c r="L74" s="79" t="str">
+        <x:v>独立金额及实际支出留空；不承诺由C14覆盖。</x:v>
+      </x:c>
+      <x:c r="M74" s="79" t="str">
+        <x:v>独立金额及实际支出留空；不承诺由C14覆盖。</x:v>
+      </x:c>
+      <x:c r="N74" s="91"/>
+      <x:c r="O74" s="91"/>
+      <x:c r="P74" s="79" t="str">
+        <x:v>发生后核实范围、工时、费用及风险；超出基线时办理CR。</x:v>
+      </x:c>
+      <x:c r="Q74" s="79" t="str">
+        <x:v>发生后核实范围、工时、费用及风险；超出基线时办理CR。</x:v>
+      </x:c>
+      <x:c r="R74" s="79" t="str">
+        <x:v>发生后核实范围、工时、费用及风险；超出基线时办理CR。</x:v>
+      </x:c>
+      <x:c r="S74" s="79" t="str">
+        <x:v>发生后核实范围、工时、费用及风险；超出基线时办理CR。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="40" customHeight="1">
+      <x:c r="A76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="B76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="C76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="D76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="E76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="F76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="G76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="H76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="I76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="J76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="K76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="L76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="M76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="N76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="O76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="P76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="Q76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="R76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
+      </x:c>
+      <x:c r="S76" s="79" t="str">
+        <x:v>预防及评估尽早开展，缺陷修复后需复测。质量不符合时先分析根因与剩余工作，保留原验收门槛；需要改变进度、工作量、费用或受控标准时提出CR并同步两种计划。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13223,6 +16881,39 @@
     <x:mergeCell ref="Q61:S61"/>
     <x:mergeCell ref="A63:S63"/>
     <x:mergeCell ref="A64:S64"/>
+    <x:mergeCell ref="A67:S67"/>
+    <x:mergeCell ref="A68:S68"/>
+    <x:mergeCell ref="A70:B70"/>
+    <x:mergeCell ref="C70:F70"/>
+    <x:mergeCell ref="G70:I70"/>
+    <x:mergeCell ref="J70:M70"/>
+    <x:mergeCell ref="N70:O70"/>
+    <x:mergeCell ref="P70:S70"/>
+    <x:mergeCell ref="A71:B71"/>
+    <x:mergeCell ref="C71:F71"/>
+    <x:mergeCell ref="G71:I71"/>
+    <x:mergeCell ref="J71:M71"/>
+    <x:mergeCell ref="N71:O71"/>
+    <x:mergeCell ref="P71:S71"/>
+    <x:mergeCell ref="A72:B72"/>
+    <x:mergeCell ref="C72:F72"/>
+    <x:mergeCell ref="G72:I72"/>
+    <x:mergeCell ref="J72:M72"/>
+    <x:mergeCell ref="N72:O72"/>
+    <x:mergeCell ref="P72:S72"/>
+    <x:mergeCell ref="A73:B73"/>
+    <x:mergeCell ref="C73:F73"/>
+    <x:mergeCell ref="G73:I73"/>
+    <x:mergeCell ref="J73:M73"/>
+    <x:mergeCell ref="N73:O73"/>
+    <x:mergeCell ref="P73:S73"/>
+    <x:mergeCell ref="A74:B74"/>
+    <x:mergeCell ref="C74:F74"/>
+    <x:mergeCell ref="G74:I74"/>
+    <x:mergeCell ref="J74:M74"/>
+    <x:mergeCell ref="N74:O74"/>
+    <x:mergeCell ref="P74:S74"/>
+    <x:mergeCell ref="A76:S76"/>
   </x:mergeCells>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="B13:B21">
@@ -13262,7 +16953,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>质量、计划复核与风险（仿真）</x:v>
+        <x:v>质量保证、成果控制、计划复核与风险（仿真）</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -13272,9 +16963,9 @@
       <x:c r="G2" s="4"/>
       <x:c r="H2" s="4"/>
     </x:row>
-    <x:row r="3" ht="30" customHeight="1">
+    <x:row r="3" ht="40" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>16项预定质量标准已填写仿真负责人、计划日期与方法。实际执行日期、结果和证据尚未产生，保持留空。</x:v>
+        <x:v>16项产品质量标准沿用SRS；8项全过程质量活动及6项度量口径嵌入既有任务。实际执行、复测与验收证据尚未产生，保持留空。</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -14326,15 +18017,31 @@
         <x:v>CR-003已修订计划；实际软件执行、支出及未来迭代结果不预填。</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="30" customHeight="1">
-      <x:c r="A43" s="4"/>
-      <x:c r="B43" s="4"/>
-      <x:c r="C43" s="4"/>
-      <x:c r="D43" s="4"/>
-      <x:c r="E43" s="4"/>
-      <x:c r="F43" s="4"/>
-      <x:c r="G43" s="4"/>
-      <x:c r="H43" s="4"/>
+    <x:row r="43" ht="96" customHeight="1">
+      <x:c r="A43" s="79" t="str">
+        <x:v>V1.1→V1.2</x:v>
+      </x:c>
+      <x:c r="B43" s="80" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C43" s="79" t="str">
+        <x:v>V1.2 / CM-R4</x:v>
+      </x:c>
+      <x:c r="D43" s="79" t="str">
+        <x:v>R01（计划编制角色）</x:v>
+      </x:c>
+      <x:c r="E43" s="79" t="str">
+        <x:v>质量活动嵌入原任务，日期不变</x:v>
+      </x:c>
+      <x:c r="F43" s="79" t="str">
+        <x:v>责任及交叉复核细化，分配不变</x:v>
+      </x:c>
+      <x:c r="G43" s="79" t="str">
+        <x:v>质量成本分类说明，金额不变</x:v>
+      </x:c>
+      <x:c r="H43" s="79" t="str">
+        <x:v>CR-004已修订计划；未预填模拟成员评审签字或实际软件结果。</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="28" customHeight="1">
       <x:c r="A44" s="60" t="str">
@@ -14441,7 +18148,7 @@
         <x:v>遗留事项</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="84" customHeight="1">
+    <x:row r="48" ht="96" customHeight="1">
       <x:c r="A48" s="63" t="str">
         <x:v>W1</x:v>
       </x:c>
@@ -14449,13 +18156,13 @@
         <x:v>2026-10-19 至 2026-10-25</x:v>
       </x:c>
       <x:c r="C48" s="63" t="str">
-        <x:v>需求／WBS与估算方法对应，识别成本与储备边界</x:v>
+        <x:v>需求与验收映射、质量分工、测试设计和成本估算前提</x:v>
       </x:c>
       <x:c r="D48" s="63" t="str">
-        <x:v>估算依据、成本控制与版本记录</x:v>
+        <x:v>需求追踪、质量活动定义及基线记录</x:v>
       </x:c>
       <x:c r="E48" s="63" t="str">
-        <x:v>R01编制／R04复核（模拟角色）</x:v>
+        <x:v>R01维护；原分配成员提供证据</x:v>
       </x:c>
       <x:c r="F48" s="69"/>
       <x:c r="G48" s="63"/>
@@ -14464,7 +18171,7 @@
       <x:c r="J48" s="63"/>
       <x:c r="K48" s="63"/>
     </x:row>
-    <x:row r="49" ht="84" customHeight="1">
+    <x:row r="49" ht="96" customHeight="1">
       <x:c r="A49" s="63" t="str">
         <x:v>W2</x:v>
       </x:c>
@@ -14472,13 +18179,13 @@
         <x:v>2026-10-26 至 2026-11-01</x:v>
       </x:c>
       <x:c r="C49" s="63" t="str">
-        <x:v>细化WBS、外部协议条件及不确定性，检查资源和储备缺口</x:v>
+        <x:v>设计接口交叉复核、外部输入、质量条件与储备缺口</x:v>
       </x:c>
       <x:c r="D49" s="63" t="str">
-        <x:v>阶段重点复核与风险响应说明</x:v>
+        <x:v>阶段重点复核及未具备条件清单</x:v>
       </x:c>
       <x:c r="E49" s="63" t="str">
-        <x:v>R01编制／R04复核（模拟角色）</x:v>
+        <x:v>R01维护；原分配成员提供证据</x:v>
       </x:c>
       <x:c r="F49" s="69"/>
       <x:c r="G49" s="63"/>
@@ -14487,7 +18194,7 @@
       <x:c r="J49" s="63"/>
       <x:c r="K49" s="63"/>
     </x:row>
-    <x:row r="50" ht="84" customHeight="1">
+    <x:row r="50" ht="96" customHeight="1">
       <x:c r="A50" s="63" t="str">
         <x:v>W3</x:v>
       </x:c>
@@ -14495,13 +18202,13 @@
         <x:v>2026-11-02 至 2026-11-08</x:v>
       </x:c>
       <x:c r="C50" s="63" t="str">
-        <x:v>检查业务活动投入与预期产出，复核剩余工作估算</x:v>
+        <x:v>模块编码规范、小批量集成及相关回归；复核剩余工作</x:v>
       </x:c>
       <x:c r="D50" s="63" t="str">
-        <x:v>周复核结论及实际偏差原因</x:v>
+        <x:v>版本证据、过程不符合项及偏差原因</x:v>
       </x:c>
       <x:c r="E50" s="63" t="str">
-        <x:v>R01编制／R04复核（模拟角色）</x:v>
+        <x:v>R01维护；原分配成员提供证据</x:v>
       </x:c>
       <x:c r="F50" s="69"/>
       <x:c r="G50" s="63"/>
@@ -14510,7 +18217,7 @@
       <x:c r="J50" s="63"/>
       <x:c r="K50" s="63"/>
     </x:row>
-    <x:row r="51" ht="84" customHeight="1">
+    <x:row r="51" ht="96" customHeight="1">
       <x:c r="A51" s="63" t="str">
         <x:v>W4</x:v>
       </x:c>
@@ -14518,13 +18225,13 @@
         <x:v>2026-11-09 至 2026-11-15</x:v>
       </x:c>
       <x:c r="C51" s="63" t="str">
-        <x:v>复核主业务链、累计成本基准和完成工作预算口径</x:v>
+        <x:v>主业务链与质量覆盖，复核累计成本及需求变更影响</x:v>
       </x:c>
       <x:c r="D51" s="63" t="str">
-        <x:v>阶段重点复核与受控修订</x:v>
+        <x:v>阶段评审记录、缺陷与受控修订</x:v>
       </x:c>
       <x:c r="E51" s="63" t="str">
-        <x:v>R01编制／R04复核（模拟角色）</x:v>
+        <x:v>R01维护；原分配成员提供证据</x:v>
       </x:c>
       <x:c r="F51" s="69"/>
       <x:c r="G51" s="63"/>
@@ -14533,7 +18240,7 @@
       <x:c r="J51" s="63"/>
       <x:c r="K51" s="63"/>
     </x:row>
-    <x:row r="52" ht="84" customHeight="1">
+    <x:row r="52" ht="96" customHeight="1">
       <x:c r="A52" s="63" t="str">
         <x:v>W5</x:v>
       </x:c>
@@ -14541,13 +18248,13 @@
         <x:v>2026-11-16 至 2026-11-22</x:v>
       </x:c>
       <x:c r="C52" s="63" t="str">
-        <x:v>复核模块集成、剩余工作量及外部条件变化</x:v>
+        <x:v>模块集成、MOCK/REAL边界、剩余验证工作和依赖</x:v>
       </x:c>
       <x:c r="D52" s="63" t="str">
-        <x:v>集成阶段估算前提与风险说明</x:v>
+        <x:v>集成证据、待验证项及风险说明</x:v>
       </x:c>
       <x:c r="E52" s="63" t="str">
-        <x:v>R01编制／R04复核（模拟角色）</x:v>
+        <x:v>R01维护；原分配成员提供证据</x:v>
       </x:c>
       <x:c r="F52" s="69"/>
       <x:c r="G52" s="63"/>
@@ -14556,7 +18263,7 @@
       <x:c r="J52" s="63"/>
       <x:c r="K52" s="63"/>
     </x:row>
-    <x:row r="53" ht="84" customHeight="1">
+    <x:row r="53" ht="96" customHeight="1">
       <x:c r="A53" s="63" t="str">
         <x:v>W6</x:v>
       </x:c>
@@ -14564,13 +18271,13 @@
         <x:v>2026-11-23 至 2026-11-29</x:v>
       </x:c>
       <x:c r="C53" s="63" t="str">
-        <x:v>复核质量活动、验证费用及真实交换条件</x:v>
+        <x:v>功能/性能/安全/兼容验证安排及质量费用，核对真实输入</x:v>
       </x:c>
       <x:c r="D53" s="63" t="str">
-        <x:v>阶段重点复核与成本预测</x:v>
+        <x:v>阶段重点复核、验证证据及成本预测</x:v>
       </x:c>
       <x:c r="E53" s="63" t="str">
-        <x:v>R01编制／R04复核（模拟角色）</x:v>
+        <x:v>R01维护；原分配成员提供证据</x:v>
       </x:c>
       <x:c r="F53" s="69"/>
       <x:c r="G53" s="63"/>
@@ -14579,7 +18286,7 @@
       <x:c r="J53" s="63"/>
       <x:c r="K53" s="63"/>
     </x:row>
-    <x:row r="54" ht="84" customHeight="1">
+    <x:row r="54" ht="96" customHeight="1">
       <x:c r="A54" s="63" t="str">
         <x:v>W7</x:v>
       </x:c>
@@ -14587,13 +18294,13 @@
         <x:v>2026-11-30 至 2026-12-06</x:v>
       </x:c>
       <x:c r="C54" s="63" t="str">
-        <x:v>复核验证、缺陷修复和交付准备的进度成本影响</x:v>
+        <x:v>缺陷修复与非作者复测，72小时和恢复证据，交付准备</x:v>
       </x:c>
       <x:c r="D54" s="63" t="str">
-        <x:v>缺陷及成本偏差处理记录</x:v>
+        <x:v>缺陷闭环、回归及偏差处理记录</x:v>
       </x:c>
       <x:c r="E54" s="63" t="str">
-        <x:v>R01编制／R04复核（模拟角色）</x:v>
+        <x:v>R01维护；原分配成员提供证据</x:v>
       </x:c>
       <x:c r="F54" s="69"/>
       <x:c r="G54" s="63"/>
@@ -14602,7 +18309,7 @@
       <x:c r="J54" s="63"/>
       <x:c r="K54" s="63"/>
     </x:row>
-    <x:row r="55" ht="84" customHeight="1">
+    <x:row r="55" ht="96" customHeight="1">
       <x:c r="A55" s="63" t="str">
         <x:v>W8</x:v>
       </x:c>
@@ -14610,13 +18317,13 @@
         <x:v>2026-12-07 至 2026-12-13</x:v>
       </x:c>
       <x:c r="C55" s="63" t="str">
-        <x:v>复核最终计划、范围质量覆盖与全部真实变更证据</x:v>
+        <x:v>需求证据、交付门槛及真实历史；核对未完成项</x:v>
       </x:c>
       <x:c r="D55" s="63" t="str">
-        <x:v>最终计划、变更单与提交历史截图</x:v>
+        <x:v>最终计划、变更单及历史截图；未完成项如实登记</x:v>
       </x:c>
       <x:c r="E55" s="63" t="str">
-        <x:v>R01编制／R04复核（模拟角色）</x:v>
+        <x:v>R01维护；原分配成员提供证据</x:v>
       </x:c>
       <x:c r="F55" s="69"/>
       <x:c r="G55" s="63"/>
@@ -14728,6 +18435,908 @@
       </x:c>
       <x:c r="K59" s="63" t="str">
         <x:v>PV／AC／EV及偏差控制详见成本预算；识别的风险响应先使用已安排的防范工作与可用容量，独立应急储备金额待评估，不能直接以C14管理储备作资金承诺。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="28" customHeight="1">
+      <x:c r="A62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="B62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="C62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="D62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="E62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="F62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="G62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="H62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="I62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="J62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+      <x:c r="K62" s="86" t="str">
+        <x:v>全过程质量活动（纳入既有任务）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="44" customHeight="1">
+      <x:c r="A63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="B63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="C63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="D63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="E63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="F63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="G63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="H63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="I63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="J63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+      <x:c r="K63" s="79" t="str">
+        <x:v>质量保证检查过程和规范，质量控制检查具体成果。以下活动细化既有工作，不增加任务或投入；计划日期由原任务引用，实际日期、结论和证据在发生后登记。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="50" customHeight="1">
+      <x:c r="A65" s="86" t="str">
+        <x:v>编号</x:v>
+      </x:c>
+      <x:c r="B65" s="86" t="str">
+        <x:v>活动与类别</x:v>
+      </x:c>
+      <x:c r="C65" s="86" t="str">
+        <x:v>执行标准</x:v>
+      </x:c>
+      <x:c r="D65" s="86" t="str">
+        <x:v>依据</x:v>
+      </x:c>
+      <x:c r="E65" s="86" t="str">
+        <x:v>对应任务</x:v>
+      </x:c>
+      <x:c r="F65" s="86" t="str">
+        <x:v>责任与复核</x:v>
+      </x:c>
+      <x:c r="G65" s="86" t="str">
+        <x:v>实际日期/结果/证据</x:v>
+      </x:c>
+      <x:c r="H65" s="86" t="str">
+        <x:v>预定输出及条件</x:v>
+      </x:c>
+      <x:c r="I65" s="86" t="str">
+        <x:v>计划开始</x:v>
+      </x:c>
+      <x:c r="J65" s="86" t="str">
+        <x:v>计划结束</x:v>
+      </x:c>
+      <x:c r="K65" s="86" t="str">
+        <x:v>实施方法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="88" customHeight="1">
+      <x:c r="A66" s="79" t="str">
+        <x:v>QA01</x:v>
+      </x:c>
+      <x:c r="B66" s="79" t="str">
+        <x:v>质量保证：需求追踪与澄清</x:v>
+      </x:c>
+      <x:c r="C66" s="79" t="str">
+        <x:v>FR/NFR/IF逐项关联WBS、AC及已知边界；歧义登记并澄清，不以笼统表述代替可执行要求。</x:v>
+      </x:c>
+      <x:c r="D66" s="79" t="str">
+        <x:v>SRS第3–7、9–10章</x:v>
+      </x:c>
+      <x:c r="E66" s="79" t="str">
+        <x:v>T1.1</x:v>
+      </x:c>
+      <x:c r="F66" s="79" t="str">
+        <x:v>R01编制；R04交叉复核</x:v>
+      </x:c>
+      <x:c r="G66" s="79"/>
+      <x:c r="H66" s="79" t="str">
+        <x:v>需求映射、歧义及决定记录；实际确认人和结论留空。</x:v>
+      </x:c>
+      <x:c r="I66" s="80" t="n">
+        <x:f>MIN('任务与甘特'!T7)</x:f>
+        <x:v>46314</x:v>
+      </x:c>
+      <x:c r="J66" s="80" t="n">
+        <x:f>MAX('任务与甘特'!U7)</x:f>
+        <x:v>46314</x:v>
+      </x:c>
+      <x:c r="K66" s="79" t="str">
+        <x:v>核对当前需求版本、业务状态、权限和指标含义，记录不符合项。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="88" customHeight="1">
+      <x:c r="A67" s="79" t="str">
+        <x:v>QA02</x:v>
+      </x:c>
+      <x:c r="B67" s="79" t="str">
+        <x:v>质量保证：测试设计及标准交底</x:v>
+      </x:c>
+      <x:c r="C67" s="79" t="str">
+        <x:v>测试大纲覆盖既定AC的正常、异常、边界及非功能场景；必需用例、环境和数据口径明确。</x:v>
+      </x:c>
+      <x:c r="D67" s="79" t="str">
+        <x:v>SRS第9章；Q01–Q16</x:v>
+      </x:c>
+      <x:c r="E67" s="79" t="str">
+        <x:v>T1.3</x:v>
+      </x:c>
+      <x:c r="F67" s="79" t="str">
+        <x:v>R04编制；R01交叉复核</x:v>
+      </x:c>
+      <x:c r="G67" s="79"/>
+      <x:c r="H67" s="79" t="str">
+        <x:v>测试大纲、合成数据和预期结果；未执行不填通过。</x:v>
+      </x:c>
+      <x:c r="I67" s="80" t="n">
+        <x:f>MIN('任务与甘特'!T9)</x:f>
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="J67" s="80" t="n">
+        <x:f>MAX('任务与甘特'!U9)</x:f>
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="K67" s="79" t="str">
+        <x:v>在实现前明确验收方法；在原测试设计投入内统一缺陷、证据和复测规则。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="88" customHeight="1">
+      <x:c r="A68" s="79" t="str">
+        <x:v>QA03</x:v>
+      </x:c>
+      <x:c r="B68" s="79" t="str">
+        <x:v>质量保证：设计交叉复核</x:v>
+      </x:c>
+      <x:c r="C68" s="79" t="str">
+        <x:v>架构、数据、状态、接口相互一致；核对权限、事务、分页、负载及外部协议前提。</x:v>
+      </x:c>
+      <x:c r="D68" s="79" t="str">
+        <x:v>FR/NFR/IF对应设计</x:v>
+      </x:c>
+      <x:c r="E68" s="79" t="str">
+        <x:v>T2.1–T2.4</x:v>
+      </x:c>
+      <x:c r="F68" s="79" t="str">
+        <x:v>按原责任及分配互核</x:v>
+      </x:c>
+      <x:c r="G68" s="79"/>
+      <x:c r="H68" s="79" t="str">
+        <x:v>设计版本、评审标注与问题处理；外部协议缺失保持未确认。</x:v>
+      </x:c>
+      <x:c r="I68" s="80" t="n">
+        <x:f>MIN('任务与甘特'!T10,'任务与甘特'!T11,'任务与甘特'!T12,'任务与甘特'!T13)</x:f>
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="J68" s="80" t="n">
+        <x:f>MAX('任务与甘特'!U10,'任务与甘特'!U11,'任务与甘特'!U12,'任务与甘特'!U13)</x:f>
+        <x:v>46323</x:v>
+      </x:c>
+      <x:c r="K68" s="79" t="str">
+        <x:v>按资源计划责任矩阵安排非作者复核；需求或契约变化先评估CR。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="88" customHeight="1">
+      <x:c r="A69" s="79" t="str">
+        <x:v>QA04</x:v>
+      </x:c>
+      <x:c r="B69" s="79" t="str">
+        <x:v>质量保证：开发与集成过程</x:v>
+      </x:c>
+      <x:c r="C69" s="79" t="str">
+        <x:v>按既定接口小批量提交、集成并验证相关场景；代码或文档复核记录具体版本和问题。</x:v>
+      </x:c>
+      <x:c r="D69" s="79" t="str">
+        <x:v>SRS；既定开发规范</x:v>
+      </x:c>
+      <x:c r="E69" s="79" t="str">
+        <x:v>T3.1–T3.19</x:v>
+      </x:c>
+      <x:c r="F69" s="79" t="str">
+        <x:v>原任务负责人及参与者</x:v>
+      </x:c>
+      <x:c r="G69" s="79"/>
+      <x:c r="H69" s="79" t="str">
+        <x:v>可审阅提交、交叉复核和相关验证证据；不预置未来提交。</x:v>
+      </x:c>
+      <x:c r="I69" s="80" t="n">
+        <x:f>MIN('任务与甘特'!T15,'任务与甘特'!T16,'任务与甘特'!T17,'任务与甘特'!T18,'任务与甘特'!T19,'任务与甘特'!T20,'任务与甘特'!T21,'任务与甘特'!T22,'任务与甘特'!T23,'任务与甘特'!T24,'任务与甘特'!T25,'任务与甘特'!T26,'任务与甘特'!T27,'任务与甘特'!T28,'任务与甘特'!T29,'任务与甘特'!T30,'任务与甘特'!T31,'任务与甘特'!T32,'任务与甘特'!T33)</x:f>
+        <x:v>46318</x:v>
+      </x:c>
+      <x:c r="J69" s="80" t="n">
+        <x:f>MAX('任务与甘特'!U15,'任务与甘特'!U16,'任务与甘特'!U17,'任务与甘特'!U18,'任务与甘特'!U19,'任务与甘特'!U20,'任务与甘特'!U21,'任务与甘特'!U22,'任务与甘特'!U23,'任务与甘特'!U24,'任务与甘特'!U25,'任务与甘特'!U26,'任务与甘特'!U27,'任务与甘特'!U28,'任务与甘特'!U29,'任务与甘特'!U30,'任务与甘特'!U31,'任务与甘特'!U32,'任务与甘特'!U33)</x:f>
+        <x:v>46345</x:v>
+      </x:c>
+      <x:c r="K69" s="79" t="str">
+        <x:v>在现有开发分配内复核输入、鉴权、状态、分页和错误处理，记录验证范围与结果。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="88" customHeight="1">
+      <x:c r="A70" s="79" t="str">
+        <x:v>QC01</x:v>
+      </x:c>
+      <x:c r="B70" s="79" t="str">
+        <x:v>质量控制：阶段成果评审</x:v>
+      </x:c>
+      <x:c r="C70" s="79" t="str">
+        <x:v>主业务链可对照既定AC演示；集成边界、失败路径和遗留缺陷明确，逐项记录达标情况。</x:v>
+      </x:c>
+      <x:c r="D70" s="79" t="str">
+        <x:v>SRS；Q01–Q16</x:v>
+      </x:c>
+      <x:c r="E70" s="79" t="str">
+        <x:v>T4.1/T4.2</x:v>
+      </x:c>
+      <x:c r="F70" s="79" t="str">
+        <x:v>R01/R02主责；R04复核</x:v>
+      </x:c>
+      <x:c r="G70" s="79"/>
+      <x:c r="H70" s="79" t="str">
+        <x:v>阶段版本、预期/实际结果、未通过项及处置。</x:v>
+      </x:c>
+      <x:c r="I70" s="80" t="n">
+        <x:f>MIN('任务与甘特'!T34,'任务与甘特'!T35)</x:f>
+        <x:v>46346</x:v>
+      </x:c>
+      <x:c r="J70" s="80" t="n">
+        <x:f>MAX('任务与甘特'!U34,'任务与甘特'!U35)</x:f>
+        <x:v>46350</x:v>
+      </x:c>
+      <x:c r="K70" s="79" t="str">
+        <x:v>检查成果是否满足标准；不以过程文档齐全代替业务结果。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="88" customHeight="1">
+      <x:c r="A71" s="79" t="str">
+        <x:v>QC02</x:v>
+      </x:c>
+      <x:c r="B71" s="79" t="str">
+        <x:v>质量控制：修复与复测闭环</x:v>
+      </x:c>
+      <x:c r="C71" s="79" t="str">
+        <x:v>执行既定测试，发现问题后分级、定位、修复、非作者复测；不合格项关闭或记录影响。</x:v>
+      </x:c>
+      <x:c r="D71" s="79" t="str">
+        <x:v>SRS 9.4；Q01–Q16</x:v>
+      </x:c>
+      <x:c r="E71" s="79" t="str">
+        <x:v>T4.3–T4.10/T5.2</x:v>
+      </x:c>
+      <x:c r="F71" s="79" t="str">
+        <x:v>原测试/修复责任人</x:v>
+      </x:c>
+      <x:c r="G71" s="79"/>
+      <x:c r="H71" s="79" t="str">
+        <x:v>缺陷号、关联AC、修复版本、复测人与结果；真实接收证据单列。</x:v>
+      </x:c>
+      <x:c r="I71" s="80" t="n">
+        <x:f>MIN('任务与甘特'!T36,'任务与甘特'!T37,'任务与甘特'!T38,'任务与甘特'!T39,'任务与甘特'!T40,'任务与甘特'!T41,'任务与甘特'!T42,'任务与甘特'!T43,'任务与甘特'!T45)</x:f>
+        <x:v>46343</x:v>
+      </x:c>
+      <x:c r="J71" s="80" t="n">
+        <x:f>MAX('任务与甘特'!U36,'任务与甘特'!U37,'任务与甘特'!U38,'任务与甘特'!U39,'任务与甘特'!U40,'任务与甘特'!U41,'任务与甘特'!U42,'任务与甘特'!U43,'任务与甘特'!U45)</x:f>
+        <x:v>46365</x:v>
+      </x:c>
+      <x:c r="K71" s="79" t="str">
+        <x:v>阻断严重功能缺陷及严重高危漏洞按原门槛控制；未通过不标记全部验收完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="88" customHeight="1">
+      <x:c r="A72" s="79" t="str">
+        <x:v>QA05</x:v>
+      </x:c>
+      <x:c r="B72" s="79" t="str">
+        <x:v>质量保证：配置与文档审计</x:v>
+      </x:c>
+      <x:c r="C72" s="79" t="str">
+        <x:v>当前源、导出和交付版本可对应；基线修订有CR、影响及真实提交证据；文件按用途收纳。</x:v>
+      </x:c>
+      <x:c r="D72" s="79" t="str">
+        <x:v>配置管理及交付规范</x:v>
+      </x:c>
+      <x:c r="E72" s="79" t="str">
+        <x:v>T2.5/T5.3/T5.5/T5.7</x:v>
+      </x:c>
+      <x:c r="F72" s="79" t="str">
+        <x:v>R01维护；原评审任务互核</x:v>
+      </x:c>
+      <x:c r="G72" s="79"/>
+      <x:c r="H72" s="79" t="str">
+        <x:v>版本映射、变更单、真实历史和交付证据索引。</x:v>
+      </x:c>
+      <x:c r="I72" s="80" t="n">
+        <x:f>MIN('任务与甘特'!T14,'任务与甘特'!T46,'任务与甘特'!T48,'任务与甘特'!T50)</x:f>
+        <x:v>46317</x:v>
+      </x:c>
+      <x:c r="J72" s="80" t="n">
+        <x:f>MAX('任务与甘特'!U14,'任务与甘特'!U46,'任务与甘特'!U48,'任务与甘特'!U50)</x:f>
+        <x:v>46367</x:v>
+      </x:c>
+      <x:c r="K72" s="79" t="str">
+        <x:v>T2.5日常登记由R01承担；R04仅在已有分配的评审任务内核对，不另计人时。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="88" customHeight="1">
+      <x:c r="A73" s="79" t="str">
+        <x:v>QA06</x:v>
+      </x:c>
+      <x:c r="B73" s="79" t="str">
+        <x:v>质量保证：复核与改进</x:v>
+      </x:c>
+      <x:c r="C73" s="79" t="str">
+        <x:v>每轮核对质量活动及不符合项原因，明确纠正措施、责任、期限和转入轮次；检查措施效果。</x:v>
+      </x:c>
+      <x:c r="D73" s="79" t="str">
+        <x:v>W1–W8维护规则</x:v>
+      </x:c>
+      <x:c r="E73" s="79" t="str">
+        <x:v>T1.2/T2.5/T4.1/T5.7</x:v>
+      </x:c>
+      <x:c r="F73" s="79" t="str">
+        <x:v>R01组织；原分配成员参与</x:v>
+      </x:c>
+      <x:c r="G73" s="79"/>
+      <x:c r="H73" s="79" t="str">
+        <x:v>周复核、根因及改进措施；实际复核日期和效果留空。</x:v>
+      </x:c>
+      <x:c r="I73" s="80" t="n">
+        <x:f>MIN('任务与甘特'!T8,'任务与甘特'!T14,'任务与甘特'!T34,'任务与甘特'!T50)</x:f>
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="J73" s="80" t="n">
+        <x:f>MAX('任务与甘特'!U8,'任务与甘特'!U14,'任务与甘特'!U34,'任务与甘特'!U50)</x:f>
+        <x:v>46367</x:v>
+      </x:c>
+      <x:c r="K73" s="79" t="str">
+        <x:v>在既有计划维护与阶段评审内完成；影响范围、资源、日期、费用或验收基线时办理CR。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="48" customHeight="1">
+      <x:c r="A75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="B75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="C75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="D75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="E75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="F75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="G75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="H75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="I75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="J75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+      <x:c r="K75" s="79" t="str">
+        <x:v>四人兼岗采用成果层面的非作者交叉复核。R04参与编码或部署时，其产物由其他已分配成员复核；无合格复核人时登记未复核并由R01评估影响。实际签字不代填，不认定已建立独立质量部门。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="28" customHeight="1">
+      <x:c r="A78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="B78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="C78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="D78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="E78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="F78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="G78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="H78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="I78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="J78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+      <x:c r="K78" s="86" t="str">
+        <x:v>质量度量与执行记录（实际值留空）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="40" customHeight="1">
+      <x:c r="A79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="B79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="C79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="D79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="E79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="F79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="G79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="H79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="I79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="J79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+      <x:c r="K79" s="79" t="str">
+        <x:v>目标引用现有SRS和Q01–Q16。比例须有明确分子、分母和证据；未执行不等于零缺陷或已通过，不另设未经定义的加权总分。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="50" customHeight="1">
+      <x:c r="A81" s="86" t="str">
+        <x:v>编号</x:v>
+      </x:c>
+      <x:c r="B81" s="86" t="str">
+        <x:v>度量对象</x:v>
+      </x:c>
+      <x:c r="C81" s="86" t="str">
+        <x:v>度量与统计口径</x:v>
+      </x:c>
+      <x:c r="D81" s="86" t="str">
+        <x:v>目标/通过条件</x:v>
+      </x:c>
+      <x:c r="E81" s="86" t="str">
+        <x:v>采集任务</x:v>
+      </x:c>
+      <x:c r="F81" s="86" t="str">
+        <x:v>责任角色</x:v>
+      </x:c>
+      <x:c r="G81" s="86" t="str">
+        <x:v>实际值</x:v>
+      </x:c>
+      <x:c r="H81" s="86" t="str">
+        <x:v>实际证据/版本</x:v>
+      </x:c>
+      <x:c r="I81" s="86" t="str">
+        <x:v>测量日期</x:v>
+      </x:c>
+      <x:c r="J81" s="86" t="str">
+        <x:v>结论</x:v>
+      </x:c>
+      <x:c r="K81" s="86" t="str">
+        <x:v>处理措施</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="88" customHeight="1">
+      <x:c r="A82" s="79" t="str">
+        <x:v>QM01</x:v>
+      </x:c>
+      <x:c r="B82" s="79" t="str">
+        <x:v>需求追踪覆盖</x:v>
+      </x:c>
+      <x:c r="C82" s="79" t="str">
+        <x:v>具备WBS及AC映射的有效需求数÷当前基线有效需求总数；分母随正式需求版本核对。</x:v>
+      </x:c>
+      <x:c r="D82" s="79" t="str">
+        <x:v>FR/NFR/IF逐项覆盖，沿用43项基线，不预置已完成比例。</x:v>
+      </x:c>
+      <x:c r="E82" s="79" t="str">
+        <x:v>T1.1/T1.3/T5.6</x:v>
+      </x:c>
+      <x:c r="F82" s="79" t="str">
+        <x:v>R01/R04</x:v>
+      </x:c>
+      <x:c r="G82" s="79"/>
+      <x:c r="H82" s="79"/>
+      <x:c r="I82" s="80"/>
+      <x:c r="J82" s="79"/>
+      <x:c r="K82" s="79"/>
+    </x:row>
+    <x:row r="83" ht="88" customHeight="1">
+      <x:c r="A83" s="79" t="str">
+        <x:v>QM02</x:v>
+      </x:c>
+      <x:c r="B83" s="79" t="str">
+        <x:v>关键必需测试</x:v>
+      </x:c>
+      <x:c r="C83" s="79" t="str">
+        <x:v>通过的关键必需用例数÷已确认关键必需用例数；未执行、阻塞、失败分别登记。</x:v>
+      </x:c>
+      <x:c r="D83" s="79" t="str">
+        <x:v>最终验收关键必需测试100%；边界和失败路径按SRS验证。</x:v>
+      </x:c>
+      <x:c r="E83" s="79" t="str">
+        <x:v>T4.3–T4.9/T5.6</x:v>
+      </x:c>
+      <x:c r="F83" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="G83" s="79"/>
+      <x:c r="H83" s="79"/>
+      <x:c r="I83" s="80"/>
+      <x:c r="J83" s="79"/>
+      <x:c r="K83" s="79"/>
+    </x:row>
+    <x:row r="84" ht="88" customHeight="1">
+      <x:c r="A84" s="79" t="str">
+        <x:v>QM03</x:v>
+      </x:c>
+      <x:c r="B84" s="79" t="str">
+        <x:v>未关闭阻断严重缺陷</x:v>
+      </x:c>
+      <x:c r="C84" s="79" t="str">
+        <x:v>按当前验收版本统计未关闭的阻断、严重功能缺陷，不把未测试视为无缺陷。</x:v>
+      </x:c>
+      <x:c r="D84" s="79" t="str">
+        <x:v>阻断严重功能缺陷0，沿用SRS 9.4；其他缺陷记录影响与修复版本。</x:v>
+      </x:c>
+      <x:c r="E84" s="79" t="str">
+        <x:v>T4.10/T5.6</x:v>
+      </x:c>
+      <x:c r="F84" s="79" t="str">
+        <x:v>R02/R04</x:v>
+      </x:c>
+      <x:c r="G84" s="79"/>
+      <x:c r="H84" s="79"/>
+      <x:c r="I84" s="80"/>
+      <x:c r="J84" s="79"/>
+      <x:c r="K84" s="79"/>
+    </x:row>
+    <x:row r="85" ht="88" customHeight="1">
+      <x:c r="A85" s="79" t="str">
+        <x:v>QM04</x:v>
+      </x:c>
+      <x:c r="B85" s="79" t="str">
+        <x:v>严重高危漏洞</x:v>
+      </x:c>
+      <x:c r="C85" s="79" t="str">
+        <x:v>对既定安全范围的扫描、人工验证和修复复测按相同版本统计。</x:v>
+      </x:c>
+      <x:c r="D85" s="79" t="str">
+        <x:v>严重高危漏洞0；其余缺陷登记影响和工程修复版本。</x:v>
+      </x:c>
+      <x:c r="E85" s="79" t="str">
+        <x:v>T4.6/T4.10</x:v>
+      </x:c>
+      <x:c r="F85" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="G85" s="79"/>
+      <x:c r="H85" s="79"/>
+      <x:c r="I85" s="80"/>
+      <x:c r="J85" s="79"/>
+      <x:c r="K85" s="79"/>
+    </x:row>
+    <x:row r="86" ht="88" customHeight="1">
+      <x:c r="A86" s="79" t="str">
+        <x:v>QM05</x:v>
+      </x:c>
+      <x:c r="B86" s="79" t="str">
+        <x:v>性能与兼容达标</x:v>
+      </x:c>
+      <x:c r="C86" s="79" t="str">
+        <x:v>按Q11–Q15分别记录负载、P95、导出、恢复、浏览器和环境结果，不合并成无依据总分。</x:v>
+      </x:c>
+      <x:c r="D86" s="79" t="str">
+        <x:v>沿用Q11–Q15及SRS量化阈值；72小时验证不替代月可用性持续目标。</x:v>
+      </x:c>
+      <x:c r="E86" s="79" t="str">
+        <x:v>T4.7/T4.8/T4.9</x:v>
+      </x:c>
+      <x:c r="F86" s="79" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="G86" s="79"/>
+      <x:c r="H86" s="79"/>
+      <x:c r="I86" s="80"/>
+      <x:c r="J86" s="79"/>
+      <x:c r="K86" s="79"/>
+    </x:row>
+    <x:row r="87" ht="88" customHeight="1">
+      <x:c r="A87" s="79" t="str">
+        <x:v>QM06</x:v>
+      </x:c>
+      <x:c r="B87" s="79" t="str">
+        <x:v>质量活动与问题闭环</x:v>
+      </x:c>
+      <x:c r="C87" s="79" t="str">
+        <x:v>记录应执行活动、实际证据、发现项、关闭/重开和转入；无证据不算已完成。</x:v>
+      </x:c>
+      <x:c r="D87" s="79" t="str">
+        <x:v>验收前处理影响基线或通过门槛的未闭环项；其余项明确责任、期限和影响。</x:v>
+      </x:c>
+      <x:c r="E87" s="79" t="str">
+        <x:v>QA01–QA06/QC01–QC02</x:v>
+      </x:c>
+      <x:c r="F87" s="79" t="str">
+        <x:v>R01及原责任人</x:v>
+      </x:c>
+      <x:c r="G87" s="79"/>
+      <x:c r="H87" s="79"/>
+      <x:c r="I87" s="80"/>
+      <x:c r="J87" s="79"/>
+      <x:c r="K87" s="79"/>
+    </x:row>
+    <x:row r="89" ht="44" customHeight="1">
+      <x:c r="A89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="B89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="C89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="D89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="E89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="F89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="G89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="H89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="I89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="J89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+      <x:c r="K89" s="79" t="str">
+        <x:v>最终放行沿用SRS 9.4–9.5：逐项需求证据、边界与失败路径、关键必需测试、功能缺陷及安全门槛均满足；实际REAL验证缺失时保留未完成。月可用性持续目标不以72小时验证替代。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="28" customHeight="1">
+      <x:c r="A92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="B92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="C92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="D92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="E92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="F92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="G92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="H92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="I92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="J92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+      <x:c r="K92" s="86" t="str">
+        <x:v>缺陷、不符合项与改进登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="44" customHeight="1">
+      <x:c r="A93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="B93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="C93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="D93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="E93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="F93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="G93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="H93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="I93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="J93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+      <x:c r="K93" s="79" t="str">
+        <x:v>发现后登记编号、影响和责任，分析根因，关联修复版本，由非作者复测；通过后关闭，未通过重开。未完成项记录原因和转入轮次；涉及受控范围、验收、排期或预算变化时办理CR。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="50" customHeight="1">
+      <x:c r="A95" s="86" t="str">
+        <x:v>缺陷/问题号</x:v>
+      </x:c>
+      <x:c r="B95" s="86" t="str">
+        <x:v>需求/AC</x:v>
+      </x:c>
+      <x:c r="C95" s="86" t="str">
+        <x:v>严重度/影响</x:v>
+      </x:c>
+      <x:c r="D95" s="86" t="str">
+        <x:v>发现日期/阶段</x:v>
+      </x:c>
+      <x:c r="E95" s="86" t="str">
+        <x:v>责任人</x:v>
+      </x:c>
+      <x:c r="F95" s="86" t="str">
+        <x:v>根因/措施</x:v>
+      </x:c>
+      <x:c r="G95" s="86" t="str">
+        <x:v>修复版本</x:v>
+      </x:c>
+      <x:c r="H95" s="86" t="str">
+        <x:v>复测人/结果</x:v>
+      </x:c>
+      <x:c r="I95" s="86" t="str">
+        <x:v>关闭日期</x:v>
+      </x:c>
+      <x:c r="J95" s="86" t="str">
+        <x:v>质量成本类别</x:v>
+      </x:c>
+      <x:c r="K95" s="86" t="str">
+        <x:v>关联CR/证据</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="72" customHeight="1">
+      <x:c r="A96" s="79"/>
+      <x:c r="B96" s="79"/>
+      <x:c r="C96" s="79"/>
+      <x:c r="D96" s="79"/>
+      <x:c r="E96" s="79"/>
+      <x:c r="F96" s="79"/>
+      <x:c r="G96" s="79"/>
+      <x:c r="H96" s="79"/>
+      <x:c r="I96" s="80"/>
+      <x:c r="J96" s="79"/>
+      <x:c r="K96" s="79"/>
+    </x:row>
+    <x:row r="97" ht="72" customHeight="1">
+      <x:c r="A97" s="79"/>
+      <x:c r="B97" s="79"/>
+      <x:c r="C97" s="79"/>
+      <x:c r="D97" s="79"/>
+      <x:c r="E97" s="79"/>
+      <x:c r="F97" s="79"/>
+      <x:c r="G97" s="79"/>
+      <x:c r="H97" s="79"/>
+      <x:c r="I97" s="80"/>
+      <x:c r="J97" s="79"/>
+      <x:c r="K97" s="79"/>
+    </x:row>
+    <x:row r="98" ht="72" customHeight="1">
+      <x:c r="A98" s="79"/>
+      <x:c r="B98" s="79"/>
+      <x:c r="C98" s="79"/>
+      <x:c r="D98" s="79"/>
+      <x:c r="E98" s="79"/>
+      <x:c r="F98" s="79"/>
+      <x:c r="G98" s="79"/>
+      <x:c r="H98" s="79"/>
+      <x:c r="I98" s="80"/>
+      <x:c r="J98" s="79"/>
+      <x:c r="K98" s="79"/>
+    </x:row>
+    <x:row r="99" ht="72" customHeight="1">
+      <x:c r="A99" s="79"/>
+      <x:c r="B99" s="79"/>
+      <x:c r="C99" s="79"/>
+      <x:c r="D99" s="79"/>
+      <x:c r="E99" s="79"/>
+      <x:c r="F99" s="79"/>
+      <x:c r="G99" s="79"/>
+      <x:c r="H99" s="79"/>
+      <x:c r="I99" s="80"/>
+      <x:c r="J99" s="79"/>
+      <x:c r="K99" s="79"/>
+    </x:row>
+    <x:row r="101" ht="40" customHeight="1">
+      <x:c r="A101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="B101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="C101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="D101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="E101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="F101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="G101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="H101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="I101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="J101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
+      </x:c>
+      <x:c r="K101" s="79" t="str">
+        <x:v>问题记录只填写真实发现和处理情况；计划编制不等于开发或验收完成。质量费用按成本预算分类记录，已包含的人工和资源费用不再次加算。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14737,6 +19346,15 @@
     <x:mergeCell ref="A57:K57"/>
     <x:mergeCell ref="A58:K58"/>
     <x:mergeCell ref="A59:K59"/>
+    <x:mergeCell ref="A62:K62"/>
+    <x:mergeCell ref="A63:K63"/>
+    <x:mergeCell ref="A75:K75"/>
+    <x:mergeCell ref="A78:K78"/>
+    <x:mergeCell ref="A79:K79"/>
+    <x:mergeCell ref="A89:K89"/>
+    <x:mergeCell ref="A92:K92"/>
+    <x:mergeCell ref="A93:K93"/>
+    <x:mergeCell ref="A101:K101"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
